--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/jun-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/jun-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>6084.56</v>
+        <v>6171.63</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>11527.62</v>
+        <v>11692.57</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>4202.69</v>
+        <v>4262.83</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>869.11</v>
+        <v>881.54</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>18902.8</v>
+        <v>19173.28</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2453.68</v>
+        <v>2488.79</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1533.04</v>
+        <v>1554.97</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2192.53</v>
+        <v>2223.91</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>11091.17</v>
+        <v>11249.87</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1744.85</v>
+        <v>1769.82</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>832.96</v>
+        <v>844.88</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2346.06</v>
+        <v>2379.63</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1090.62</v>
+        <v>1106.23</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>3204.1</v>
+        <v>3249.95</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>828.63</v>
+        <v>840.48</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>6483.6</v>
+        <v>6576.37</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1106.88</v>
+        <v>1122.72</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>4347.51</v>
+        <v>4409.72</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>893.88</v>
+        <v>906.67</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>5429.74</v>
+        <v>5507.44</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1105.08</v>
+        <v>1120.89</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>10455.63</v>
+        <v>10605.24</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1573.93</v>
+        <v>1596.45</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1878.1</v>
+        <v>1904.97</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>5482.25</v>
+        <v>5560.7</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>28144.73</v>
+        <v>28547.46</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1100.92</v>
+        <v>1116.67</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>3137.68</v>
+        <v>3174.48</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>7318.61</v>
+        <v>7404.47</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1439.35</v>
+        <v>1456.23</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>6335.54</v>
+        <v>6409.86</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>5595.76</v>
+        <v>5661.4</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1718.96</v>
+        <v>1739.13</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>17439.8</v>
+        <v>17644.37</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>14002.57</v>
+        <v>14166.83</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>4880.96</v>
+        <v>4938.22</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>55714.85</v>
+        <v>56368.41</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2055.85</v>
+        <v>2079.96</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>3406.54</v>
+        <v>3446.5</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>949.38</v>
+        <v>960.52</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1279.2</v>
+        <v>1294.21</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1106.42</v>
+        <v>1119.4</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>3590.74</v>
+        <v>3632.86</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>870.17</v>
+        <v>880.38</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>8354.709999999999</v>
+        <v>8452.709999999999</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>794.91</v>
+        <v>804.24</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1058.97</v>
+        <v>1071.39</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>4292.22</v>
+        <v>4342.57</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>4916.15</v>
+        <v>4973.82</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>2142.85</v>
+        <v>2167.99</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>857</v>
+        <v>867.0599999999999</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>25472.43</v>
+        <v>25771.24</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>9110.780000000001</v>
+        <v>9217.66</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>6935.42</v>
+        <v>7016.78</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>892.3200000000001</v>
+        <v>902.79</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>4423.65</v>
+        <v>4475.54</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1349.69</v>
+        <v>1365.52</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>990.63</v>
+        <v>1002.25</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>876.4</v>
+        <v>886.6799999999999</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>786.13</v>
+        <v>795.35</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>4668.27</v>
+        <v>4723.03</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>834.62</v>
+        <v>844.41</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>4663.13</v>
+        <v>4717.83</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>3116.13</v>
+        <v>3152.69</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>7027.63</v>
+        <v>7110.07</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>60130.69</v>
+        <v>60836.05</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>2384.06</v>
+        <v>2412.03</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1415.04</v>
+        <v>1431.64</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1770.34</v>
+        <v>1791.11</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>13809.42</v>
+        <v>13971.41</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>4511.25</v>
+        <v>4564.17</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>17024.73</v>
+        <v>17224.44</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>4413.38</v>
+        <v>4465.15</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>3075.94</v>
+        <v>3112.02</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>792.24</v>
+        <v>801.53</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>976.9</v>
+        <v>988.36</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>6799.8</v>
+        <v>6879.56</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>32690.54</v>
+        <v>33243.42</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>4427.73</v>
+        <v>4502.61</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>3165.41</v>
+        <v>3218.95</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>4436.79</v>
+        <v>4511.83</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>1470.31</v>
+        <v>1495.18</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>849.1900000000001</v>
+        <v>863.5599999999999</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>4726.36</v>
+        <v>4806.29</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>22340.88</v>
+        <v>22718.72</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1674.18</v>
+        <v>1702.5</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1971.98</v>
+        <v>2005.33</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>8452.49</v>
+        <v>8595.440000000001</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>49397.58</v>
+        <v>50233.01</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1204.51</v>
+        <v>1224.88</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>1254.64</v>
+        <v>1275.86</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>1622.77</v>
+        <v>1650.21</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>848.97</v>
+        <v>863.3200000000001</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>2124.37</v>
+        <v>2160.3</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>6634.82</v>
+        <v>6747.03</v>
       </c>
     </row>
     <row r="97">
@@ -6368,7 +6368,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>40521.43</v>
+        <v>41206.74</v>
       </c>
     </row>
     <row r="98">
@@ -6429,7 +6429,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>1638.53</v>
+        <v>1666.24</v>
       </c>
     </row>
     <row r="99">
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>4341.09</v>
+        <v>4414.51</v>
       </c>
     </row>
     <row r="100">
@@ -6551,7 +6551,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>24896.38</v>
+        <v>25317.44</v>
       </c>
     </row>
     <row r="101">
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>2658.95</v>
+        <v>2703.91</v>
       </c>
     </row>
     <row r="102">
@@ -6673,7 +6673,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>2777.79</v>
+        <v>2824.77</v>
       </c>
     </row>
     <row r="103">
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>961</v>
+        <v>977.26</v>
       </c>
     </row>
     <row r="104">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>1021.7</v>
+        <v>1038.98</v>
       </c>
     </row>
     <row r="105">
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>2309.27</v>
+        <v>2348.32</v>
       </c>
     </row>
     <row r="106">
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>7312.55</v>
+        <v>7436.23</v>
       </c>
     </row>
     <row r="107">
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2542.65</v>
+        <v>2585.66</v>
       </c>
     </row>
     <row r="108">
@@ -7039,7 +7039,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>14661.3</v>
+        <v>14909.26</v>
       </c>
     </row>
     <row r="109">
@@ -7100,7 +7100,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>5158.27</v>
+        <v>5245.51</v>
       </c>
     </row>
     <row r="110">
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>783.51</v>
+        <v>796.76</v>
       </c>
     </row>
     <row r="111">
@@ -7222,7 +7222,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>1126.66</v>
+        <v>1145.71</v>
       </c>
     </row>
     <row r="112">
@@ -7283,7 +7283,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>1426.8</v>
+        <v>1450.93</v>
       </c>
     </row>
     <row r="113">
@@ -7344,7 +7344,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>5161.5</v>
+        <v>5248.79</v>
       </c>
     </row>
     <row r="114">
@@ -7405,7 +7405,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>2653.48</v>
+        <v>2698.36</v>
       </c>
     </row>
     <row r="115">
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>4947.28</v>
+        <v>5030.95</v>
       </c>
     </row>
     <row r="116">
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>9401.139999999999</v>
+        <v>9560.139999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>2676.74</v>
+        <v>2722.01</v>
       </c>
     </row>
     <row r="118">
@@ -7649,7 +7649,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>2727.35</v>
+        <v>2773.47</v>
       </c>
     </row>
     <row r="119">
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1649.17</v>
+        <v>1677.06</v>
       </c>
     </row>
     <row r="120">
@@ -7771,7 +7771,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>1573.32</v>
+        <v>1599.93</v>
       </c>
     </row>
     <row r="121">
@@ -7832,7 +7832,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>3488.67</v>
+        <v>3547.67</v>
       </c>
     </row>
     <row r="122">
@@ -7893,7 +7893,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>2219.93</v>
+        <v>2257.48</v>
       </c>
     </row>
     <row r="123">
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>3504.59</v>
+        <v>3563.86</v>
       </c>
     </row>
     <row r="124">
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>1445.45</v>
+        <v>1469.9</v>
       </c>
     </row>
     <row r="125">
@@ -8076,7 +8076,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>11073.17</v>
+        <v>11260.44</v>
       </c>
     </row>
     <row r="126">
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>2503.97</v>
+        <v>2546.32</v>
       </c>
     </row>
     <row r="127">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>2864.66</v>
+        <v>2913.11</v>
       </c>
     </row>
     <row r="128">
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>3793.25</v>
+        <v>3831.83</v>
       </c>
     </row>
     <row r="129">
@@ -8320,7 +8320,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>2199.3</v>
+        <v>2221.66</v>
       </c>
     </row>
     <row r="130">
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>2316.29</v>
+        <v>2339.84</v>
       </c>
     </row>
     <row r="131">
@@ -8442,7 +8442,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>1295.17</v>
+        <v>1308.34</v>
       </c>
     </row>
     <row r="132">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>2922.62</v>
+        <v>2952.35</v>
       </c>
     </row>
     <row r="133">
@@ -8564,7 +8564,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>1161.01</v>
+        <v>1172.82</v>
       </c>
     </row>
     <row r="134">
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>873.74</v>
+        <v>882.63</v>
       </c>
     </row>
     <row r="135">
@@ -8686,7 +8686,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>3836.55</v>
+        <v>3875.56</v>
       </c>
     </row>
     <row r="136">
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>3460.14</v>
+        <v>3495.32</v>
       </c>
     </row>
     <row r="137">
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>1456.32</v>
+        <v>1471.13</v>
       </c>
     </row>
     <row r="138">
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>2364.76</v>
+        <v>2388.81</v>
       </c>
     </row>
     <row r="139">
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>2584.48</v>
+        <v>2610.76</v>
       </c>
     </row>
     <row r="140">
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1910.51</v>
+        <v>1929.94</v>
       </c>
     </row>
     <row r="141">
@@ -9052,7 +9052,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>2739.81</v>
+        <v>2767.68</v>
       </c>
     </row>
     <row r="142">
@@ -9113,7 +9113,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>16075.95</v>
+        <v>16239.43</v>
       </c>
     </row>
     <row r="143">
@@ -9174,7 +9174,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>4789.98</v>
+        <v>4838.7</v>
       </c>
     </row>
     <row r="144">
@@ -9235,7 +9235,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>1702.7</v>
+        <v>1720.02</v>
       </c>
     </row>
     <row r="145">
@@ -9296,7 +9296,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>1301.33</v>
+        <v>1314.56</v>
       </c>
     </row>
     <row r="146">
@@ -9357,7 +9357,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>1763.4</v>
+        <v>1781.33</v>
       </c>
     </row>
     <row r="147">
@@ -9418,7 +9418,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>4017.95</v>
+        <v>4058.81</v>
       </c>
     </row>
     <row r="148">
@@ -9479,7 +9479,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>3042.36</v>
+        <v>3073.3</v>
       </c>
     </row>
     <row r="149">
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>1187.11</v>
+        <v>1199.18</v>
       </c>
     </row>
     <row r="150">
@@ -9601,7 +9601,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>3840.73</v>
+        <v>3879.79</v>
       </c>
     </row>
     <row r="151">
@@ -9662,7 +9662,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>1909.93</v>
+        <v>1929.35</v>
       </c>
     </row>
     <row r="152">
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>2431.78</v>
+        <v>2456.51</v>
       </c>
     </row>
     <row r="153">
@@ -9784,7 +9784,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>1962.2</v>
+        <v>1982.16</v>
       </c>
     </row>
     <row r="154">
@@ -9845,7 +9845,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>2087.89</v>
+        <v>2109.13</v>
       </c>
     </row>
     <row r="155">
@@ -9906,7 +9906,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>2098.6</v>
+        <v>2119.95</v>
       </c>
     </row>
     <row r="156">
@@ -9967,7 +9967,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>1106.94</v>
+        <v>1118.2</v>
       </c>
     </row>
     <row r="157">
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>3457.15</v>
+        <v>3492.3</v>
       </c>
     </row>
     <row r="158">
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>1474.51</v>
+        <v>1489.5</v>
       </c>
     </row>
     <row r="159">
@@ -10150,7 +10150,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>943.9</v>
+        <v>953.5</v>
       </c>
     </row>
     <row r="160">
@@ -10211,7 +10211,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>948.4299999999999</v>
+        <v>958.08</v>
       </c>
     </row>
     <row r="161">
@@ -10272,7 +10272,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>8958.75</v>
+        <v>9049.85</v>
       </c>
     </row>
     <row r="162">
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>2213.76</v>
+        <v>2236.27</v>
       </c>
     </row>
     <row r="163">
@@ -10394,7 +10394,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>845.92</v>
+        <v>854.52</v>
       </c>
     </row>
     <row r="164">
@@ -10455,7 +10455,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>8737.040000000001</v>
+        <v>8825.889999999999</v>
       </c>
     </row>
     <row r="165">
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>2526.03</v>
+        <v>2551.71</v>
       </c>
     </row>
     <row r="166">
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>5560.53</v>
+        <v>5617.07</v>
       </c>
     </row>
     <row r="167">
@@ -10638,7 +10638,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>2239.98</v>
+        <v>2262.76</v>
       </c>
     </row>
     <row r="168">
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>3013.1</v>
+        <v>3043.75</v>
       </c>
     </row>
     <row r="169">
@@ -10760,7 +10760,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>871.65</v>
+        <v>880.51</v>
       </c>
     </row>
     <row r="170">
@@ -10821,7 +10821,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>13964.62</v>
+        <v>14106.63</v>
       </c>
     </row>
     <row r="171">
@@ -10882,7 +10882,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>14560.76</v>
+        <v>14708.83</v>
       </c>
     </row>
     <row r="172">
@@ -10943,7 +10943,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>3525.67</v>
+        <v>3561.52</v>
       </c>
     </row>
     <row r="173">
@@ -11004,7 +11004,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>784.58</v>
+        <v>792.55</v>
       </c>
     </row>
     <row r="174">
@@ -11065,7 +11065,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>791.67</v>
+        <v>799.72</v>
       </c>
     </row>
     <row r="175">
@@ -11126,7 +11126,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>16812.99</v>
+        <v>16983.97</v>
       </c>
     </row>
     <row r="176">
@@ -11187,7 +11187,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>2213.79</v>
+        <v>2236.31</v>
       </c>
     </row>
     <row r="177">
@@ -11248,7 +11248,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>9904.780000000001</v>
+        <v>10005.5</v>
       </c>
     </row>
     <row r="178">
@@ -11309,7 +11309,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>3143.81</v>
+        <v>3175.78</v>
       </c>
     </row>
     <row r="179">
@@ -11370,7 +11370,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>1568.08</v>
+        <v>1584.02</v>
       </c>
     </row>
     <row r="180">
@@ -11431,7 +11431,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>8133.5</v>
+        <v>8216.209999999999</v>
       </c>
     </row>
     <row r="181">
@@ -11492,7 +11492,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>874.9299999999999</v>
+        <v>883.83</v>
       </c>
     </row>
     <row r="182">
@@ -11553,7 +11553,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>846.35</v>
+        <v>854.95</v>
       </c>
     </row>
     <row r="183">
@@ -11614,7 +11614,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>3785.57</v>
+        <v>3824.06</v>
       </c>
     </row>
     <row r="184">
@@ -11675,7 +11675,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>2886.11</v>
+        <v>2915.46</v>
       </c>
     </row>
     <row r="185">
@@ -11736,7 +11736,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>7920.1</v>
+        <v>8000.64</v>
       </c>
     </row>
     <row r="186">
@@ -11797,7 +11797,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>2766.52</v>
+        <v>2794.66</v>
       </c>
     </row>
     <row r="187">
@@ -11858,7 +11858,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>6531.15</v>
+        <v>6597.57</v>
       </c>
     </row>
     <row r="188">
@@ -11919,7 +11919,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>3643.57</v>
+        <v>3677.74</v>
       </c>
     </row>
     <row r="189">
@@ -11980,7 +11980,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>10748.4</v>
+        <v>10849.22</v>
       </c>
     </row>
     <row r="190">
@@ -12041,7 +12041,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>1096.31</v>
+        <v>1106.59</v>
       </c>
     </row>
     <row r="191">
@@ -12102,7 +12102,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>17049.02</v>
+        <v>17208.92</v>
       </c>
     </row>
     <row r="192">
@@ -12163,7 +12163,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>1590.21</v>
+        <v>1605.13</v>
       </c>
     </row>
     <row r="193">
@@ -12224,7 +12224,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>10753.63</v>
+        <v>10854.49</v>
       </c>
     </row>
     <row r="194">
@@ -12285,7 +12285,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>857.9400000000001</v>
+        <v>865.98</v>
       </c>
     </row>
     <row r="195">
@@ -12346,7 +12346,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>5405.68</v>
+        <v>5456.38</v>
       </c>
     </row>
     <row r="196">
@@ -12407,7 +12407,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>1402.1</v>
+        <v>1415.25</v>
       </c>
     </row>
     <row r="197">
@@ -12468,7 +12468,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>5750.12</v>
+        <v>5804.05</v>
       </c>
     </row>
     <row r="198">
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>5498.32</v>
+        <v>5549.89</v>
       </c>
     </row>
     <row r="199">
@@ -12590,7 +12590,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>803.13</v>
+        <v>810.67</v>
       </c>
     </row>
     <row r="200">
@@ -12651,7 +12651,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>13304.42</v>
+        <v>13429.2</v>
       </c>
     </row>
     <row r="201">
@@ -12712,7 +12712,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>1019.57</v>
+        <v>1029.13</v>
       </c>
     </row>
     <row r="202">
@@ -12773,7 +12773,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>1257.2</v>
+        <v>1268.99</v>
       </c>
     </row>
     <row r="203">
@@ -12834,7 +12834,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>860.24</v>
+        <v>868.3099999999999</v>
       </c>
     </row>
     <row r="204">
@@ -12895,7 +12895,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>791.8099999999999</v>
+        <v>799.24</v>
       </c>
     </row>
     <row r="205">
@@ -12956,7 +12956,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>1510.29</v>
+        <v>1524.46</v>
       </c>
     </row>
     <row r="206">
@@ -13017,7 +13017,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>11934.05</v>
+        <v>12045.98</v>
       </c>
     </row>
     <row r="207">
@@ -13078,7 +13078,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>853.1900000000001</v>
+        <v>861.1900000000001</v>
       </c>
     </row>
     <row r="208">
@@ -13139,7 +13139,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>1460.48</v>
+        <v>1474.18</v>
       </c>
     </row>
     <row r="209">
@@ -13200,7 +13200,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>2679</v>
+        <v>2704.12</v>
       </c>
     </row>
     <row r="210">
@@ -13261,7 +13261,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>8140.3</v>
+        <v>8216.65</v>
       </c>
     </row>
     <row r="211">
@@ -13322,7 +13322,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>1384.91</v>
+        <v>1397.9</v>
       </c>
     </row>
     <row r="212">
@@ -13383,7 +13383,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>17166.73</v>
+        <v>17327.74</v>
       </c>
     </row>
     <row r="213">
@@ -13444,7 +13444,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>4027.46</v>
+        <v>4065.23</v>
       </c>
     </row>
     <row r="214">
@@ -13505,7 +13505,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>3664.66</v>
+        <v>3699.03</v>
       </c>
     </row>
     <row r="215">
@@ -13566,7 +13566,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>920.8099999999999</v>
+        <v>929.45</v>
       </c>
     </row>
     <row r="216">
@@ -13627,7 +13627,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>1637.41</v>
+        <v>1652.77</v>
       </c>
     </row>
     <row r="217">
@@ -13688,7 +13688,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>9371.43</v>
+        <v>9459.32</v>
       </c>
     </row>
     <row r="218">
@@ -13749,7 +13749,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>2673.07</v>
+        <v>2698.14</v>
       </c>
     </row>
     <row r="219">
@@ -13810,7 +13810,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>1298.58</v>
+        <v>1310.76</v>
       </c>
     </row>
     <row r="220">
@@ -13871,7 +13871,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>8400.58</v>
+        <v>8479.370000000001</v>
       </c>
     </row>
     <row r="221">
@@ -13932,7 +13932,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>869.22</v>
+        <v>877.37</v>
       </c>
     </row>
     <row r="222">
@@ -13993,7 +13993,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>10836.17</v>
+        <v>10937.8</v>
       </c>
     </row>
     <row r="223">
@@ -14054,7 +14054,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>2291.08</v>
+        <v>2312.57</v>
       </c>
     </row>
     <row r="224">
@@ -14115,7 +14115,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>7263.49</v>
+        <v>7331.61</v>
       </c>
     </row>
     <row r="225">
@@ -14176,7 +14176,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>7480.3</v>
+        <v>7550.46</v>
       </c>
     </row>
     <row r="226">
@@ -14237,7 +14237,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>2752.25</v>
+        <v>2778.06</v>
       </c>
     </row>
     <row r="227">
@@ -14298,7 +14298,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>2162.93</v>
+        <v>2183.21</v>
       </c>
     </row>
     <row r="228">
@@ -14359,7 +14359,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>5600.95</v>
+        <v>5653.48</v>
       </c>
     </row>
     <row r="229">
@@ -14420,7 +14420,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>3231.19</v>
+        <v>3261.5</v>
       </c>
     </row>
     <row r="230">
@@ -14481,7 +14481,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>4485.77</v>
+        <v>4527.85</v>
       </c>
     </row>
     <row r="231">
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>2431.05</v>
+        <v>2453.85</v>
       </c>
     </row>
     <row r="232">
@@ -14603,7 +14603,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>2121.64</v>
+        <v>2141.54</v>
       </c>
     </row>
     <row r="233">
@@ -14664,7 +14664,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>11003.03</v>
+        <v>11106.23</v>
       </c>
     </row>
     <row r="234">
@@ -14725,7 +14725,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>1714.74</v>
+        <v>1730.82</v>
       </c>
     </row>
     <row r="235">
@@ -14786,7 +14786,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>1220.39</v>
+        <v>1231.84</v>
       </c>
     </row>
     <row r="236">
@@ -14847,7 +14847,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>4088.8</v>
+        <v>4127.15</v>
       </c>
     </row>
     <row r="237">
@@ -14908,7 +14908,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>2169.07</v>
+        <v>2152.62</v>
       </c>
     </row>
     <row r="238">
@@ -14969,7 +14969,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>2657.89</v>
+        <v>2637.72</v>
       </c>
     </row>
     <row r="239">
@@ -15030,7 +15030,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>11983.52</v>
+        <v>11892.61</v>
       </c>
     </row>
     <row r="240">
@@ -15091,7 +15091,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>1660.26</v>
+        <v>1647.67</v>
       </c>
     </row>
     <row r="241">
@@ -15152,7 +15152,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>2210.57</v>
+        <v>2193.8</v>
       </c>
     </row>
     <row r="242">
@@ -15213,7 +15213,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>901.64</v>
+        <v>894.8</v>
       </c>
     </row>
     <row r="243">
@@ -15274,7 +15274,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>1242.55</v>
+        <v>1233.12</v>
       </c>
     </row>
     <row r="244">
@@ -15335,7 +15335,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>2849.52</v>
+        <v>2827.9</v>
       </c>
     </row>
     <row r="245">
@@ -15396,7 +15396,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>2404.55</v>
+        <v>2386.31</v>
       </c>
     </row>
     <row r="246">
@@ -15457,7 +15457,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>3320.64</v>
+        <v>3295.45</v>
       </c>
     </row>
     <row r="247">
@@ -15518,7 +15518,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>5223.02</v>
+        <v>5183.4</v>
       </c>
     </row>
     <row r="248">
@@ -15579,7 +15579,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>2053.95</v>
+        <v>2038.37</v>
       </c>
     </row>
     <row r="249">
@@ -15640,7 +15640,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>3132.79</v>
+        <v>3109.03</v>
       </c>
     </row>
     <row r="250">
@@ -15701,7 +15701,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>1980.82</v>
+        <v>1965.8</v>
       </c>
     </row>
     <row r="251">
@@ -15762,7 +15762,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>5091.25</v>
+        <v>5052.63</v>
       </c>
     </row>
     <row r="252">
@@ -15823,7 +15823,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>1905.56</v>
+        <v>1891.11</v>
       </c>
     </row>
     <row r="253">
@@ -15884,7 +15884,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>8127.92</v>
+        <v>8066.26</v>
       </c>
     </row>
     <row r="254">
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>1109.1</v>
+        <v>1100.69</v>
       </c>
     </row>
     <row r="255">
@@ -16006,7 +16006,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>3154.73</v>
+        <v>3130.79</v>
       </c>
     </row>
     <row r="256">
@@ -16067,7 +16067,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>2869.65</v>
+        <v>2847.88</v>
       </c>
     </row>
     <row r="257">
@@ -16128,7 +16128,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>6800.18</v>
+        <v>6748.59</v>
       </c>
     </row>
     <row r="258">
@@ -16189,7 +16189,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>873.1</v>
+        <v>866.48</v>
       </c>
     </row>
     <row r="259">
@@ -16250,7 +16250,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>2429.79</v>
+        <v>2411.36</v>
       </c>
     </row>
     <row r="260">
@@ -16311,7 +16311,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>2177.48</v>
+        <v>2160.96</v>
       </c>
     </row>
     <row r="261">
@@ -16372,7 +16372,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>1724.26</v>
+        <v>1711.18</v>
       </c>
     </row>
     <row r="262">
@@ -16433,7 +16433,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>5070.96</v>
+        <v>5032.49</v>
       </c>
     </row>
     <row r="263">
@@ -16494,7 +16494,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>1116.8</v>
+        <v>1108.33</v>
       </c>
     </row>
     <row r="264">
@@ -16555,7 +16555,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>3674.26</v>
+        <v>3646.39</v>
       </c>
     </row>
     <row r="265">
@@ -16616,7 +16616,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>4104.74</v>
+        <v>4073.6</v>
       </c>
     </row>
     <row r="266">
@@ -16677,7 +16677,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>2265.59</v>
+        <v>2248.41</v>
       </c>
     </row>
     <row r="267">
@@ -16738,7 +16738,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>35614.15</v>
+        <v>35343.98</v>
       </c>
     </row>
     <row r="268">
@@ -16799,7 +16799,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>1713.33</v>
+        <v>1700.34</v>
       </c>
     </row>
     <row r="269">
@@ -16860,7 +16860,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>819.04</v>
+        <v>812.83</v>
       </c>
     </row>
     <row r="270">
@@ -16921,7 +16921,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>1831.99</v>
+        <v>1818.09</v>
       </c>
     </row>
     <row r="271">
@@ -16982,7 +16982,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>3182.49</v>
+        <v>3158.34</v>
       </c>
     </row>
     <row r="272">
@@ -17043,7 +17043,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>1294.22</v>
+        <v>1284.4</v>
       </c>
     </row>
     <row r="273">
@@ -17104,7 +17104,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>3894.62</v>
+        <v>3865.08</v>
       </c>
     </row>
     <row r="274">
@@ -17165,7 +17165,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>6901</v>
+        <v>6848.65</v>
       </c>
     </row>
     <row r="275">
@@ -17226,7 +17226,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>2024.02</v>
+        <v>2008.66</v>
       </c>
     </row>
     <row r="276">
@@ -17287,7 +17287,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>1660.06</v>
+        <v>1632.01</v>
       </c>
     </row>
     <row r="277">
@@ -17348,7 +17348,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>11835.85</v>
+        <v>11635.88</v>
       </c>
     </row>
     <row r="278">
@@ -17409,7 +17409,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>7584.2</v>
+        <v>7456.06</v>
       </c>
     </row>
     <row r="279">
@@ -17470,7 +17470,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>3537.08</v>
+        <v>3477.32</v>
       </c>
     </row>
     <row r="280">
@@ -17531,7 +17531,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>987.6900000000001</v>
+        <v>971</v>
       </c>
     </row>
     <row r="281">
@@ -17592,7 +17592,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>2702.48</v>
+        <v>2656.82</v>
       </c>
     </row>
     <row r="282">
@@ -17653,7 +17653,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>821.42</v>
+        <v>807.54</v>
       </c>
     </row>
     <row r="283">
@@ -17714,7 +17714,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>3734.33</v>
+        <v>3671.23</v>
       </c>
     </row>
     <row r="284">
@@ -17775,7 +17775,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>1370.52</v>
+        <v>1347.36</v>
       </c>
     </row>
     <row r="285">
@@ -17836,7 +17836,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>911.29</v>
+        <v>895.89</v>
       </c>
     </row>
     <row r="286">
@@ -17897,7 +17897,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>1103.87</v>
+        <v>1085.22</v>
       </c>
     </row>
     <row r="287">
@@ -17958,7 +17958,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>1367.68</v>
+        <v>1344.57</v>
       </c>
     </row>
     <row r="288">
@@ -18019,7 +18019,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>794.85</v>
+        <v>781.42</v>
       </c>
     </row>
     <row r="289">
@@ -18080,7 +18080,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>2433.59</v>
+        <v>2392.47</v>
       </c>
     </row>
     <row r="290">
@@ -18141,7 +18141,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>2462.26</v>
+        <v>2420.66</v>
       </c>
     </row>
     <row r="291">
@@ -18202,7 +18202,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>1953.09</v>
+        <v>1920.09</v>
       </c>
     </row>
     <row r="292">
@@ -18263,7 +18263,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>1964.44</v>
+        <v>1931.25</v>
       </c>
     </row>
     <row r="293">
@@ -18324,7 +18324,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>2566.22</v>
+        <v>2522.86</v>
       </c>
     </row>
     <row r="294">
@@ -18385,7 +18385,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>1806.24</v>
+        <v>1775.72</v>
       </c>
     </row>
     <row r="295">
@@ -18446,7 +18446,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>1015.6</v>
+        <v>998.4400000000001</v>
       </c>
     </row>
     <row r="296">
@@ -18507,7 +18507,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>7867.39</v>
+        <v>7734.46</v>
       </c>
     </row>
     <row r="297">
@@ -18568,7 +18568,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>923.14</v>
+        <v>907.54</v>
       </c>
     </row>
     <row r="298">
@@ -18629,7 +18629,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>3277.91</v>
+        <v>3222.53</v>
       </c>
     </row>
     <row r="299">
@@ -18690,7 +18690,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>2086.56</v>
+        <v>2051.3</v>
       </c>
     </row>
     <row r="300">
@@ -18751,7 +18751,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>74855.12</v>
+        <v>73590.38</v>
       </c>
     </row>
     <row r="301">
@@ -18812,7 +18812,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>25371.65</v>
+        <v>24942.98</v>
       </c>
     </row>
     <row r="302">
@@ -18873,7 +18873,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>1248.65</v>
+        <v>1227.56</v>
       </c>
     </row>
     <row r="303">
@@ -18934,7 +18934,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>3150.13</v>
+        <v>3096.9</v>
       </c>
     </row>
     <row r="304">
@@ -18995,7 +18995,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>8438.950000000001</v>
+        <v>8296.370000000001</v>
       </c>
     </row>
     <row r="305">
@@ -19056,7 +19056,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>2567.03</v>
+        <v>2523.66</v>
       </c>
     </row>
     <row r="306">
@@ -19117,7 +19117,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>5682.38</v>
+        <v>5586.37</v>
       </c>
     </row>
     <row r="307">
@@ -19178,7 +19178,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>10061.73</v>
+        <v>9891.73</v>
       </c>
     </row>
     <row r="308">
@@ -19239,7 +19239,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>797.3200000000001</v>
+        <v>783.85</v>
       </c>
     </row>
     <row r="309">
@@ -19300,7 +19300,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>2378.18</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="310">
@@ -19361,7 +19361,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>3248.07</v>
+        <v>3193.19</v>
       </c>
     </row>
     <row r="311">
@@ -19422,7 +19422,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>3839.26</v>
+        <v>3774.39</v>
       </c>
     </row>
     <row r="312">
@@ -19483,7 +19483,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>2979.66</v>
+        <v>2929.32</v>
       </c>
     </row>
     <row r="313">
@@ -19544,7 +19544,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>1340.79</v>
+        <v>1318.13</v>
       </c>
     </row>
     <row r="314">
@@ -19605,7 +19605,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>5711.16</v>
+        <v>5614.67</v>
       </c>
     </row>
     <row r="315">
@@ -19666,7 +19666,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>1752.63</v>
+        <v>1723.01</v>
       </c>
     </row>
     <row r="316">
@@ -19727,7 +19727,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>1698.17</v>
+        <v>1669.48</v>
       </c>
     </row>
     <row r="317">
@@ -19788,7 +19788,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>12672.72</v>
+        <v>12458.6</v>
       </c>
     </row>
     <row r="318">
@@ -19849,7 +19849,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>1150.15</v>
+        <v>1130.72</v>
       </c>
     </row>
     <row r="319">
@@ -19910,7 +19910,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>2394.79</v>
+        <v>2360.81</v>
       </c>
     </row>
     <row r="320">
@@ -19971,7 +19971,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>8717.16</v>
+        <v>8593.440000000001</v>
       </c>
     </row>
     <row r="321">
@@ -20032,7 +20032,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>3242.94</v>
+        <v>3196.92</v>
       </c>
     </row>
     <row r="322">
@@ -20093,7 +20093,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>3722.49</v>
+        <v>3669.66</v>
       </c>
     </row>
     <row r="323">
@@ -20154,7 +20154,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>1111.91</v>
+        <v>1096.13</v>
       </c>
     </row>
     <row r="324">
@@ -20215,7 +20215,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>8302.84</v>
+        <v>8185</v>
       </c>
     </row>
     <row r="325">
@@ -20276,7 +20276,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>2383.06</v>
+        <v>2349.24</v>
       </c>
     </row>
     <row r="326">
@@ -20337,7 +20337,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>1066.99</v>
+        <v>1051.84</v>
       </c>
     </row>
     <row r="327">
@@ -20398,7 +20398,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>2189.96</v>
+        <v>2158.88</v>
       </c>
     </row>
     <row r="328">
@@ -20459,7 +20459,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>3320.69</v>
+        <v>3273.56</v>
       </c>
     </row>
     <row r="329">
@@ -20520,7 +20520,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>1181.33</v>
+        <v>1164.56</v>
       </c>
     </row>
     <row r="330">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>2404.44</v>
+        <v>2370.31</v>
       </c>
     </row>
     <row r="331">
@@ -20642,7 +20642,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>1644.86</v>
+        <v>1621.51</v>
       </c>
     </row>
     <row r="332">
@@ -20703,7 +20703,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>1794.12</v>
+        <v>1768.66</v>
       </c>
     </row>
     <row r="333">
@@ -20764,7 +20764,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>5467.72</v>
+        <v>5390.12</v>
       </c>
     </row>
     <row r="334">
@@ -20825,7 +20825,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>1702.21</v>
+        <v>1678.05</v>
       </c>
     </row>
     <row r="335">
@@ -20886,7 +20886,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>15162.87</v>
+        <v>14947.67</v>
       </c>
     </row>
     <row r="336">
@@ -20947,7 +20947,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>2284.06</v>
+        <v>2251.64</v>
       </c>
     </row>
     <row r="337">
@@ -21008,7 +21008,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>2287.83</v>
+        <v>2255.36</v>
       </c>
     </row>
     <row r="338">
@@ -21069,7 +21069,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>7182.91</v>
+        <v>7080.97</v>
       </c>
     </row>
     <row r="339">
@@ -21130,7 +21130,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>5375.12</v>
+        <v>5298.83</v>
       </c>
     </row>
     <row r="340">
@@ -21191,7 +21191,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>1761.48</v>
+        <v>1736.48</v>
       </c>
     </row>
     <row r="341">
@@ -21252,7 +21252,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>3457.76</v>
+        <v>3408.69</v>
       </c>
     </row>
     <row r="342">
@@ -21313,7 +21313,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>5503.75</v>
+        <v>5425.64</v>
       </c>
     </row>
     <row r="343">
@@ -21374,7 +21374,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>5075.19</v>
+        <v>5003.16</v>
       </c>
     </row>
     <row r="344">
@@ -21435,7 +21435,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>1533.26</v>
+        <v>1511.5</v>
       </c>
     </row>
     <row r="345">
@@ -21496,7 +21496,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>3971.96</v>
+        <v>3915.59</v>
       </c>
     </row>
     <row r="346">
@@ -21557,7 +21557,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>55493.92</v>
+        <v>54706.33</v>
       </c>
     </row>
     <row r="347">
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>3685.97</v>
+        <v>3633.66</v>
       </c>
     </row>
     <row r="348">
@@ -21679,7 +21679,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>843.63</v>
+        <v>831.65</v>
       </c>
     </row>
     <row r="349">
@@ -21740,7 +21740,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>1246.66</v>
+        <v>1228.97</v>
       </c>
     </row>
     <row r="350">
@@ -21801,7 +21801,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>2436.5</v>
+        <v>2401.93</v>
       </c>
     </row>
     <row r="351">
@@ -21862,7 +21862,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>1659.37</v>
+        <v>1635.82</v>
       </c>
     </row>
     <row r="352">
@@ -21923,7 +21923,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>3162.25</v>
+        <v>3117.37</v>
       </c>
     </row>
     <row r="353">
@@ -21984,7 +21984,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>969.96</v>
+        <v>956.2</v>
       </c>
     </row>
     <row r="354">
@@ -22045,7 +22045,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>1633.77</v>
+        <v>1610.58</v>
       </c>
     </row>
     <row r="355">
@@ -22106,7 +22106,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>13444.05</v>
+        <v>13253.24</v>
       </c>
     </row>
     <row r="356">
@@ -22167,7 +22167,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>19090.12</v>
+        <v>18819.19</v>
       </c>
     </row>
     <row r="357">
@@ -22228,7 +22228,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>3458.09</v>
+        <v>3409.02</v>
       </c>
     </row>
     <row r="358">
@@ -22289,7 +22289,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>2641.39</v>
+        <v>2603.9</v>
       </c>
     </row>
     <row r="359">
@@ -22350,7 +22350,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>5860.23</v>
+        <v>5777.06</v>
       </c>
     </row>
     <row r="360">
@@ -22411,7 +22411,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>3554.65</v>
+        <v>3504.2</v>
       </c>
     </row>
     <row r="361">
@@ -22472,7 +22472,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>3043.98</v>
+        <v>3000.78</v>
       </c>
     </row>
     <row r="362">
@@ -22533,7 +22533,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>23480.86</v>
+        <v>23147.61</v>
       </c>
     </row>
     <row r="363">
@@ -22594,7 +22594,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>1757.4</v>
+        <v>1732.46</v>
       </c>
     </row>
     <row r="364">
@@ -22655,7 +22655,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>879.66</v>
+        <v>867.17</v>
       </c>
     </row>
     <row r="365">
@@ -22716,7 +22716,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>6213.18</v>
+        <v>6125</v>
       </c>
     </row>
     <row r="366">
@@ -22777,7 +22777,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>7190.18</v>
+        <v>7088.13</v>
       </c>
     </row>
     <row r="367">
@@ -22838,7 +22838,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>893.58</v>
+        <v>880.9</v>
       </c>
     </row>
     <row r="368">
@@ -22899,7 +22899,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>4868.51</v>
+        <v>4799.41</v>
       </c>
     </row>
     <row r="369">
@@ -22960,7 +22960,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>793.0599999999999</v>
+        <v>781.8</v>
       </c>
     </row>
     <row r="370">
@@ -23021,7 +23021,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>1230.45</v>
+        <v>1212.99</v>
       </c>
     </row>
     <row r="371">
@@ -23082,7 +23082,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>2324.84</v>
+        <v>2291.85</v>
       </c>
     </row>
     <row r="372">
@@ -23143,7 +23143,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>2425.18</v>
+        <v>2390.77</v>
       </c>
     </row>
     <row r="373">
@@ -23204,7 +23204,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>2089.58</v>
+        <v>2059.93</v>
       </c>
     </row>
     <row r="374">
@@ -23265,7 +23265,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>2473.52</v>
+        <v>2438.42</v>
       </c>
     </row>
     <row r="375">
@@ -23326,7 +23326,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>4261.21</v>
+        <v>4200.73</v>
       </c>
     </row>
     <row r="376">
@@ -23387,7 +23387,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>1327.59</v>
+        <v>1308.75</v>
       </c>
     </row>
     <row r="377">
@@ -23448,7 +23448,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>3871.96</v>
+        <v>3817.01</v>
       </c>
     </row>
     <row r="378">
@@ -23509,7 +23509,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>3250.84</v>
+        <v>3204.7</v>
       </c>
     </row>
     <row r="379">
@@ -23570,7 +23570,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>1361</v>
+        <v>1341.69</v>
       </c>
     </row>
     <row r="380">
@@ -23631,7 +23631,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>6585.92</v>
+        <v>6495.43</v>
       </c>
     </row>
     <row r="381">
@@ -23692,7 +23692,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>2660.7</v>
+        <v>2624.14</v>
       </c>
     </row>
     <row r="382">
@@ -23753,7 +23753,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>842.9400000000001</v>
+        <v>831.35</v>
       </c>
     </row>
     <row r="383">
@@ -23814,7 +23814,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>1336.01</v>
+        <v>1317.65</v>
       </c>
     </row>
     <row r="384">
@@ -23875,7 +23875,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>1293.95</v>
+        <v>1276.17</v>
       </c>
     </row>
     <row r="385">
@@ -23936,7 +23936,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>5142.29</v>
+        <v>5071.63</v>
       </c>
     </row>
     <row r="386">
@@ -23997,7 +23997,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>5542.72</v>
+        <v>5466.56</v>
       </c>
     </row>
     <row r="387">
@@ -24058,7 +24058,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>793.02</v>
+        <v>782.13</v>
       </c>
     </row>
     <row r="388">
@@ -24119,7 +24119,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>10974.69</v>
+        <v>10823.9</v>
       </c>
     </row>
     <row r="389">
@@ -24180,7 +24180,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>2348.79</v>
+        <v>2316.52</v>
       </c>
     </row>
     <row r="390">
@@ -24241,7 +24241,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>1186.36</v>
+        <v>1170.06</v>
       </c>
     </row>
     <row r="391">
@@ -24302,7 +24302,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>2490.73</v>
+        <v>2456.51</v>
       </c>
     </row>
     <row r="392">
@@ -24363,7 +24363,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>4206.51</v>
+        <v>4148.71</v>
       </c>
     </row>
     <row r="393">
@@ -24424,7 +24424,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>3133.59</v>
+        <v>3090.53</v>
       </c>
     </row>
     <row r="394">
@@ -24485,7 +24485,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>2272.29</v>
+        <v>2241.07</v>
       </c>
     </row>
     <row r="395">
@@ -24546,7 +24546,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>4108.3</v>
+        <v>4051.85</v>
       </c>
     </row>
     <row r="396">
@@ -24607,7 +24607,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>842.54</v>
+        <v>830.96</v>
       </c>
     </row>
     <row r="397">
@@ -24668,7 +24668,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>1719.44</v>
+        <v>1695.81</v>
       </c>
     </row>
     <row r="398">
@@ -24729,7 +24729,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>4427.73</v>
+        <v>4366.89</v>
       </c>
     </row>
     <row r="399">
@@ -24790,7 +24790,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>8852.809999999999</v>
+        <v>8731.17</v>
       </c>
     </row>
     <row r="400">
@@ -24851,7 +24851,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>2197.06</v>
+        <v>2166.87</v>
       </c>
     </row>
     <row r="401">
@@ -24912,7 +24912,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>1494.97</v>
+        <v>1474.43</v>
       </c>
     </row>
     <row r="402">
@@ -24973,7 +24973,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>6649.81</v>
+        <v>6558.43</v>
       </c>
     </row>
     <row r="403">
@@ -25034,7 +25034,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>2207.71</v>
+        <v>2177.38</v>
       </c>
     </row>
     <row r="404">
@@ -25095,7 +25095,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>3157.02</v>
+        <v>3113.64</v>
       </c>
     </row>
     <row r="405">
@@ -25156,7 +25156,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>2702.21</v>
+        <v>2665.08</v>
       </c>
     </row>
     <row r="406">
@@ -25217,7 +25217,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>2379.03</v>
+        <v>2346.34</v>
       </c>
     </row>
     <row r="407">
@@ -25278,7 +25278,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>2841.35</v>
+        <v>2802.31</v>
       </c>
     </row>
     <row r="408">
@@ -25339,7 +25339,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>2671.13</v>
+        <v>2634.42</v>
       </c>
     </row>
     <row r="409">
@@ -25400,7 +25400,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>7568.72</v>
+        <v>7464.72</v>
       </c>
     </row>
     <row r="410">
@@ -25461,7 +25461,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>1792.03</v>
+        <v>1767.4</v>
       </c>
     </row>
     <row r="411">
@@ -25522,7 +25522,7 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>6940.43</v>
+        <v>6845.07</v>
       </c>
     </row>
     <row r="412">
@@ -25583,7 +25583,7 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>1152.7</v>
+        <v>1136.86</v>
       </c>
     </row>
     <row r="413">
@@ -25644,7 +25644,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>1247.2</v>
+        <v>1230.06</v>
       </c>
     </row>
     <row r="414">
@@ -25705,7 +25705,7 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>1012.63</v>
+        <v>998.71</v>
       </c>
     </row>
     <row r="415">
@@ -25766,7 +25766,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>1283.64</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="416">
@@ -25827,7 +25827,7 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>1294.76</v>
+        <v>1276.97</v>
       </c>
     </row>
     <row r="417">
@@ -25888,7 +25888,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>3206.29</v>
+        <v>3162.23</v>
       </c>
     </row>
     <row r="418">
@@ -25949,7 +25949,7 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>823.08</v>
+        <v>811.77</v>
       </c>
     </row>
     <row r="419">
@@ -26010,7 +26010,7 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>3105.2</v>
+        <v>3062.53</v>
       </c>
     </row>
     <row r="420">
@@ -26071,7 +26071,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>28456.63</v>
+        <v>28065.63</v>
       </c>
     </row>
     <row r="421">
@@ -26132,7 +26132,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>1925.85</v>
+        <v>1899.39</v>
       </c>
     </row>
     <row r="422">
@@ -26193,7 +26193,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>28766.78</v>
+        <v>28371.52</v>
       </c>
     </row>
     <row r="423">
@@ -26254,7 +26254,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>2283.39</v>
+        <v>2252.01</v>
       </c>
     </row>
     <row r="424">
@@ -26315,7 +26315,7 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>6755.22</v>
+        <v>6662.4</v>
       </c>
     </row>
     <row r="425">
@@ -26376,7 +26376,7 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>874.83</v>
+        <v>862.8099999999999</v>
       </c>
     </row>
     <row r="426">
@@ -26437,7 +26437,7 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>1740.08</v>
+        <v>1716.17</v>
       </c>
     </row>
     <row r="427">
@@ -26498,7 +26498,7 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>1214.83</v>
+        <v>1198.14</v>
       </c>
     </row>
     <row r="428">
@@ -26559,7 +26559,7 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>836.73</v>
+        <v>825.23</v>
       </c>
     </row>
     <row r="429">
@@ -26620,7 +26620,7 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>11727.96</v>
+        <v>11566.82</v>
       </c>
     </row>
     <row r="430">
@@ -26681,7 +26681,7 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>826.65</v>
+        <v>821.53</v>
       </c>
     </row>
     <row r="431">
@@ -26742,7 +26742,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>7409.64</v>
+        <v>7363.7</v>
       </c>
     </row>
     <row r="432">
@@ -26803,7 +26803,7 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>7858.36</v>
+        <v>7809.65</v>
       </c>
     </row>
     <row r="433">
@@ -26864,7 +26864,7 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>3369.18</v>
+        <v>3348.29</v>
       </c>
     </row>
     <row r="434">
@@ -26925,7 +26925,7 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>2314.18</v>
+        <v>2299.83</v>
       </c>
     </row>
     <row r="435">
@@ -26986,7 +26986,7 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>2216.15</v>
+        <v>2202.41</v>
       </c>
     </row>
     <row r="436">
@@ -27047,7 +27047,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>1062.02</v>
+        <v>1055.43</v>
       </c>
     </row>
     <row r="437">
@@ -27108,7 +27108,7 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>1914.62</v>
+        <v>1902.75</v>
       </c>
     </row>
     <row r="438">
@@ -27169,7 +27169,7 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>2284.59</v>
+        <v>2270.43</v>
       </c>
     </row>
     <row r="439">
@@ -27230,7 +27230,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>1969.49</v>
+        <v>1957.28</v>
       </c>
     </row>
     <row r="440">
@@ -27291,7 +27291,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>9168.190000000001</v>
+        <v>9111.35</v>
       </c>
     </row>
     <row r="441">
@@ -27352,7 +27352,7 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>8287</v>
+        <v>8235.620000000001</v>
       </c>
     </row>
     <row r="442">
@@ -27413,7 +27413,7 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>2373.05</v>
+        <v>2358.34</v>
       </c>
     </row>
     <row r="443">
@@ -27474,7 +27474,7 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>7050.21</v>
+        <v>7006.5</v>
       </c>
     </row>
     <row r="444">
@@ -27535,7 +27535,7 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>62894.58</v>
+        <v>62504.65</v>
       </c>
     </row>
     <row r="445">
@@ -27596,7 +27596,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>2209.87</v>
+        <v>2196.17</v>
       </c>
     </row>
     <row r="446">
@@ -27657,7 +27657,7 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>1363.37</v>
+        <v>1354.92</v>
       </c>
     </row>
     <row r="447">
@@ -27718,7 +27718,7 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>1796.75</v>
+        <v>1785.62</v>
       </c>
     </row>
     <row r="448">
@@ -27779,7 +27779,7 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>1651.23</v>
+        <v>1640.99</v>
       </c>
     </row>
     <row r="449">
@@ -27840,7 +27840,7 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>2146.04</v>
+        <v>2132.74</v>
       </c>
     </row>
     <row r="450">
@@ -27901,7 +27901,7 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>19663.69</v>
+        <v>19541.78</v>
       </c>
     </row>
     <row r="451">
@@ -27962,7 +27962,7 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>4742.6</v>
+        <v>4713.2</v>
       </c>
     </row>
     <row r="452">
@@ -28023,7 +28023,7 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>1935.04</v>
+        <v>1923.04</v>
       </c>
     </row>
     <row r="453">
@@ -28084,7 +28084,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>808.3</v>
+        <v>803.29</v>
       </c>
     </row>
     <row r="454">
@@ -28145,7 +28145,7 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>11962.99</v>
+        <v>11888.82</v>
       </c>
     </row>
     <row r="455">
@@ -28206,7 +28206,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>1151.45</v>
+        <v>1144.31</v>
       </c>
     </row>
     <row r="456">
@@ -28267,7 +28267,7 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>9020.66</v>
+        <v>8964.73</v>
       </c>
     </row>
     <row r="457">
@@ -28328,7 +28328,7 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>1794.87</v>
+        <v>1783.74</v>
       </c>
     </row>
     <row r="458">
@@ -28389,7 +28389,7 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>16973.01</v>
+        <v>16867.78</v>
       </c>
     </row>
     <row r="459">
@@ -28450,7 +28450,7 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>1450.2</v>
+        <v>1441.21</v>
       </c>
     </row>
     <row r="460">
@@ -28511,7 +28511,7 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>3066.6</v>
+        <v>3047.59</v>
       </c>
     </row>
     <row r="461">
@@ -28572,7 +28572,7 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>16522.77</v>
+        <v>16420.33</v>
       </c>
     </row>
     <row r="462">
@@ -28633,7 +28633,7 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>1171.48</v>
+        <v>1164.21</v>
       </c>
     </row>
     <row r="463">
@@ -28694,7 +28694,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>820.04</v>
+        <v>814.96</v>
       </c>
     </row>
     <row r="464">
@@ -28755,7 +28755,7 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>1733.23</v>
+        <v>1722.48</v>
       </c>
     </row>
     <row r="465">
@@ -28816,7 +28816,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>922.14</v>
+        <v>916.42</v>
       </c>
     </row>
     <row r="466">
@@ -28877,7 +28877,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>2995.22</v>
+        <v>2976.65</v>
       </c>
     </row>
     <row r="467">
@@ -28938,7 +28938,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>1781.99</v>
+        <v>1770.94</v>
       </c>
     </row>
     <row r="468">
@@ -28999,7 +28999,7 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>2650.87</v>
+        <v>2634.44</v>
       </c>
     </row>
     <row r="469">
@@ -29060,7 +29060,7 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>2371.08</v>
+        <v>2356.38</v>
       </c>
     </row>
     <row r="470">
@@ -29121,7 +29121,7 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>3762.12</v>
+        <v>3738.8</v>
       </c>
     </row>
     <row r="471">
@@ -29182,7 +29182,7 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>5315.16</v>
+        <v>5282.21</v>
       </c>
     </row>
     <row r="472">
@@ -29243,7 +29243,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>4939.76</v>
+        <v>4909.13</v>
       </c>
     </row>
     <row r="473">
@@ -29304,7 +29304,7 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>42751.32</v>
+        <v>42486.27</v>
       </c>
     </row>
     <row r="474">
@@ -29365,7 +29365,7 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>1621.74</v>
+        <v>1611.68</v>
       </c>
     </row>
     <row r="475">
@@ -29426,7 +29426,7 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>7570.29</v>
+        <v>7523.36</v>
       </c>
     </row>
     <row r="476">
@@ -29487,7 +29487,7 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>4727.55</v>
+        <v>4698.24</v>
       </c>
     </row>
     <row r="477">
@@ -29548,7 +29548,7 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>955.5</v>
+        <v>949.58</v>
       </c>
     </row>
     <row r="478">
@@ -29609,7 +29609,7 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>7184.57</v>
+        <v>7140.03</v>
       </c>
     </row>
     <row r="479">
@@ -29670,7 +29670,7 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>8837.780000000001</v>
+        <v>8877.92</v>
       </c>
     </row>
     <row r="480">
@@ -29731,7 +29731,7 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>2610.3</v>
+        <v>2622.16</v>
       </c>
     </row>
     <row r="481">
@@ -29792,7 +29792,7 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>12233.43</v>
+        <v>12288.99</v>
       </c>
     </row>
     <row r="482">
@@ -29853,7 +29853,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>4062.46</v>
+        <v>4080.91</v>
       </c>
     </row>
     <row r="483">
@@ -29914,7 +29914,7 @@
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>2212.55</v>
+        <v>2222.6</v>
       </c>
     </row>
     <row r="484">
@@ -29975,7 +29975,7 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>3880.11</v>
+        <v>3897.74</v>
       </c>
     </row>
     <row r="485">
@@ -30036,7 +30036,7 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>30898.74</v>
+        <v>31039.07</v>
       </c>
     </row>
     <row r="486">
@@ -30097,7 +30097,7 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>2052.22</v>
+        <v>2061.54</v>
       </c>
     </row>
     <row r="487">
@@ -30158,7 +30158,7 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>1212.22</v>
+        <v>1217.73</v>
       </c>
     </row>
     <row r="488">
@@ -30219,7 +30219,7 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>2088.69</v>
+        <v>2098.17</v>
       </c>
     </row>
     <row r="489">
@@ -30280,7 +30280,7 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>3865.59</v>
+        <v>3883.15</v>
       </c>
     </row>
     <row r="490">
@@ -30341,7 +30341,7 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>1561.01</v>
+        <v>1568.1</v>
       </c>
     </row>
     <row r="491">
@@ -30402,7 +30402,7 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>9492.370000000001</v>
+        <v>9535.48</v>
       </c>
     </row>
     <row r="492">
@@ -30463,7 +30463,7 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>1195.77</v>
+        <v>1201.2</v>
       </c>
     </row>
     <row r="493">
@@ -30524,7 +30524,7 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>2426.54</v>
+        <v>2437.56</v>
       </c>
     </row>
     <row r="494">
@@ -30585,7 +30585,7 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>13353.48</v>
+        <v>13414.13</v>
       </c>
     </row>
     <row r="495">
@@ -30646,7 +30646,7 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>14384.58</v>
+        <v>14449.91</v>
       </c>
     </row>
     <row r="496">
@@ -30707,7 +30707,7 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>7380.88</v>
+        <v>7414.4</v>
       </c>
     </row>
     <row r="497">
@@ -30768,7 +30768,7 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>918.26</v>
+        <v>922.4299999999999</v>
       </c>
     </row>
     <row r="498">
@@ -30829,7 +30829,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>2212.64</v>
+        <v>2222.69</v>
       </c>
     </row>
     <row r="499">
@@ -30890,7 +30890,7 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>4583.4</v>
+        <v>4604.22</v>
       </c>
     </row>
     <row r="500">
@@ -30951,7 +30951,7 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>998.4400000000001</v>
+        <v>1002.97</v>
       </c>
     </row>
     <row r="501">
@@ -31012,7 +31012,7 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>8358.889999999999</v>
+        <v>8396.85</v>
       </c>
     </row>
     <row r="502">
@@ -31073,7 +31073,7 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>42860.35</v>
+        <v>43055.01</v>
       </c>
     </row>
     <row r="503">
@@ -31134,7 +31134,7 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>3159.86</v>
+        <v>3174.22</v>
       </c>
     </row>
     <row r="504">
@@ -31195,7 +31195,7 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>1192.91</v>
+        <v>1198.32</v>
       </c>
     </row>
     <row r="505">
@@ -31256,7 +31256,7 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>61179.01</v>
+        <v>61456.86</v>
       </c>
     </row>
     <row r="506">
@@ -31317,7 +31317,7 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>3412.5</v>
+        <v>3428</v>
       </c>
     </row>
     <row r="507">
@@ -31378,7 +31378,7 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>5595.76</v>
+        <v>5621.17</v>
       </c>
     </row>
     <row r="508">
@@ -31439,7 +31439,7 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>3167.77</v>
+        <v>3182.16</v>
       </c>
     </row>
     <row r="509">
@@ -31500,7 +31500,7 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>16969.69</v>
+        <v>17046.76</v>
       </c>
     </row>
     <row r="510">
@@ -31561,7 +31561,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>6255.16</v>
+        <v>6283.56</v>
       </c>
     </row>
     <row r="511">
@@ -31622,7 +31622,7 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>4414.8</v>
+        <v>4480.54</v>
       </c>
     </row>
     <row r="512">
@@ -31683,7 +31683,7 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>24340.36</v>
+        <v>24702.8</v>
       </c>
     </row>
     <row r="513">
@@ -31744,7 +31744,7 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>2205.53</v>
+        <v>2238.38</v>
       </c>
     </row>
     <row r="514">
@@ -31805,7 +31805,7 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>895.08</v>
+        <v>908.41</v>
       </c>
     </row>
     <row r="515">
@@ -31866,7 +31866,7 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>1315.89</v>
+        <v>1335.49</v>
       </c>
     </row>
     <row r="516">
@@ -31927,7 +31927,7 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>2169.74</v>
+        <v>2202.04</v>
       </c>
     </row>
     <row r="517">
@@ -31988,7 +31988,7 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>2145.17</v>
+        <v>2177.11</v>
       </c>
     </row>
     <row r="518">
@@ -32049,7 +32049,7 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>3565.72</v>
+        <v>3618.81</v>
       </c>
     </row>
     <row r="519">
@@ -32110,7 +32110,7 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>2239.36</v>
+        <v>2272.7</v>
       </c>
     </row>
     <row r="520">
@@ -32171,7 +32171,7 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>822.35</v>
+        <v>834.6</v>
       </c>
     </row>
     <row r="521">
@@ -32232,7 +32232,7 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>3410.87</v>
+        <v>3461.66</v>
       </c>
     </row>
     <row r="522">
@@ -32293,7 +32293,7 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>839.45</v>
+        <v>851.95</v>
       </c>
     </row>
     <row r="523">
@@ -32354,7 +32354,7 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>1172.96</v>
+        <v>1190.43</v>
       </c>
     </row>
     <row r="524">
@@ -32415,7 +32415,7 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>1508.09</v>
+        <v>1530.55</v>
       </c>
     </row>
     <row r="525">
@@ -32476,7 +32476,7 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>3656.54</v>
+        <v>3710.99</v>
       </c>
     </row>
     <row r="526">
@@ -32537,7 +32537,7 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>1184.7</v>
+        <v>1202.34</v>
       </c>
     </row>
     <row r="527">
@@ -32598,7 +32598,7 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>2539.04</v>
+        <v>2576.84</v>
       </c>
     </row>
     <row r="528">
@@ -32659,7 +32659,7 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>7264.74</v>
+        <v>7372.91</v>
       </c>
     </row>
     <row r="529">
@@ -32720,7 +32720,7 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>854.47</v>
+        <v>867.2</v>
       </c>
     </row>
     <row r="530">
@@ -32781,7 +32781,7 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>3219.98</v>
+        <v>3267.92</v>
       </c>
     </row>
     <row r="531">
@@ -32842,7 +32842,7 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>2527.48</v>
+        <v>2565.12</v>
       </c>
     </row>
     <row r="532">
@@ -32903,7 +32903,7 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>4607.78</v>
+        <v>4676.4</v>
       </c>
     </row>
     <row r="533">
@@ -32964,7 +32964,7 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>6288.2</v>
+        <v>6381.83</v>
       </c>
     </row>
     <row r="534">
@@ -33025,7 +33025,7 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>3473.81</v>
+        <v>3525.54</v>
       </c>
     </row>
     <row r="535">
@@ -33086,7 +33086,7 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>4607.81</v>
+        <v>4676.42</v>
       </c>
     </row>
     <row r="536">
@@ -33147,7 +33147,7 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>1444.89</v>
+        <v>1466.4</v>
       </c>
     </row>
     <row r="537">
@@ -33208,7 +33208,7 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>1371.21</v>
+        <v>1391.63</v>
       </c>
     </row>
     <row r="538">
@@ -33269,7 +33269,7 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>5248.39</v>
+        <v>5326.54</v>
       </c>
     </row>
     <row r="539">
@@ -33330,7 +33330,7 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>1163.5</v>
+        <v>1180.83</v>
       </c>
     </row>
     <row r="540">
@@ -33391,7 +33391,7 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>2102.1</v>
+        <v>2133.4</v>
       </c>
     </row>
     <row r="541">
@@ -33452,7 +33452,7 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>1005.26</v>
+        <v>1020.23</v>
       </c>
     </row>
     <row r="542">
@@ -33513,7 +33513,7 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>9043.280000000001</v>
+        <v>9177.940000000001</v>
       </c>
     </row>
     <row r="543">
@@ -33574,7 +33574,7 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>1871.38</v>
+        <v>1899.24</v>
       </c>
     </row>
     <row r="544">
@@ -33635,7 +33635,7 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>955.5700000000001</v>
+        <v>973.74</v>
       </c>
     </row>
     <row r="545">
@@ -33696,7 +33696,7 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>4816.45</v>
+        <v>4908.02</v>
       </c>
     </row>
     <row r="546">
@@ -33757,7 +33757,7 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>893.78</v>
+        <v>910.77</v>
       </c>
     </row>
     <row r="547">
@@ -33818,7 +33818,7 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>3933.81</v>
+        <v>4008.6</v>
       </c>
     </row>
     <row r="548">
@@ -33879,7 +33879,7 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>835.8200000000001</v>
+        <v>851.71</v>
       </c>
     </row>
     <row r="549">
@@ -33940,7 +33940,7 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>966.48</v>
+        <v>984.85</v>
       </c>
     </row>
     <row r="550">
@@ -34001,7 +34001,7 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>2528.62</v>
+        <v>2576.69</v>
       </c>
     </row>
     <row r="551">
@@ -34062,7 +34062,7 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>798.09</v>
+        <v>813.26</v>
       </c>
     </row>
     <row r="552">
@@ -34123,7 +34123,7 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>5822.33</v>
+        <v>5933.02</v>
       </c>
     </row>
     <row r="553">
@@ -34184,7 +34184,7 @@
         </is>
       </c>
       <c r="M553" s="2" t="n">
-        <v>981.23</v>
+        <v>999.89</v>
       </c>
     </row>
     <row r="554">
@@ -34245,7 +34245,7 @@
         </is>
       </c>
       <c r="M554" s="2" t="n">
-        <v>2535.34</v>
+        <v>2583.55</v>
       </c>
     </row>
     <row r="555">
@@ -34306,7 +34306,7 @@
         </is>
       </c>
       <c r="M555" s="2" t="n">
-        <v>4536.57</v>
+        <v>4622.81</v>
       </c>
     </row>
     <row r="556">
@@ -34367,7 +34367,7 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>8574.559999999999</v>
+        <v>8737.57</v>
       </c>
     </row>
     <row r="557">
@@ -34428,7 +34428,7 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>1718.73</v>
+        <v>1751.4</v>
       </c>
     </row>
     <row r="558">
@@ -34489,7 +34489,7 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>807.98</v>
+        <v>823.34</v>
       </c>
     </row>
     <row r="559">
@@ -34550,7 +34550,7 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>2322.4</v>
+        <v>2366.55</v>
       </c>
     </row>
     <row r="560">
@@ -34611,7 +34611,7 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>1631.66</v>
+        <v>1662.68</v>
       </c>
     </row>
     <row r="561">
@@ -34672,7 +34672,7 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>1015.16</v>
+        <v>1034.46</v>
       </c>
     </row>
     <row r="562">
@@ -34733,7 +34733,7 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>4639.38</v>
+        <v>4727.58</v>
       </c>
     </row>
     <row r="563">
@@ -34794,7 +34794,7 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>16262.44</v>
+        <v>16571.61</v>
       </c>
     </row>
     <row r="564">
@@ -34855,7 +34855,7 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>4363.18</v>
+        <v>4446.13</v>
       </c>
     </row>
     <row r="565">
@@ -34916,7 +34916,7 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>5545.11</v>
+        <v>5650.53</v>
       </c>
     </row>
     <row r="566">
@@ -34977,7 +34977,7 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>5757.37</v>
+        <v>5866.83</v>
       </c>
     </row>
     <row r="567">
@@ -35038,7 +35038,7 @@
         </is>
       </c>
       <c r="M567" s="2" t="n">
-        <v>854.97</v>
+        <v>871.23</v>
       </c>
     </row>
     <row r="568">
@@ -35099,7 +35099,7 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>2728.59</v>
+        <v>2780.47</v>
       </c>
     </row>
     <row r="569">
@@ -35160,7 +35160,7 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>5043.83</v>
+        <v>5139.73</v>
       </c>
     </row>
     <row r="570">
@@ -35221,7 +35221,7 @@
         </is>
       </c>
       <c r="M570" s="2" t="n">
-        <v>1508.94</v>
+        <v>1537.63</v>
       </c>
     </row>
     <row r="571">
@@ -35282,7 +35282,7 @@
         </is>
       </c>
       <c r="M571" s="2" t="n">
-        <v>3159.42</v>
+        <v>3219.49</v>
       </c>
     </row>
     <row r="572">
@@ -35343,7 +35343,7 @@
         </is>
       </c>
       <c r="M572" s="2" t="n">
-        <v>5008.61</v>
+        <v>5103.83</v>
       </c>
     </row>
     <row r="573">
@@ -35404,7 +35404,7 @@
         </is>
       </c>
       <c r="M573" s="2" t="n">
-        <v>13495.95</v>
+        <v>13752.53</v>
       </c>
     </row>
     <row r="574">
@@ -35465,7 +35465,7 @@
         </is>
       </c>
       <c r="M574" s="2" t="n">
-        <v>14261.17</v>
+        <v>14532.3</v>
       </c>
     </row>
     <row r="575">
@@ -35526,7 +35526,7 @@
         </is>
       </c>
       <c r="M575" s="2" t="n">
-        <v>1890.35</v>
+        <v>1926.29</v>
       </c>
     </row>
     <row r="576">
@@ -35587,7 +35587,7 @@
         </is>
       </c>
       <c r="M576" s="2" t="n">
-        <v>3590.76</v>
+        <v>3659.03</v>
       </c>
     </row>
     <row r="577">
@@ -35648,7 +35648,7 @@
         </is>
       </c>
       <c r="M577" s="2" t="n">
-        <v>68619.17</v>
+        <v>69923.73</v>
       </c>
     </row>
     <row r="578">
@@ -35709,7 +35709,7 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>14757.49</v>
+        <v>15038.06</v>
       </c>
     </row>
     <row r="579">
@@ -35770,7 +35770,7 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>831.6</v>
+        <v>847.41</v>
       </c>
     </row>
     <row r="580">
@@ -35831,7 +35831,7 @@
         </is>
       </c>
       <c r="M580" s="2" t="n">
-        <v>791.99</v>
+        <v>807.05</v>
       </c>
     </row>
     <row r="581">
@@ -35892,7 +35892,7 @@
         </is>
       </c>
       <c r="M581" s="2" t="n">
-        <v>2913.78</v>
+        <v>2969.17</v>
       </c>
     </row>
     <row r="582">
@@ -35953,7 +35953,7 @@
         </is>
       </c>
       <c r="M582" s="2" t="n">
-        <v>70180.59</v>
+        <v>71514.83</v>
       </c>
     </row>
     <row r="583">
@@ -36014,7 +36014,7 @@
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>1103.49</v>
+        <v>1124.47</v>
       </c>
     </row>
     <row r="584">
@@ -36075,7 +36075,7 @@
         </is>
       </c>
       <c r="M584" s="2" t="n">
-        <v>2546.5</v>
+        <v>2594.91</v>
       </c>
     </row>
     <row r="585">
@@ -36136,7 +36136,7 @@
         </is>
       </c>
       <c r="M585" s="2" t="n">
-        <v>804.51</v>
+        <v>819.8</v>
       </c>
     </row>
     <row r="586">
@@ -36197,7 +36197,7 @@
         </is>
       </c>
       <c r="M586" s="2" t="n">
-        <v>9120.93</v>
+        <v>9294.33</v>
       </c>
     </row>
     <row r="587">
@@ -36258,7 +36258,7 @@
         </is>
       </c>
       <c r="M587" s="2" t="n">
-        <v>985.6</v>
+        <v>1004.33</v>
       </c>
     </row>
     <row r="588">
@@ -36319,7 +36319,7 @@
         </is>
       </c>
       <c r="M588" s="2" t="n">
-        <v>1404.24</v>
+        <v>1430.94</v>
       </c>
     </row>
     <row r="589">
@@ -36380,7 +36380,7 @@
         </is>
       </c>
       <c r="M589" s="2" t="n">
-        <v>879.76</v>
+        <v>896.48</v>
       </c>
     </row>
     <row r="590">
@@ -36441,7 +36441,7 @@
         </is>
       </c>
       <c r="M590" s="2" t="n">
-        <v>5824.96</v>
+        <v>5935.7</v>
       </c>
     </row>
     <row r="591">
@@ -36502,7 +36502,7 @@
         </is>
       </c>
       <c r="M591" s="2" t="n">
-        <v>800.9299999999999</v>
+        <v>816.16</v>
       </c>
     </row>
     <row r="592">
@@ -36563,7 +36563,7 @@
         </is>
       </c>
       <c r="M592" s="2" t="n">
-        <v>1936.12</v>
+        <v>1972.93</v>
       </c>
     </row>
     <row r="593">
@@ -36624,7 +36624,7 @@
         </is>
       </c>
       <c r="M593" s="2" t="n">
-        <v>966.48</v>
+        <v>984.85</v>
       </c>
     </row>
     <row r="594">
@@ -36685,7 +36685,7 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>794.9</v>
+        <v>810.01</v>
       </c>
     </row>
     <row r="595">
@@ -36746,7 +36746,7 @@
         </is>
       </c>
       <c r="M595" s="2" t="n">
-        <v>6656.51</v>
+        <v>6783.06</v>
       </c>
     </row>
     <row r="596">
@@ -36807,7 +36807,7 @@
         </is>
       </c>
       <c r="M596" s="2" t="n">
-        <v>10473.41</v>
+        <v>10672.53</v>
       </c>
     </row>
     <row r="597">
@@ -36868,7 +36868,7 @@
         </is>
       </c>
       <c r="M597" s="2" t="n">
-        <v>793</v>
+        <v>808.0700000000001</v>
       </c>
     </row>
     <row r="598">
@@ -36929,7 +36929,7 @@
         </is>
       </c>
       <c r="M598" s="2" t="n">
-        <v>1109.93</v>
+        <v>1131.03</v>
       </c>
     </row>
     <row r="599">
@@ -36990,7 +36990,7 @@
         </is>
       </c>
       <c r="M599" s="2" t="n">
-        <v>829.51</v>
+        <v>845.28</v>
       </c>
     </row>
     <row r="600">
@@ -37051,7 +37051,7 @@
         </is>
       </c>
       <c r="M600" s="2" t="n">
-        <v>967.6900000000001</v>
+        <v>986.09</v>
       </c>
     </row>
     <row r="601">
@@ -37112,7 +37112,7 @@
         </is>
       </c>
       <c r="M601" s="2" t="n">
-        <v>3114.95</v>
+        <v>3174.17</v>
       </c>
     </row>
     <row r="602">
@@ -37173,7 +37173,7 @@
         </is>
       </c>
       <c r="M602" s="2" t="n">
-        <v>1818.66</v>
+        <v>1853.23</v>
       </c>
     </row>
     <row r="603">
@@ -37234,7 +37234,7 @@
         </is>
       </c>
       <c r="M603" s="2" t="n">
-        <v>17146.36</v>
+        <v>17533.06</v>
       </c>
     </row>
     <row r="604">
@@ -37295,7 +37295,7 @@
         </is>
       </c>
       <c r="M604" s="2" t="n">
-        <v>3159.3</v>
+        <v>3230.55</v>
       </c>
     </row>
     <row r="605">
@@ -37356,7 +37356,7 @@
         </is>
       </c>
       <c r="M605" s="2" t="n">
-        <v>5687.99</v>
+        <v>5816.27</v>
       </c>
     </row>
     <row r="606">
@@ -37417,7 +37417,7 @@
         </is>
       </c>
       <c r="M606" s="2" t="n">
-        <v>16075.95</v>
+        <v>16438.5</v>
       </c>
     </row>
     <row r="607">
@@ -37478,7 +37478,7 @@
         </is>
       </c>
       <c r="M607" s="2" t="n">
-        <v>4727.76</v>
+        <v>4834.38</v>
       </c>
     </row>
     <row r="608">
@@ -37539,7 +37539,7 @@
         </is>
       </c>
       <c r="M608" s="2" t="n">
-        <v>2314.03</v>
+        <v>2366.22</v>
       </c>
     </row>
     <row r="609">
@@ -37600,7 +37600,7 @@
         </is>
       </c>
       <c r="M609" s="2" t="n">
-        <v>828.9400000000001</v>
+        <v>847.64</v>
       </c>
     </row>
     <row r="610">
@@ -37661,7 +37661,7 @@
         </is>
       </c>
       <c r="M610" s="2" t="n">
-        <v>837.65</v>
+        <v>856.54</v>
       </c>
     </row>
     <row r="611">
@@ -37722,7 +37722,7 @@
         </is>
       </c>
       <c r="M611" s="2" t="n">
-        <v>1748.65</v>
+        <v>1788.08</v>
       </c>
     </row>
     <row r="612">
@@ -37783,7 +37783,7 @@
         </is>
       </c>
       <c r="M612" s="2" t="n">
-        <v>794.13</v>
+        <v>812.04</v>
       </c>
     </row>
     <row r="613">
@@ -37844,7 +37844,7 @@
         </is>
       </c>
       <c r="M613" s="2" t="n">
-        <v>1597.19</v>
+        <v>1633.21</v>
       </c>
     </row>
     <row r="614">
@@ -37905,7 +37905,7 @@
         </is>
       </c>
       <c r="M614" s="2" t="n">
-        <v>1443.73</v>
+        <v>1476.29</v>
       </c>
     </row>
     <row r="615">
@@ -37966,7 +37966,7 @@
         </is>
       </c>
       <c r="M615" s="2" t="n">
-        <v>852.8</v>
+        <v>872.03</v>
       </c>
     </row>
     <row r="616">
@@ -38027,7 +38027,7 @@
         </is>
       </c>
       <c r="M616" s="2" t="n">
-        <v>10490.73</v>
+        <v>10727.32</v>
       </c>
     </row>
     <row r="617">
@@ -38088,7 +38088,7 @@
         </is>
       </c>
       <c r="M617" s="2" t="n">
-        <v>1290.92</v>
+        <v>1320.04</v>
       </c>
     </row>
     <row r="618">
@@ -38149,7 +38149,7 @@
         </is>
       </c>
       <c r="M618" s="2" t="n">
-        <v>3285.07</v>
+        <v>3359.15</v>
       </c>
     </row>
     <row r="619">
@@ -38210,7 +38210,7 @@
         </is>
       </c>
       <c r="M619" s="2" t="n">
-        <v>6286.6</v>
+        <v>6428.38</v>
       </c>
     </row>
     <row r="620">
@@ -38271,7 +38271,7 @@
         </is>
       </c>
       <c r="M620" s="2" t="n">
-        <v>3224.67</v>
+        <v>3297.4</v>
       </c>
     </row>
     <row r="621">
@@ -38332,7 +38332,7 @@
         </is>
       </c>
       <c r="M621" s="2" t="n">
-        <v>961.99</v>
+        <v>983.6900000000001</v>
       </c>
     </row>
     <row r="622">
@@ -38393,7 +38393,7 @@
         </is>
       </c>
       <c r="M622" s="2" t="n">
-        <v>11745.35</v>
+        <v>12010.24</v>
       </c>
     </row>
     <row r="623">
@@ -38454,7 +38454,7 @@
         </is>
       </c>
       <c r="M623" s="2" t="n">
-        <v>845</v>
+        <v>864.0599999999999</v>
       </c>
     </row>
     <row r="624">
@@ -38515,7 +38515,7 @@
         </is>
       </c>
       <c r="M624" s="2" t="n">
-        <v>1009.48</v>
+        <v>1032.25</v>
       </c>
     </row>
     <row r="625">
@@ -38576,7 +38576,7 @@
         </is>
       </c>
       <c r="M625" s="2" t="n">
-        <v>3205.68</v>
+        <v>3277.98</v>
       </c>
     </row>
     <row r="626">
@@ -38637,7 +38637,7 @@
         </is>
       </c>
       <c r="M626" s="2" t="n">
-        <v>2334.28</v>
+        <v>2386.92</v>
       </c>
     </row>
     <row r="627">
@@ -38698,7 +38698,7 @@
         </is>
       </c>
       <c r="M627" s="2" t="n">
-        <v>1013.64</v>
+        <v>1036.5</v>
       </c>
     </row>
     <row r="628">
@@ -38759,7 +38759,7 @@
         </is>
       </c>
       <c r="M628" s="2" t="n">
-        <v>5722.89</v>
+        <v>5851.95</v>
       </c>
     </row>
     <row r="629">
@@ -38820,7 +38820,7 @@
         </is>
       </c>
       <c r="M629" s="2" t="n">
-        <v>840.47</v>
+        <v>859.42</v>
       </c>
     </row>
     <row r="630">
@@ -38881,7 +38881,7 @@
         </is>
       </c>
       <c r="M630" s="2" t="n">
-        <v>3381.32</v>
+        <v>3457.58</v>
       </c>
     </row>
     <row r="631">
@@ -38942,7 +38942,7 @@
         </is>
       </c>
       <c r="M631" s="2" t="n">
-        <v>14912.18</v>
+        <v>15248.49</v>
       </c>
     </row>
     <row r="632">
@@ -39003,7 +39003,7 @@
         </is>
       </c>
       <c r="M632" s="2" t="n">
-        <v>6387.43</v>
+        <v>6531.48</v>
       </c>
     </row>
     <row r="633">
@@ -39064,7 +39064,7 @@
         </is>
       </c>
       <c r="M633" s="2" t="n">
-        <v>4898.96</v>
+        <v>5009.44</v>
       </c>
     </row>
     <row r="634">
@@ -39125,7 +39125,7 @@
         </is>
       </c>
       <c r="M634" s="2" t="n">
-        <v>2412.02</v>
+        <v>2466.42</v>
       </c>
     </row>
     <row r="635">
@@ -39186,7 +39186,7 @@
         </is>
       </c>
       <c r="M635" s="2" t="n">
-        <v>908.09</v>
+        <v>928.5700000000001</v>
       </c>
     </row>
     <row r="636">
@@ -39251,7 +39251,7 @@
         </is>
       </c>
       <c r="M636" s="2" t="n">
-        <v>106625.67</v>
+        <v>109030.35</v>
       </c>
     </row>
     <row r="637">
@@ -39312,7 +39312,7 @@
         </is>
       </c>
       <c r="M637" s="2" t="n">
-        <v>4289.95</v>
+        <v>4386.7</v>
       </c>
     </row>
     <row r="638">
@@ -39373,7 +39373,7 @@
         </is>
       </c>
       <c r="M638" s="2" t="n">
-        <v>791.86</v>
+        <v>809.72</v>
       </c>
     </row>
     <row r="639">
@@ -39434,7 +39434,7 @@
         </is>
       </c>
       <c r="M639" s="2" t="n">
-        <v>8195.98</v>
+        <v>8380.82</v>
       </c>
     </row>
     <row r="640">
@@ -39495,7 +39495,7 @@
         </is>
       </c>
       <c r="M640" s="2" t="n">
-        <v>1975.02</v>
+        <v>2019.56</v>
       </c>
     </row>
     <row r="641">
@@ -39556,7 +39556,7 @@
         </is>
       </c>
       <c r="M641" s="2" t="n">
-        <v>2799.89</v>
+        <v>2863.04</v>
       </c>
     </row>
     <row r="642">
@@ -39617,7 +39617,7 @@
         </is>
       </c>
       <c r="M642" s="2" t="n">
-        <v>6159.55</v>
+        <v>6298.46</v>
       </c>
     </row>
     <row r="643">
@@ -39678,7 +39678,7 @@
         </is>
       </c>
       <c r="M643" s="2" t="n">
-        <v>3476.9</v>
+        <v>3555.32</v>
       </c>
     </row>
     <row r="644">
@@ -39739,7 +39739,7 @@
         </is>
       </c>
       <c r="M644" s="2" t="n">
-        <v>2917.25</v>
+        <v>2983.04</v>
       </c>
     </row>
     <row r="645">
@@ -39800,7 +39800,7 @@
         </is>
       </c>
       <c r="M645" s="2" t="n">
-        <v>873.55</v>
+        <v>893.25</v>
       </c>
     </row>
     <row r="646">
@@ -39861,7 +39861,7 @@
         </is>
       </c>
       <c r="M646" s="2" t="n">
-        <v>2310.98</v>
+        <v>2363.1</v>
       </c>
     </row>
     <row r="647">
@@ -39922,7 +39922,7 @@
         </is>
       </c>
       <c r="M647" s="2" t="n">
-        <v>2218.12</v>
+        <v>2268.15</v>
       </c>
     </row>
     <row r="648">
@@ -39983,7 +39983,7 @@
         </is>
       </c>
       <c r="M648" s="2" t="n">
-        <v>12245.23</v>
+        <v>12521.39</v>
       </c>
     </row>
     <row r="649">
@@ -40044,7 +40044,7 @@
         </is>
       </c>
       <c r="M649" s="2" t="n">
-        <v>11514.09</v>
+        <v>11773.76</v>
       </c>
     </row>
     <row r="650">
@@ -40105,7 +40105,7 @@
         </is>
       </c>
       <c r="M650" s="2" t="n">
-        <v>4905.43</v>
+        <v>5016.06</v>
       </c>
     </row>
     <row r="651">
@@ -40166,7 +40166,7 @@
         </is>
       </c>
       <c r="M651" s="2" t="n">
-        <v>1670.04</v>
+        <v>1707.7</v>
       </c>
     </row>
     <row r="652">
@@ -40227,7 +40227,7 @@
         </is>
       </c>
       <c r="M652" s="2" t="n">
-        <v>1170.35</v>
+        <v>1196.74</v>
       </c>
     </row>
     <row r="653">
@@ -40288,7 +40288,7 @@
         </is>
       </c>
       <c r="M653" s="2" t="n">
-        <v>796.1799999999999</v>
+        <v>814.14</v>
       </c>
     </row>
     <row r="654">
@@ -40349,7 +40349,7 @@
         </is>
       </c>
       <c r="M654" s="2" t="n">
-        <v>5490.18</v>
+        <v>5614</v>
       </c>
     </row>
     <row r="655">
@@ -40410,7 +40410,7 @@
         </is>
       </c>
       <c r="M655" s="2" t="n">
-        <v>10751.94</v>
+        <v>10994.43</v>
       </c>
     </row>
     <row r="656">
@@ -40471,7 +40471,7 @@
         </is>
       </c>
       <c r="M656" s="2" t="n">
-        <v>3220.5</v>
+        <v>3293.13</v>
       </c>
     </row>
     <row r="657">
@@ -40532,7 +40532,7 @@
         </is>
       </c>
       <c r="M657" s="2" t="n">
-        <v>1294.22</v>
+        <v>1323.4</v>
       </c>
     </row>
     <row r="658">
@@ -40593,7 +40593,7 @@
         </is>
       </c>
       <c r="M658" s="2" t="n">
-        <v>1246.98</v>
+        <v>1275.1</v>
       </c>
     </row>
     <row r="659">
@@ -40654,7 +40654,7 @@
         </is>
       </c>
       <c r="M659" s="2" t="n">
-        <v>3373.26</v>
+        <v>3449.34</v>
       </c>
     </row>
     <row r="660">
@@ -40715,7 +40715,7 @@
         </is>
       </c>
       <c r="M660" s="2" t="n">
-        <v>2315.81</v>
+        <v>2368.04</v>
       </c>
     </row>
     <row r="661">
@@ -40776,7 +40776,7 @@
         </is>
       </c>
       <c r="M661" s="2" t="n">
-        <v>3139.05</v>
+        <v>3209.85</v>
       </c>
     </row>
     <row r="662">
@@ -40837,7 +40837,7 @@
         </is>
       </c>
       <c r="M662" s="2" t="n">
-        <v>4388.55</v>
+        <v>4487.52</v>
       </c>
     </row>
     <row r="663">
@@ -40898,7 +40898,7 @@
         </is>
       </c>
       <c r="M663" s="2" t="n">
-        <v>1220.44</v>
+        <v>1228.87</v>
       </c>
     </row>
     <row r="664">
@@ -40959,7 +40959,7 @@
         </is>
       </c>
       <c r="M664" s="2" t="n">
-        <v>1323.05</v>
+        <v>1332.19</v>
       </c>
     </row>
     <row r="665">
@@ -41020,7 +41020,7 @@
         </is>
       </c>
       <c r="M665" s="2" t="n">
-        <v>6196.79</v>
+        <v>6239.57</v>
       </c>
     </row>
     <row r="666">
@@ -41081,7 +41081,7 @@
         </is>
       </c>
       <c r="M666" s="2" t="n">
-        <v>3131.91</v>
+        <v>3153.53</v>
       </c>
     </row>
     <row r="667">
@@ -41142,7 +41142,7 @@
         </is>
       </c>
       <c r="M667" s="2" t="n">
-        <v>830.9299999999999</v>
+        <v>836.67</v>
       </c>
     </row>
     <row r="668">
@@ -41203,7 +41203,7 @@
         </is>
       </c>
       <c r="M668" s="2" t="n">
-        <v>1237.38</v>
+        <v>1245.92</v>
       </c>
     </row>
     <row r="669">
@@ -41264,7 +41264,7 @@
         </is>
       </c>
       <c r="M669" s="2" t="n">
-        <v>925.49</v>
+        <v>931.88</v>
       </c>
     </row>
     <row r="670">
@@ -41325,7 +41325,7 @@
         </is>
       </c>
       <c r="M670" s="2" t="n">
-        <v>2819.18</v>
+        <v>2838.64</v>
       </c>
     </row>
     <row r="671">
@@ -41386,7 +41386,7 @@
         </is>
       </c>
       <c r="M671" s="2" t="n">
-        <v>1984.6</v>
+        <v>1998.3</v>
       </c>
     </row>
     <row r="672">
@@ -41447,7 +41447,7 @@
         </is>
       </c>
       <c r="M672" s="2" t="n">
-        <v>8438.860000000001</v>
+        <v>8497.120000000001</v>
       </c>
     </row>
     <row r="673">
@@ -41508,7 +41508,7 @@
         </is>
       </c>
       <c r="M673" s="2" t="n">
-        <v>4470.15</v>
+        <v>4501.01</v>
       </c>
     </row>
     <row r="674">
@@ -41569,7 +41569,7 @@
         </is>
       </c>
       <c r="M674" s="2" t="n">
-        <v>10925.23</v>
+        <v>11000.66</v>
       </c>
     </row>
     <row r="675">
@@ -41630,7 +41630,7 @@
         </is>
       </c>
       <c r="M675" s="2" t="n">
-        <v>2411.72</v>
+        <v>2428.37</v>
       </c>
     </row>
     <row r="676">
@@ -41691,7 +41691,7 @@
         </is>
       </c>
       <c r="M676" s="2" t="n">
-        <v>1891.6</v>
+        <v>1904.66</v>
       </c>
     </row>
     <row r="677">
@@ -41752,7 +41752,7 @@
         </is>
       </c>
       <c r="M677" s="2" t="n">
-        <v>3338.82</v>
+        <v>3361.87</v>
       </c>
     </row>
     <row r="678">
@@ -41813,7 +41813,7 @@
         </is>
       </c>
       <c r="M678" s="2" t="n">
-        <v>1975.11</v>
+        <v>1988.74</v>
       </c>
     </row>
     <row r="679">
@@ -41874,7 +41874,7 @@
         </is>
       </c>
       <c r="M679" s="2" t="n">
-        <v>2149.52</v>
+        <v>2164.36</v>
       </c>
     </row>
     <row r="680">
@@ -41935,7 +41935,7 @@
         </is>
       </c>
       <c r="M680" s="2" t="n">
-        <v>12681.03</v>
+        <v>12768.58</v>
       </c>
     </row>
     <row r="681">
@@ -41996,7 +41996,7 @@
         </is>
       </c>
       <c r="M681" s="2" t="n">
-        <v>2093.4</v>
+        <v>2107.86</v>
       </c>
     </row>
     <row r="682">
@@ -42057,7 +42057,7 @@
         </is>
       </c>
       <c r="M682" s="2" t="n">
-        <v>1676.88</v>
+        <v>1688.46</v>
       </c>
     </row>
     <row r="683">
@@ -42118,7 +42118,7 @@
         </is>
       </c>
       <c r="M683" s="2" t="n">
-        <v>792.9</v>
+        <v>798.38</v>
       </c>
     </row>
     <row r="684">
@@ -42179,7 +42179,7 @@
         </is>
       </c>
       <c r="M684" s="2" t="n">
-        <v>4498.97</v>
+        <v>4530.04</v>
       </c>
     </row>
     <row r="685">
@@ -42240,7 +42240,7 @@
         </is>
       </c>
       <c r="M685" s="2" t="n">
-        <v>2808.71</v>
+        <v>2828.1</v>
       </c>
     </row>
     <row r="686">
@@ -42301,7 +42301,7 @@
         </is>
       </c>
       <c r="M686" s="2" t="n">
-        <v>7112.44</v>
+        <v>7161.54</v>
       </c>
     </row>
     <row r="687">
@@ -42362,7 +42362,7 @@
         </is>
       </c>
       <c r="M687" s="2" t="n">
-        <v>3518.18</v>
+        <v>3542.47</v>
       </c>
     </row>
     <row r="688">
@@ -42423,7 +42423,7 @@
         </is>
       </c>
       <c r="M688" s="2" t="n">
-        <v>921.38</v>
+        <v>927.74</v>
       </c>
     </row>
     <row r="689">
@@ -42484,7 +42484,7 @@
         </is>
       </c>
       <c r="M689" s="2" t="n">
-        <v>10939.11</v>
+        <v>11014.63</v>
       </c>
     </row>
     <row r="690">
@@ -42545,7 +42545,7 @@
         </is>
       </c>
       <c r="M690" s="2" t="n">
-        <v>805.11</v>
+        <v>810.67</v>
       </c>
     </row>
     <row r="691">
@@ -42606,7 +42606,7 @@
         </is>
       </c>
       <c r="M691" s="2" t="n">
-        <v>5041.85</v>
+        <v>5076.66</v>
       </c>
     </row>
     <row r="692">
@@ -42667,7 +42667,7 @@
         </is>
       </c>
       <c r="M692" s="2" t="n">
-        <v>1067.01</v>
+        <v>1074.38</v>
       </c>
     </row>
     <row r="693">
@@ -42728,7 +42728,7 @@
         </is>
       </c>
       <c r="M693" s="2" t="n">
-        <v>8931.08</v>
+        <v>8992.74</v>
       </c>
     </row>
     <row r="694">
@@ -42789,7 +42789,7 @@
         </is>
       </c>
       <c r="M694" s="2" t="n">
-        <v>813.98</v>
+        <v>819.6</v>
       </c>
     </row>
     <row r="695">
@@ -42850,7 +42850,7 @@
         </is>
       </c>
       <c r="M695" s="2" t="n">
-        <v>10381.13</v>
+        <v>10452.8</v>
       </c>
     </row>
     <row r="696">
@@ -42911,7 +42911,7 @@
         </is>
       </c>
       <c r="M696" s="2" t="n">
-        <v>1734.84</v>
+        <v>1746.82</v>
       </c>
     </row>
     <row r="697">
@@ -42972,7 +42972,7 @@
         </is>
       </c>
       <c r="M697" s="2" t="n">
-        <v>2495.17</v>
+        <v>2512.4</v>
       </c>
     </row>
     <row r="698">
@@ -43033,7 +43033,7 @@
         </is>
       </c>
       <c r="M698" s="2" t="n">
-        <v>2097.64</v>
+        <v>2112.12</v>
       </c>
     </row>
     <row r="699">
@@ -43094,7 +43094,7 @@
         </is>
       </c>
       <c r="M699" s="2" t="n">
-        <v>4636.06</v>
+        <v>4668.07</v>
       </c>
     </row>
     <row r="700">
@@ -43155,7 +43155,7 @@
         </is>
       </c>
       <c r="M700" s="2" t="n">
-        <v>13157.44</v>
+        <v>13248.28</v>
       </c>
     </row>
     <row r="701">
@@ -43216,7 +43216,7 @@
         </is>
       </c>
       <c r="M701" s="2" t="n">
-        <v>827.64</v>
+        <v>833.35</v>
       </c>
     </row>
     <row r="702">
@@ -43277,7 +43277,7 @@
         </is>
       </c>
       <c r="M702" s="2" t="n">
-        <v>6334.4</v>
+        <v>6378.14</v>
       </c>
     </row>
     <row r="703">
@@ -43338,7 +43338,7 @@
         </is>
       </c>
       <c r="M703" s="2" t="n">
-        <v>20715.37</v>
+        <v>20858.39</v>
       </c>
     </row>
     <row r="704">
@@ -43399,7 +43399,7 @@
         </is>
       </c>
       <c r="M704" s="2" t="n">
-        <v>5595.76</v>
+        <v>5634.39</v>
       </c>
     </row>
     <row r="705">
@@ -43460,7 +43460,7 @@
         </is>
       </c>
       <c r="M705" s="2" t="n">
-        <v>1993.29</v>
+        <v>2007.05</v>
       </c>
     </row>
     <row r="706">
@@ -43521,7 +43521,7 @@
         </is>
       </c>
       <c r="M706" s="2" t="n">
-        <v>2592.93</v>
+        <v>2610.83</v>
       </c>
     </row>
     <row r="707">
@@ -43582,7 +43582,7 @@
         </is>
       </c>
       <c r="M707" s="2" t="n">
-        <v>807.78</v>
+        <v>813.36</v>
       </c>
     </row>
     <row r="708">
@@ -43643,7 +43643,7 @@
         </is>
       </c>
       <c r="M708" s="2" t="n">
-        <v>1890.42</v>
+        <v>1903.47</v>
       </c>
     </row>
     <row r="709">
@@ -43704,7 +43704,7 @@
         </is>
       </c>
       <c r="M709" s="2" t="n">
-        <v>4564.28</v>
+        <v>4595.79</v>
       </c>
     </row>
     <row r="710">
@@ -43765,7 +43765,7 @@
         </is>
       </c>
       <c r="M710" s="2" t="n">
-        <v>1134.91</v>
+        <v>1142.75</v>
       </c>
     </row>
     <row r="711">
@@ -43826,7 +43826,7 @@
         </is>
       </c>
       <c r="M711" s="2" t="n">
-        <v>6635.4</v>
+        <v>6681.21</v>
       </c>
     </row>
     <row r="712">
@@ -43887,7 +43887,7 @@
         </is>
       </c>
       <c r="M712" s="2" t="n">
-        <v>2459.76</v>
+        <v>2476.74</v>
       </c>
     </row>
     <row r="713">
@@ -43948,7 +43948,7 @@
         </is>
       </c>
       <c r="M713" s="2" t="n">
-        <v>2751.36</v>
+        <v>2770.36</v>
       </c>
     </row>
     <row r="714">
@@ -44009,7 +44009,7 @@
         </is>
       </c>
       <c r="M714" s="2" t="n">
-        <v>5125.62</v>
+        <v>5141.47</v>
       </c>
     </row>
     <row r="715">
@@ -44070,7 +44070,7 @@
         </is>
       </c>
       <c r="M715" s="2" t="n">
-        <v>1869.91</v>
+        <v>1875.69</v>
       </c>
     </row>
     <row r="716">
@@ -44131,7 +44131,7 @@
         </is>
       </c>
       <c r="M716" s="2" t="n">
-        <v>5779.78</v>
+        <v>5797.65</v>
       </c>
     </row>
     <row r="717">
@@ -44192,7 +44192,7 @@
         </is>
       </c>
       <c r="M717" s="2" t="n">
-        <v>15561.83</v>
+        <v>15609.95</v>
       </c>
     </row>
     <row r="718">
@@ -44253,7 +44253,7 @@
         </is>
       </c>
       <c r="M718" s="2" t="n">
-        <v>871.52</v>
+        <v>874.22</v>
       </c>
     </row>
     <row r="719">
@@ -44314,7 +44314,7 @@
         </is>
       </c>
       <c r="M719" s="2" t="n">
-        <v>931.84</v>
+        <v>934.72</v>
       </c>
     </row>
     <row r="720">
@@ -44375,7 +44375,7 @@
         </is>
       </c>
       <c r="M720" s="2" t="n">
-        <v>909.09</v>
+        <v>911.9</v>
       </c>
     </row>
     <row r="721">
@@ -44436,7 +44436,7 @@
         </is>
       </c>
       <c r="M721" s="2" t="n">
-        <v>4502.76</v>
+        <v>4516.69</v>
       </c>
     </row>
     <row r="722">
@@ -44497,7 +44497,7 @@
         </is>
       </c>
       <c r="M722" s="2" t="n">
-        <v>2628.74</v>
+        <v>2636.87</v>
       </c>
     </row>
     <row r="723">
@@ -44558,7 +44558,7 @@
         </is>
       </c>
       <c r="M723" s="2" t="n">
-        <v>4128.32</v>
+        <v>4141.08</v>
       </c>
     </row>
     <row r="724">
@@ -44619,7 +44619,7 @@
         </is>
       </c>
       <c r="M724" s="2" t="n">
-        <v>2831.49</v>
+        <v>2840.24</v>
       </c>
     </row>
     <row r="725">
@@ -44680,7 +44680,7 @@
         </is>
       </c>
       <c r="M725" s="2" t="n">
-        <v>4101.42</v>
+        <v>4114.1</v>
       </c>
     </row>
     <row r="726">
@@ -44741,7 +44741,7 @@
         </is>
       </c>
       <c r="M726" s="2" t="n">
-        <v>5445.73</v>
+        <v>5462.56</v>
       </c>
     </row>
     <row r="727">
@@ -44802,7 +44802,7 @@
         </is>
       </c>
       <c r="M727" s="2" t="n">
-        <v>886.22</v>
+        <v>888.96</v>
       </c>
     </row>
     <row r="728">
@@ -44863,7 +44863,7 @@
         </is>
       </c>
       <c r="M728" s="2" t="n">
-        <v>1104.31</v>
+        <v>1107.72</v>
       </c>
     </row>
     <row r="729">
@@ -44924,7 +44924,7 @@
         </is>
       </c>
       <c r="M729" s="2" t="n">
-        <v>18764.6</v>
+        <v>18822.61</v>
       </c>
     </row>
     <row r="730">
@@ -44985,7 +44985,7 @@
         </is>
       </c>
       <c r="M730" s="2" t="n">
-        <v>7013.14</v>
+        <v>7034.82</v>
       </c>
     </row>
     <row r="731">
@@ -45046,7 +45046,7 @@
         </is>
       </c>
       <c r="M731" s="2" t="n">
-        <v>7192.59</v>
+        <v>7214.83</v>
       </c>
     </row>
     <row r="732">
@@ -45107,7 +45107,7 @@
         </is>
       </c>
       <c r="M732" s="2" t="n">
-        <v>4446.64</v>
+        <v>4460.39</v>
       </c>
     </row>
     <row r="733">
@@ -45168,7 +45168,7 @@
         </is>
       </c>
       <c r="M733" s="2" t="n">
-        <v>2432.34</v>
+        <v>2439.86</v>
       </c>
     </row>
     <row r="734">
@@ -45229,7 +45229,7 @@
         </is>
       </c>
       <c r="M734" s="2" t="n">
-        <v>1844.9</v>
+        <v>1850.6</v>
       </c>
     </row>
     <row r="735">
@@ -45290,7 +45290,7 @@
         </is>
       </c>
       <c r="M735" s="2" t="n">
-        <v>5811.37</v>
+        <v>5829.34</v>
       </c>
     </row>
     <row r="736">
@@ -45351,7 +45351,7 @@
         </is>
       </c>
       <c r="M736" s="2" t="n">
-        <v>5551.84</v>
+        <v>5569</v>
       </c>
     </row>
     <row r="737">
@@ -45412,7 +45412,7 @@
         </is>
       </c>
       <c r="M737" s="2" t="n">
-        <v>1016.13</v>
+        <v>1019.28</v>
       </c>
     </row>
     <row r="738">
@@ -45473,7 +45473,7 @@
         </is>
       </c>
       <c r="M738" s="2" t="n">
-        <v>1523.68</v>
+        <v>1528.39</v>
       </c>
     </row>
     <row r="739">
@@ -45534,7 +45534,7 @@
         </is>
       </c>
       <c r="M739" s="2" t="n">
-        <v>3061.43</v>
+        <v>3070.89</v>
       </c>
     </row>
     <row r="740">
@@ -45595,7 +45595,7 @@
         </is>
       </c>
       <c r="M740" s="2" t="n">
-        <v>3602.75</v>
+        <v>3613.89</v>
       </c>
     </row>
     <row r="741">
@@ -45656,7 +45656,7 @@
         </is>
       </c>
       <c r="M741" s="2" t="n">
-        <v>1604.5</v>
+        <v>1609.47</v>
       </c>
     </row>
     <row r="742">
@@ -45717,7 +45717,7 @@
         </is>
       </c>
       <c r="M742" s="2" t="n">
-        <v>4186.48</v>
+        <v>4199.42</v>
       </c>
     </row>
     <row r="743">
@@ -45778,7 +45778,7 @@
         </is>
       </c>
       <c r="M743" s="2" t="n">
-        <v>1683.06</v>
+        <v>1688.26</v>
       </c>
     </row>
     <row r="744">
@@ -45839,7 +45839,7 @@
         </is>
       </c>
       <c r="M744" s="2" t="n">
-        <v>3721.84</v>
+        <v>3733.34</v>
       </c>
     </row>
     <row r="745">
@@ -45900,7 +45900,7 @@
         </is>
       </c>
       <c r="M745" s="2" t="n">
-        <v>2764.68</v>
+        <v>2773.23</v>
       </c>
     </row>
     <row r="746">
@@ -45961,7 +45961,7 @@
         </is>
       </c>
       <c r="M746" s="2" t="n">
-        <v>2495.18</v>
+        <v>2502.9</v>
       </c>
     </row>
     <row r="747">
@@ -46022,7 +46022,7 @@
         </is>
       </c>
       <c r="M747" s="2" t="n">
-        <v>1766.46</v>
+        <v>1771.92</v>
       </c>
     </row>
     <row r="748">
@@ -46083,7 +46083,7 @@
         </is>
       </c>
       <c r="M748" s="2" t="n">
-        <v>2088.53</v>
+        <v>2094.99</v>
       </c>
     </row>
     <row r="749">
@@ -46144,7 +46144,7 @@
         </is>
       </c>
       <c r="M749" s="2" t="n">
-        <v>7167.56</v>
+        <v>7189.72</v>
       </c>
     </row>
     <row r="750">
@@ -46205,7 +46205,7 @@
         </is>
       </c>
       <c r="M750" s="2" t="n">
-        <v>1396.09</v>
+        <v>1400.41</v>
       </c>
     </row>
     <row r="751">
@@ -46266,7 +46266,7 @@
         </is>
       </c>
       <c r="M751" s="2" t="n">
-        <v>10045.92</v>
+        <v>10076.98</v>
       </c>
     </row>
     <row r="752">
@@ -46327,7 +46327,7 @@
         </is>
       </c>
       <c r="M752" s="2" t="n">
-        <v>13166.68</v>
+        <v>13207.39</v>
       </c>
     </row>
     <row r="753">
@@ -46388,7 +46388,7 @@
         </is>
       </c>
       <c r="M753" s="2" t="n">
-        <v>17488.21</v>
+        <v>17542.27</v>
       </c>
     </row>
     <row r="754">
@@ -46449,7 +46449,7 @@
         </is>
       </c>
       <c r="M754" s="2" t="n">
-        <v>1574.83</v>
+        <v>1570.67</v>
       </c>
     </row>
     <row r="755">
@@ -46510,7 +46510,7 @@
         </is>
       </c>
       <c r="M755" s="2" t="n">
-        <v>3342.53</v>
+        <v>3333.69</v>
       </c>
     </row>
     <row r="756">
@@ -46571,7 +46571,7 @@
         </is>
       </c>
       <c r="M756" s="2" t="n">
-        <v>4882.11</v>
+        <v>4869.2</v>
       </c>
     </row>
     <row r="757">
@@ -46632,7 +46632,7 @@
         </is>
       </c>
       <c r="M757" s="2" t="n">
-        <v>1107.5</v>
+        <v>1104.57</v>
       </c>
     </row>
     <row r="758">
@@ -46693,7 +46693,7 @@
         </is>
       </c>
       <c r="M758" s="2" t="n">
-        <v>1725.06</v>
+        <v>1720.5</v>
       </c>
     </row>
     <row r="759">
@@ -46754,7 +46754,7 @@
         </is>
       </c>
       <c r="M759" s="2" t="n">
-        <v>8221.02</v>
+        <v>8199.280000000001</v>
       </c>
     </row>
     <row r="760">
@@ -46815,7 +46815,7 @@
         </is>
       </c>
       <c r="M760" s="2" t="n">
-        <v>2561.29</v>
+        <v>2554.52</v>
       </c>
     </row>
     <row r="761">
@@ -46876,7 +46876,7 @@
         </is>
       </c>
       <c r="M761" s="2" t="n">
-        <v>23241.65</v>
+        <v>23180.18</v>
       </c>
     </row>
     <row r="762">
@@ -46937,7 +46937,7 @@
         </is>
       </c>
       <c r="M762" s="2" t="n">
-        <v>840.86</v>
+        <v>838.64</v>
       </c>
     </row>
     <row r="763">
@@ -46998,7 +46998,7 @@
         </is>
       </c>
       <c r="M763" s="2" t="n">
-        <v>1834.64</v>
+        <v>1829.79</v>
       </c>
     </row>
     <row r="764">
@@ -47059,7 +47059,7 @@
         </is>
       </c>
       <c r="M764" s="2" t="n">
-        <v>4057.81</v>
+        <v>4047.08</v>
       </c>
     </row>
     <row r="765">
@@ -47120,7 +47120,7 @@
         </is>
       </c>
       <c r="M765" s="2" t="n">
-        <v>1060.8</v>
+        <v>1057.99</v>
       </c>
     </row>
     <row r="766">
@@ -47181,7 +47181,7 @@
         </is>
       </c>
       <c r="M766" s="2" t="n">
-        <v>1520.9</v>
+        <v>1516.88</v>
       </c>
     </row>
     <row r="767">
@@ -47242,7 +47242,7 @@
         </is>
       </c>
       <c r="M767" s="2" t="n">
-        <v>2190.96</v>
+        <v>2185.16</v>
       </c>
     </row>
     <row r="768">
@@ -47303,7 +47303,7 @@
         </is>
       </c>
       <c r="M768" s="2" t="n">
-        <v>5903.03</v>
+        <v>5887.42</v>
       </c>
     </row>
     <row r="769">
@@ -47364,7 +47364,7 @@
         </is>
       </c>
       <c r="M769" s="2" t="n">
-        <v>1323.84</v>
+        <v>1320.34</v>
       </c>
     </row>
     <row r="770">
@@ -47425,7 +47425,7 @@
         </is>
       </c>
       <c r="M770" s="2" t="n">
-        <v>5836.03</v>
+        <v>5820.59</v>
       </c>
     </row>
     <row r="771">
@@ -47486,7 +47486,7 @@
         </is>
       </c>
       <c r="M771" s="2" t="n">
-        <v>3037.62</v>
+        <v>3029.59</v>
       </c>
     </row>
     <row r="772">
@@ -47547,7 +47547,7 @@
         </is>
       </c>
       <c r="M772" s="2" t="n">
-        <v>1047.86</v>
+        <v>1045.09</v>
       </c>
     </row>
     <row r="773">
@@ -47608,7 +47608,7 @@
         </is>
       </c>
       <c r="M773" s="2" t="n">
-        <v>1106.01</v>
+        <v>1103.09</v>
       </c>
     </row>
     <row r="774">
@@ -47669,7 +47669,7 @@
         </is>
       </c>
       <c r="M774" s="2" t="n">
-        <v>1081.21</v>
+        <v>1078.35</v>
       </c>
     </row>
     <row r="775">
@@ -47730,7 +47730,7 @@
         </is>
       </c>
       <c r="M775" s="2" t="n">
-        <v>10199.98</v>
+        <v>10173.01</v>
       </c>
     </row>
     <row r="776">
@@ -47791,7 +47791,7 @@
         </is>
       </c>
       <c r="M776" s="2" t="n">
-        <v>2885.4</v>
+        <v>2877.77</v>
       </c>
     </row>
     <row r="777">
@@ -47852,7 +47852,7 @@
         </is>
       </c>
       <c r="M777" s="2" t="n">
-        <v>1538.2</v>
+        <v>1534.13</v>
       </c>
     </row>
     <row r="778">
@@ -47913,7 +47913,7 @@
         </is>
       </c>
       <c r="M778" s="2" t="n">
-        <v>2716</v>
+        <v>2708.82</v>
       </c>
     </row>
     <row r="779">
@@ -47974,7 +47974,7 @@
         </is>
       </c>
       <c r="M779" s="2" t="n">
-        <v>2137.63</v>
+        <v>2131.98</v>
       </c>
     </row>
     <row r="780">
@@ -48035,7 +48035,7 @@
         </is>
       </c>
       <c r="M780" s="2" t="n">
-        <v>3964.31</v>
+        <v>3953.82</v>
       </c>
     </row>
     <row r="781">
@@ -48096,7 +48096,7 @@
         </is>
       </c>
       <c r="M781" s="2" t="n">
-        <v>2992.58</v>
+        <v>2984.66</v>
       </c>
     </row>
     <row r="782">
@@ -48157,7 +48157,7 @@
         </is>
       </c>
       <c r="M782" s="2" t="n">
-        <v>1026.78</v>
+        <v>1024.06</v>
       </c>
     </row>
     <row r="783">
@@ -48218,7 +48218,7 @@
         </is>
       </c>
       <c r="M783" s="2" t="n">
-        <v>13036.22</v>
+        <v>13001.74</v>
       </c>
     </row>
     <row r="784">
@@ -48279,7 +48279,7 @@
         </is>
       </c>
       <c r="M784" s="2" t="n">
-        <v>6101.98</v>
+        <v>6085.85</v>
       </c>
     </row>
     <row r="785">
@@ -48340,7 +48340,7 @@
         </is>
       </c>
       <c r="M785" s="2" t="n">
-        <v>11207.64</v>
+        <v>11178</v>
       </c>
     </row>
     <row r="786">
@@ -48401,7 +48401,7 @@
         </is>
       </c>
       <c r="M786" s="2" t="n">
-        <v>1581.03</v>
+        <v>1576.85</v>
       </c>
     </row>
     <row r="787">
@@ -48462,7 +48462,7 @@
         </is>
       </c>
       <c r="M787" s="2" t="n">
-        <v>4181.93</v>
+        <v>4170.87</v>
       </c>
     </row>
     <row r="788">
@@ -48523,7 +48523,7 @@
         </is>
       </c>
       <c r="M788" s="2" t="n">
-        <v>7418.04</v>
+        <v>7398.42</v>
       </c>
     </row>
     <row r="789">
@@ -48584,7 +48584,7 @@
         </is>
       </c>
       <c r="M789" s="2" t="n">
-        <v>3512.47</v>
+        <v>3503.18</v>
       </c>
     </row>
     <row r="790">
@@ -48645,7 +48645,7 @@
         </is>
       </c>
       <c r="M790" s="2" t="n">
-        <v>2403.09</v>
+        <v>2396.73</v>
       </c>
     </row>
     <row r="791">
@@ -48706,7 +48706,7 @@
         </is>
       </c>
       <c r="M791" s="2" t="n">
-        <v>8913.040000000001</v>
+        <v>8889.459999999999</v>
       </c>
     </row>
     <row r="792">
@@ -48767,7 +48767,7 @@
         </is>
       </c>
       <c r="M792" s="2" t="n">
-        <v>2509.14</v>
+        <v>2502.5</v>
       </c>
     </row>
     <row r="793">
@@ -48828,7 +48828,7 @@
         </is>
       </c>
       <c r="M793" s="2" t="n">
-        <v>1286.1</v>
+        <v>1282.7</v>
       </c>
     </row>
     <row r="794">
@@ -48889,7 +48889,7 @@
         </is>
       </c>
       <c r="M794" s="2" t="n">
-        <v>5597.02</v>
+        <v>5582.22</v>
       </c>
     </row>
     <row r="795">
@@ -48950,7 +48950,7 @@
         </is>
       </c>
       <c r="M795" s="2" t="n">
-        <v>4861.51</v>
+        <v>4848.65</v>
       </c>
     </row>
     <row r="796">
@@ -49011,7 +49011,7 @@
         </is>
       </c>
       <c r="M796" s="2" t="n">
-        <v>2578.27</v>
+        <v>2571.46</v>
       </c>
     </row>
     <row r="797">
@@ -49072,7 +49072,7 @@
         </is>
       </c>
       <c r="M797" s="2" t="n">
-        <v>2381.89</v>
+        <v>2375.59</v>
       </c>
     </row>
     <row r="798">
@@ -49133,7 +49133,7 @@
         </is>
       </c>
       <c r="M798" s="2" t="n">
-        <v>8979.93</v>
+        <v>8956.18</v>
       </c>
     </row>
     <row r="799">
@@ -49194,7 +49194,7 @@
         </is>
       </c>
       <c r="M799" s="2" t="n">
-        <v>6117.79</v>
+        <v>6101.61</v>
       </c>
     </row>
     <row r="800">
@@ -49255,7 +49255,7 @@
         </is>
       </c>
       <c r="M800" s="2" t="n">
-        <v>4914.65</v>
+        <v>4849.19</v>
       </c>
     </row>
     <row r="801">
@@ -49316,7 +49316,7 @@
         </is>
       </c>
       <c r="M801" s="2" t="n">
-        <v>4125.29</v>
+        <v>4070.34</v>
       </c>
     </row>
     <row r="802">
@@ -49377,7 +49377,7 @@
         </is>
       </c>
       <c r="M802" s="2" t="n">
-        <v>800.11</v>
+        <v>789.45</v>
       </c>
     </row>
     <row r="803">
@@ -49438,7 +49438,7 @@
         </is>
       </c>
       <c r="M803" s="2" t="n">
-        <v>2504.78</v>
+        <v>2471.42</v>
       </c>
     </row>
     <row r="804">
@@ -49499,7 +49499,7 @@
         </is>
       </c>
       <c r="M804" s="2" t="n">
-        <v>5137.84</v>
+        <v>5069.4</v>
       </c>
     </row>
     <row r="805">
@@ -49560,7 +49560,7 @@
         </is>
       </c>
       <c r="M805" s="2" t="n">
-        <v>858.23</v>
+        <v>846.8</v>
       </c>
     </row>
     <row r="806">
@@ -49621,7 +49621,7 @@
         </is>
       </c>
       <c r="M806" s="2" t="n">
-        <v>990.85</v>
+        <v>977.65</v>
       </c>
     </row>
     <row r="807">
@@ -49682,7 +49682,7 @@
         </is>
       </c>
       <c r="M807" s="2" t="n">
-        <v>29581.09</v>
+        <v>29187.07</v>
       </c>
     </row>
     <row r="808">
@@ -49743,7 +49743,7 @@
         </is>
       </c>
       <c r="M808" s="2" t="n">
-        <v>3331.47</v>
+        <v>3287.09</v>
       </c>
     </row>
     <row r="809">
@@ -49804,7 +49804,7 @@
         </is>
       </c>
       <c r="M809" s="2" t="n">
-        <v>4338.5</v>
+        <v>4280.71</v>
       </c>
     </row>
     <row r="810">
@@ -49865,7 +49865,7 @@
         </is>
       </c>
       <c r="M810" s="2" t="n">
-        <v>10075.66</v>
+        <v>9941.450000000001</v>
       </c>
     </row>
     <row r="811">
@@ -49926,7 +49926,7 @@
         </is>
       </c>
       <c r="M811" s="2" t="n">
-        <v>1048.98</v>
+        <v>1035.01</v>
       </c>
     </row>
     <row r="812">
@@ -49987,7 +49987,7 @@
         </is>
       </c>
       <c r="M812" s="2" t="n">
-        <v>3331.9</v>
+        <v>3287.52</v>
       </c>
     </row>
     <row r="813">
@@ -50048,7 +50048,7 @@
         </is>
       </c>
       <c r="M813" s="2" t="n">
-        <v>2855.87</v>
+        <v>2817.82</v>
       </c>
     </row>
     <row r="814">
@@ -50109,7 +50109,7 @@
         </is>
       </c>
       <c r="M814" s="2" t="n">
-        <v>4596.29</v>
+        <v>4535.07</v>
       </c>
     </row>
     <row r="815">
@@ -50170,7 +50170,7 @@
         </is>
       </c>
       <c r="M815" s="2" t="n">
-        <v>1605.82</v>
+        <v>1584.43</v>
       </c>
     </row>
     <row r="816">
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="M816" s="2" t="n">
-        <v>7684.47</v>
+        <v>7582.11</v>
       </c>
     </row>
     <row r="817">
@@ -50292,7 +50292,7 @@
         </is>
       </c>
       <c r="M817" s="2" t="n">
-        <v>3389.53</v>
+        <v>3344.38</v>
       </c>
     </row>
     <row r="818">
@@ -50353,7 +50353,7 @@
         </is>
       </c>
       <c r="M818" s="2" t="n">
-        <v>791.54</v>
+        <v>781</v>
       </c>
     </row>
     <row r="819">
@@ -50414,7 +50414,7 @@
         </is>
       </c>
       <c r="M819" s="2" t="n">
-        <v>2475.08</v>
+        <v>2442.11</v>
       </c>
     </row>
     <row r="820">
@@ -50475,7 +50475,7 @@
         </is>
       </c>
       <c r="M820" s="2" t="n">
-        <v>1356.04</v>
+        <v>1337.97</v>
       </c>
     </row>
     <row r="821">
@@ -50536,7 +50536,7 @@
         </is>
       </c>
       <c r="M821" s="2" t="n">
-        <v>14636.56</v>
+        <v>14441.59</v>
       </c>
     </row>
     <row r="822">
@@ -50597,7 +50597,7 @@
         </is>
       </c>
       <c r="M822" s="2" t="n">
-        <v>2767.32</v>
+        <v>2730.46</v>
       </c>
     </row>
     <row r="823">
@@ -50658,7 +50658,7 @@
         </is>
       </c>
       <c r="M823" s="2" t="n">
-        <v>27050.91</v>
+        <v>26690.59</v>
       </c>
     </row>
     <row r="824">
@@ -50723,7 +50723,7 @@
         </is>
       </c>
       <c r="M824" s="2" t="n">
-        <v>68379.95</v>
+        <v>67469.12</v>
       </c>
     </row>
     <row r="825">
@@ -50784,7 +50784,7 @@
         </is>
       </c>
       <c r="M825" s="2" t="n">
-        <v>1847.13</v>
+        <v>1822.52</v>
       </c>
     </row>
     <row r="826">
@@ -50845,7 +50845,7 @@
         </is>
       </c>
       <c r="M826" s="2" t="n">
-        <v>5602.34</v>
+        <v>5527.72</v>
       </c>
     </row>
     <row r="827">
@@ -50906,7 +50906,7 @@
         </is>
       </c>
       <c r="M827" s="2" t="n">
-        <v>40045.26</v>
+        <v>39511.85</v>
       </c>
     </row>
     <row r="828">
@@ -50967,7 +50967,7 @@
         </is>
       </c>
       <c r="M828" s="2" t="n">
-        <v>2452.75</v>
+        <v>2420.08</v>
       </c>
     </row>
     <row r="829">
@@ -51028,7 +51028,7 @@
         </is>
       </c>
       <c r="M829" s="2" t="n">
-        <v>797.1799999999999</v>
+        <v>786.5599999999999</v>
       </c>
     </row>
     <row r="830">
@@ -51089,7 +51089,7 @@
         </is>
       </c>
       <c r="M830" s="2" t="n">
-        <v>9441.440000000001</v>
+        <v>9315.68</v>
       </c>
     </row>
     <row r="831">
@@ -51150,7 +51150,7 @@
         </is>
       </c>
       <c r="M831" s="2" t="n">
-        <v>21847.17</v>
+        <v>21556.16</v>
       </c>
     </row>
     <row r="832">
@@ -51211,7 +51211,7 @@
         </is>
       </c>
       <c r="M832" s="2" t="n">
-        <v>1664.09</v>
+        <v>1641.92</v>
       </c>
     </row>
     <row r="833">
@@ -51272,7 +51272,7 @@
         </is>
       </c>
       <c r="M833" s="2" t="n">
-        <v>15110.6</v>
+        <v>14909.33</v>
       </c>
     </row>
     <row r="834">
@@ -51333,7 +51333,7 @@
         </is>
       </c>
       <c r="M834" s="2" t="n">
-        <v>1777.87</v>
+        <v>1754.18</v>
       </c>
     </row>
     <row r="835">
@@ -51394,7 +51394,7 @@
         </is>
       </c>
       <c r="M835" s="2" t="n">
-        <v>3051.83</v>
+        <v>3011.18</v>
       </c>
     </row>
     <row r="836">
@@ -51455,7 +51455,7 @@
         </is>
       </c>
       <c r="M836" s="2" t="n">
-        <v>1986.85</v>
+        <v>1960.38</v>
       </c>
     </row>
     <row r="837">
@@ -51516,7 +51516,7 @@
         </is>
       </c>
       <c r="M837" s="2" t="n">
-        <v>11386.34</v>
+        <v>11234.67</v>
       </c>
     </row>
     <row r="838">
@@ -51577,7 +51577,7 @@
         </is>
       </c>
       <c r="M838" s="2" t="n">
-        <v>2089.81</v>
+        <v>2061.97</v>
       </c>
     </row>
     <row r="839">
@@ -51638,7 +51638,7 @@
         </is>
       </c>
       <c r="M839" s="2" t="n">
-        <v>6917.9</v>
+        <v>6825.75</v>
       </c>
     </row>
     <row r="840">
@@ -51699,7 +51699,7 @@
         </is>
       </c>
       <c r="M840" s="2" t="n">
-        <v>6733.9</v>
+        <v>6644.2</v>
       </c>
     </row>
     <row r="841">
@@ -51760,7 +51760,7 @@
         </is>
       </c>
       <c r="M841" s="2" t="n">
-        <v>1046.35</v>
+        <v>1032.42</v>
       </c>
     </row>
     <row r="842">
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="M842" s="2" t="n">
-        <v>895.08</v>
+        <v>883.16</v>
       </c>
     </row>
     <row r="843">
@@ -51882,7 +51882,7 @@
         </is>
       </c>
       <c r="M843" s="2" t="n">
-        <v>831.47</v>
+        <v>820.4</v>
       </c>
     </row>
     <row r="844">
@@ -51943,7 +51943,7 @@
         </is>
       </c>
       <c r="M844" s="2" t="n">
-        <v>44399.46</v>
+        <v>43808.05</v>
       </c>
     </row>
     <row r="845">
@@ -52004,7 +52004,7 @@
         </is>
       </c>
       <c r="M845" s="2" t="n">
-        <v>5641.34</v>
+        <v>5566.19</v>
       </c>
     </row>
     <row r="846">
@@ -52065,7 +52065,7 @@
         </is>
       </c>
       <c r="M846" s="2" t="n">
-        <v>9217.280000000001</v>
+        <v>9094.5</v>
       </c>
     </row>
     <row r="847">
@@ -52126,7 +52126,7 @@
         </is>
       </c>
       <c r="M847" s="2" t="n">
-        <v>2248.29</v>
+        <v>2218.34</v>
       </c>
     </row>
     <row r="848">
@@ -52187,7 +52187,7 @@
         </is>
       </c>
       <c r="M848" s="2" t="n">
-        <v>4625.99</v>
+        <v>4564.37</v>
       </c>
     </row>
     <row r="849">
@@ -52248,7 +52248,7 @@
         </is>
       </c>
       <c r="M849" s="2" t="n">
-        <v>6573.66</v>
+        <v>6486.1</v>
       </c>
     </row>
     <row r="850">
@@ -52309,7 +52309,7 @@
         </is>
       </c>
       <c r="M850" s="2" t="n">
-        <v>1582.55</v>
+        <v>1561.47</v>
       </c>
     </row>
     <row r="851">
@@ -52370,7 +52370,7 @@
         </is>
       </c>
       <c r="M851" s="2" t="n">
-        <v>3423.83</v>
+        <v>3378.22</v>
       </c>
     </row>
     <row r="852">
@@ -52431,7 +52431,7 @@
         </is>
       </c>
       <c r="M852" s="2" t="n">
-        <v>4772.75</v>
+        <v>4709.18</v>
       </c>
     </row>
     <row r="853">
@@ -52492,7 +52492,7 @@
         </is>
       </c>
       <c r="M853" s="2" t="n">
-        <v>2135.42</v>
+        <v>2106.97</v>
       </c>
     </row>
     <row r="854">
@@ -52553,7 +52553,7 @@
         </is>
       </c>
       <c r="M854" s="2" t="n">
-        <v>800.9</v>
+        <v>790.23</v>
       </c>
     </row>
     <row r="855">
@@ -52614,7 +52614,7 @@
         </is>
       </c>
       <c r="M855" s="2" t="n">
-        <v>1258.39</v>
+        <v>1241.62</v>
       </c>
     </row>
     <row r="856">
@@ -52675,7 +52675,7 @@
         </is>
       </c>
       <c r="M856" s="2" t="n">
-        <v>920.52</v>
+        <v>908.26</v>
       </c>
     </row>
     <row r="857">
@@ -52736,7 +52736,7 @@
         </is>
       </c>
       <c r="M857" s="2" t="n">
-        <v>3518.72</v>
+        <v>3471.85</v>
       </c>
     </row>
     <row r="858">
@@ -52797,7 +52797,7 @@
         </is>
       </c>
       <c r="M858" s="2" t="n">
-        <v>25323.18</v>
+        <v>24827.51</v>
       </c>
     </row>
     <row r="859">
@@ -52858,7 +52858,7 @@
         </is>
       </c>
       <c r="M859" s="2" t="n">
-        <v>5683.73</v>
+        <v>5572.48</v>
       </c>
     </row>
     <row r="860">
@@ -52919,7 +52919,7 @@
         </is>
       </c>
       <c r="M860" s="2" t="n">
-        <v>9531.129999999999</v>
+        <v>9344.57</v>
       </c>
     </row>
     <row r="861">
@@ -52980,7 +52980,7 @@
         </is>
       </c>
       <c r="M861" s="2" t="n">
-        <v>21174.06</v>
+        <v>20759.6</v>
       </c>
     </row>
     <row r="862">
@@ -53041,7 +53041,7 @@
         </is>
       </c>
       <c r="M862" s="2" t="n">
-        <v>6337.83</v>
+        <v>6213.78</v>
       </c>
     </row>
     <row r="863">
@@ -53102,7 +53102,7 @@
         </is>
       </c>
       <c r="M863" s="2" t="n">
-        <v>1530.95</v>
+        <v>1500.98</v>
       </c>
     </row>
     <row r="864">
@@ -53163,7 +53163,7 @@
         </is>
       </c>
       <c r="M864" s="2" t="n">
-        <v>5154.74</v>
+        <v>5053.84</v>
       </c>
     </row>
     <row r="865">
@@ -53224,7 +53224,7 @@
         </is>
       </c>
       <c r="M865" s="2" t="n">
-        <v>5388.29</v>
+        <v>5282.82</v>
       </c>
     </row>
     <row r="866">
@@ -53285,7 +53285,7 @@
         </is>
       </c>
       <c r="M866" s="2" t="n">
-        <v>5326.24</v>
+        <v>5221.99</v>
       </c>
     </row>
     <row r="867">
@@ -53346,7 +53346,7 @@
         </is>
       </c>
       <c r="M867" s="2" t="n">
-        <v>803.21</v>
+        <v>787.49</v>
       </c>
     </row>
     <row r="868">
@@ -53407,7 +53407,7 @@
         </is>
       </c>
       <c r="M868" s="2" t="n">
-        <v>2401.84</v>
+        <v>2354.82</v>
       </c>
     </row>
     <row r="869">
@@ -53468,7 +53468,7 @@
         </is>
       </c>
       <c r="M869" s="2" t="n">
-        <v>77590.78999999999</v>
+        <v>76072.05</v>
       </c>
     </row>
     <row r="870">
@@ -53529,7 +53529,7 @@
         </is>
       </c>
       <c r="M870" s="2" t="n">
-        <v>3759.79</v>
+        <v>3686.19</v>
       </c>
     </row>
     <row r="871">
@@ -53590,7 +53590,7 @@
         </is>
       </c>
       <c r="M871" s="2" t="n">
-        <v>3507.52</v>
+        <v>3438.86</v>
       </c>
     </row>
     <row r="872">
@@ -53651,7 +53651,7 @@
         </is>
       </c>
       <c r="M872" s="2" t="n">
-        <v>5993.57</v>
+        <v>5876.26</v>
       </c>
     </row>
     <row r="873">
@@ -53712,7 +53712,7 @@
         </is>
       </c>
       <c r="M873" s="2" t="n">
-        <v>4168.76</v>
+        <v>4087.16</v>
       </c>
     </row>
     <row r="874">
@@ -53773,7 +53773,7 @@
         </is>
       </c>
       <c r="M874" s="2" t="n">
-        <v>794.47</v>
+        <v>778.92</v>
       </c>
     </row>
     <row r="875">
@@ -53834,7 +53834,7 @@
         </is>
       </c>
       <c r="M875" s="2" t="n">
-        <v>2525.14</v>
+        <v>2475.71</v>
       </c>
     </row>
     <row r="876">
@@ -53895,7 +53895,7 @@
         </is>
       </c>
       <c r="M876" s="2" t="n">
-        <v>7266.71</v>
+        <v>7124.48</v>
       </c>
     </row>
     <row r="877">
@@ -53956,7 +53956,7 @@
         </is>
       </c>
       <c r="M877" s="2" t="n">
-        <v>5780.87</v>
+        <v>5667.71</v>
       </c>
     </row>
     <row r="878">
@@ -54017,7 +54017,7 @@
         </is>
       </c>
       <c r="M878" s="2" t="n">
-        <v>2742.55</v>
+        <v>2688.87</v>
       </c>
     </row>
     <row r="879">
@@ -54078,7 +54078,7 @@
         </is>
       </c>
       <c r="M879" s="2" t="n">
-        <v>1852.21</v>
+        <v>1815.96</v>
       </c>
     </row>
     <row r="880">
@@ -54139,7 +54139,7 @@
         </is>
       </c>
       <c r="M880" s="2" t="n">
-        <v>1657.23</v>
+        <v>1624.79</v>
       </c>
     </row>
     <row r="881">
@@ -54200,7 +54200,7 @@
         </is>
       </c>
       <c r="M881" s="2" t="n">
-        <v>1075.15</v>
+        <v>1054.11</v>
       </c>
     </row>
     <row r="882">
@@ -54261,7 +54261,7 @@
         </is>
       </c>
       <c r="M882" s="2" t="n">
-        <v>10007.73</v>
+        <v>9811.84</v>
       </c>
     </row>
     <row r="883">
@@ -54322,7 +54322,7 @@
         </is>
       </c>
       <c r="M883" s="2" t="n">
-        <v>2767.2</v>
+        <v>2713.03</v>
       </c>
     </row>
     <row r="884">
@@ -54383,7 +54383,7 @@
         </is>
       </c>
       <c r="M884" s="2" t="n">
-        <v>2515.25</v>
+        <v>2466.01</v>
       </c>
     </row>
     <row r="885">
@@ -54444,7 +54444,7 @@
         </is>
       </c>
       <c r="M885" s="2" t="n">
-        <v>2515.23</v>
+        <v>2465.99</v>
       </c>
     </row>
     <row r="886">
@@ -54505,7 +54505,7 @@
         </is>
       </c>
       <c r="M886" s="2" t="n">
-        <v>1848.01</v>
+        <v>1811.83</v>
       </c>
     </row>
     <row r="887">
@@ -54566,7 +54566,7 @@
         </is>
       </c>
       <c r="M887" s="2" t="n">
-        <v>4272.69</v>
+        <v>4189.06</v>
       </c>
     </row>
     <row r="888">
@@ -54627,7 +54627,7 @@
         </is>
       </c>
       <c r="M888" s="2" t="n">
-        <v>3844.12</v>
+        <v>3768.87</v>
       </c>
     </row>
     <row r="889">
@@ -54688,7 +54688,7 @@
         </is>
       </c>
       <c r="M889" s="2" t="n">
-        <v>1667.56</v>
+        <v>1634.92</v>
       </c>
     </row>
     <row r="890">
@@ -54749,7 +54749,7 @@
         </is>
       </c>
       <c r="M890" s="2" t="n">
-        <v>2949.43</v>
+        <v>2891.7</v>
       </c>
     </row>
     <row r="891">
@@ -54810,7 +54810,7 @@
         </is>
       </c>
       <c r="M891" s="2" t="n">
-        <v>9821.65</v>
+        <v>9629.4</v>
       </c>
     </row>
     <row r="892">
@@ -54871,7 +54871,7 @@
         </is>
       </c>
       <c r="M892" s="2" t="n">
-        <v>792.23</v>
+        <v>776.72</v>
       </c>
     </row>
     <row r="893">
@@ -54932,7 +54932,7 @@
         </is>
       </c>
       <c r="M893" s="2" t="n">
-        <v>1072.45</v>
+        <v>1051.46</v>
       </c>
     </row>
     <row r="894">
@@ -54993,7 +54993,7 @@
         </is>
       </c>
       <c r="M894" s="2" t="n">
-        <v>973.96</v>
+        <v>954.9</v>
       </c>
     </row>
     <row r="895">
@@ -55054,7 +55054,7 @@
         </is>
       </c>
       <c r="M895" s="2" t="n">
-        <v>2455.78</v>
+        <v>2407.71</v>
       </c>
     </row>
     <row r="896">
@@ -55115,7 +55115,7 @@
         </is>
       </c>
       <c r="M896" s="2" t="n">
-        <v>18264.41</v>
+        <v>17906.91</v>
       </c>
     </row>
     <row r="897">
@@ -55176,7 +55176,7 @@
         </is>
       </c>
       <c r="M897" s="2" t="n">
-        <v>3159.01</v>
+        <v>3097.18</v>
       </c>
     </row>
     <row r="898">
@@ -55237,7 +55237,7 @@
         </is>
       </c>
       <c r="M898" s="2" t="n">
-        <v>1655.02</v>
+        <v>1622.62</v>
       </c>
     </row>
     <row r="899">
@@ -55298,7 +55298,7 @@
         </is>
       </c>
       <c r="M899" s="2" t="n">
-        <v>2108.16</v>
+        <v>2066.9</v>
       </c>
     </row>
     <row r="900">
@@ -55359,7 +55359,7 @@
         </is>
       </c>
       <c r="M900" s="2" t="n">
-        <v>6356.89</v>
+        <v>6232.47</v>
       </c>
     </row>
     <row r="901">
@@ -55420,7 +55420,7 @@
         </is>
       </c>
       <c r="M901" s="2" t="n">
-        <v>1753.11</v>
+        <v>1718.8</v>
       </c>
     </row>
     <row r="902">
@@ -55481,7 +55481,7 @@
         </is>
       </c>
       <c r="M902" s="2" t="n">
-        <v>1626.26</v>
+        <v>1594.42</v>
       </c>
     </row>
     <row r="903">
@@ -55542,7 +55542,7 @@
         </is>
       </c>
       <c r="M903" s="2" t="n">
-        <v>16406.69</v>
+        <v>16085.55</v>
       </c>
     </row>
     <row r="904">
@@ -55603,7 +55603,7 @@
         </is>
       </c>
       <c r="M904" s="2" t="n">
-        <v>3202.99</v>
+        <v>3140.3</v>
       </c>
     </row>
     <row r="905">
@@ -55664,7 +55664,7 @@
         </is>
       </c>
       <c r="M905" s="2" t="n">
-        <v>1689.37</v>
+        <v>1656.3</v>
       </c>
     </row>
     <row r="906">
@@ -55725,7 +55725,7 @@
         </is>
       </c>
       <c r="M906" s="2" t="n">
-        <v>1144.31</v>
+        <v>1121.91</v>
       </c>
     </row>
     <row r="907">
@@ -55786,7 +55786,7 @@
         </is>
       </c>
       <c r="M907" s="2" t="n">
-        <v>2093.4</v>
+        <v>2052.43</v>
       </c>
     </row>
     <row r="908">
@@ -55847,7 +55847,7 @@
         </is>
       </c>
       <c r="M908" s="2" t="n">
-        <v>8807.26</v>
+        <v>8634.870000000001</v>
       </c>
     </row>
     <row r="909">
@@ -55908,7 +55908,7 @@
         </is>
       </c>
       <c r="M909" s="2" t="n">
-        <v>26816.91</v>
+        <v>26292</v>
       </c>
     </row>
     <row r="910">
@@ -55969,7 +55969,7 @@
         </is>
       </c>
       <c r="M910" s="2" t="n">
-        <v>3678.75</v>
+        <v>3606.74</v>
       </c>
     </row>
     <row r="911">
@@ -56030,7 +56030,7 @@
         </is>
       </c>
       <c r="M911" s="2" t="n">
-        <v>3621.7</v>
+        <v>3568.04</v>
       </c>
     </row>
     <row r="912">
@@ -56091,7 +56091,7 @@
         </is>
       </c>
       <c r="M912" s="2" t="n">
-        <v>798.13</v>
+        <v>786.3099999999999</v>
       </c>
     </row>
     <row r="913">
@@ -56152,7 +56152,7 @@
         </is>
       </c>
       <c r="M913" s="2" t="n">
-        <v>7999.07</v>
+        <v>7880.56</v>
       </c>
     </row>
     <row r="914">
@@ -56213,7 +56213,7 @@
         </is>
       </c>
       <c r="M914" s="2" t="n">
-        <v>1318.29</v>
+        <v>1298.76</v>
       </c>
     </row>
     <row r="915">
@@ -56274,7 +56274,7 @@
         </is>
       </c>
       <c r="M915" s="2" t="n">
-        <v>1327.98</v>
+        <v>1308.3</v>
       </c>
     </row>
     <row r="916">
@@ -56335,7 +56335,7 @@
         </is>
       </c>
       <c r="M916" s="2" t="n">
-        <v>4831.08</v>
+        <v>4759.51</v>
       </c>
     </row>
     <row r="917">
@@ -56396,7 +56396,7 @@
         </is>
       </c>
       <c r="M917" s="2" t="n">
-        <v>2350.73</v>
+        <v>2315.91</v>
       </c>
     </row>
     <row r="918">
@@ -56457,7 +56457,7 @@
         </is>
       </c>
       <c r="M918" s="2" t="n">
-        <v>7350.36</v>
+        <v>7241.46</v>
       </c>
     </row>
     <row r="919">
@@ -56518,7 +56518,7 @@
         </is>
       </c>
       <c r="M919" s="2" t="n">
-        <v>8435.790000000001</v>
+        <v>8310.809999999999</v>
       </c>
     </row>
     <row r="920">
@@ -56579,7 +56579,7 @@
         </is>
       </c>
       <c r="M920" s="2" t="n">
-        <v>1619.14</v>
+        <v>1595.15</v>
       </c>
     </row>
     <row r="921">
@@ -56640,7 +56640,7 @@
         </is>
       </c>
       <c r="M921" s="2" t="n">
-        <v>32267.56</v>
+        <v>31789.49</v>
       </c>
     </row>
     <row r="922">
@@ -56701,7 +56701,7 @@
         </is>
       </c>
       <c r="M922" s="2" t="n">
-        <v>2046.05</v>
+        <v>2015.73</v>
       </c>
     </row>
     <row r="923">
@@ -56762,7 +56762,7 @@
         </is>
       </c>
       <c r="M923" s="2" t="n">
-        <v>4110.51</v>
+        <v>4049.61</v>
       </c>
     </row>
     <row r="924">
@@ -56823,7 +56823,7 @@
         </is>
       </c>
       <c r="M924" s="2" t="n">
-        <v>7366.17</v>
+        <v>7257.03</v>
       </c>
     </row>
     <row r="925">
@@ -56884,7 +56884,7 @@
         </is>
       </c>
       <c r="M925" s="2" t="n">
-        <v>7795.12</v>
+        <v>7679.63</v>
       </c>
     </row>
     <row r="926">
@@ -56945,7 +56945,7 @@
         </is>
       </c>
       <c r="M926" s="2" t="n">
-        <v>3953.43</v>
+        <v>3894.85</v>
       </c>
     </row>
     <row r="927">
@@ -57006,7 +57006,7 @@
         </is>
       </c>
       <c r="M927" s="2" t="n">
-        <v>34858.63</v>
+        <v>34342.17</v>
       </c>
     </row>
     <row r="928">
@@ -57067,7 +57067,7 @@
         </is>
       </c>
       <c r="M928" s="2" t="n">
-        <v>2302.59</v>
+        <v>2268.47</v>
       </c>
     </row>
     <row r="929">
@@ -57128,7 +57128,7 @@
         </is>
       </c>
       <c r="M929" s="2" t="n">
-        <v>1498.39</v>
+        <v>1476.19</v>
       </c>
     </row>
     <row r="930">
@@ -57189,7 +57189,7 @@
         </is>
       </c>
       <c r="M930" s="2" t="n">
-        <v>3257.97</v>
+        <v>3209.71</v>
       </c>
     </row>
     <row r="931">
@@ -57250,7 +57250,7 @@
         </is>
       </c>
       <c r="M931" s="2" t="n">
-        <v>9254.68</v>
+        <v>9117.57</v>
       </c>
     </row>
     <row r="932">
@@ -57311,7 +57311,7 @@
         </is>
       </c>
       <c r="M932" s="2" t="n">
-        <v>39742.73</v>
+        <v>39153.9</v>
       </c>
     </row>
     <row r="933">
@@ -57372,7 +57372,7 @@
         </is>
       </c>
       <c r="M933" s="2" t="n">
-        <v>2622.26</v>
+        <v>2583.41</v>
       </c>
     </row>
     <row r="934">
@@ -57433,7 +57433,7 @@
         </is>
       </c>
       <c r="M934" s="2" t="n">
-        <v>2572.45</v>
+        <v>2534.33</v>
       </c>
     </row>
     <row r="935">
@@ -57494,7 +57494,7 @@
         </is>
       </c>
       <c r="M935" s="2" t="n">
-        <v>7005.93</v>
+        <v>6902.13</v>
       </c>
     </row>
     <row r="936">
@@ -57555,7 +57555,7 @@
         </is>
       </c>
       <c r="M936" s="2" t="n">
-        <v>793.09</v>
+        <v>781.34</v>
       </c>
     </row>
     <row r="937">
@@ -57616,7 +57616,7 @@
         </is>
       </c>
       <c r="M937" s="2" t="n">
-        <v>978.25</v>
+        <v>963.76</v>
       </c>
     </row>
     <row r="938">
@@ -57677,7 +57677,7 @@
         </is>
       </c>
       <c r="M938" s="2" t="n">
-        <v>17997.85</v>
+        <v>17731.2</v>
       </c>
     </row>
     <row r="939">
@@ -57738,7 +57738,7 @@
         </is>
       </c>
       <c r="M939" s="2" t="n">
-        <v>1563.85</v>
+        <v>1540.68</v>
       </c>
     </row>
     <row r="940">
@@ -57799,7 +57799,7 @@
         </is>
       </c>
       <c r="M940" s="2" t="n">
-        <v>1106.87</v>
+        <v>1090.47</v>
       </c>
     </row>
     <row r="941">
@@ -57860,7 +57860,7 @@
         </is>
       </c>
       <c r="M941" s="2" t="n">
-        <v>1421.45</v>
+        <v>1400.39</v>
       </c>
     </row>
     <row r="942">
@@ -57921,7 +57921,7 @@
         </is>
       </c>
       <c r="M942" s="2" t="n">
-        <v>1268.88</v>
+        <v>1250.08</v>
       </c>
     </row>
     <row r="943">
@@ -57982,7 +57982,7 @@
         </is>
       </c>
       <c r="M943" s="2" t="n">
-        <v>5132.18</v>
+        <v>5056.15</v>
       </c>
     </row>
     <row r="944">
@@ -58043,7 +58043,7 @@
         </is>
       </c>
       <c r="M944" s="2" t="n">
-        <v>2687.23</v>
+        <v>2647.41</v>
       </c>
     </row>
     <row r="945">
@@ -58104,7 +58104,7 @@
         </is>
       </c>
       <c r="M945" s="2" t="n">
-        <v>4701.95</v>
+        <v>4632.28</v>
       </c>
     </row>
     <row r="946">
@@ -58165,7 +58165,7 @@
         </is>
       </c>
       <c r="M946" s="2" t="n">
-        <v>2192.73</v>
+        <v>2160.24</v>
       </c>
     </row>
     <row r="947">
@@ -58226,7 +58226,7 @@
         </is>
       </c>
       <c r="M947" s="2" t="n">
-        <v>1237.31</v>
+        <v>1218.98</v>
       </c>
     </row>
     <row r="948">
@@ -58287,7 +58287,7 @@
         </is>
       </c>
       <c r="M948" s="2" t="n">
-        <v>4769</v>
+        <v>4698.34</v>
       </c>
     </row>
     <row r="949">
@@ -58348,7 +58348,7 @@
         </is>
       </c>
       <c r="M949" s="2" t="n">
-        <v>2003.92</v>
+        <v>1974.23</v>
       </c>
     </row>
     <row r="950">
@@ -58409,7 +58409,7 @@
         </is>
       </c>
       <c r="M950" s="2" t="n">
-        <v>7234.47</v>
+        <v>7127.28</v>
       </c>
     </row>
     <row r="951">
@@ -58470,7 +58470,7 @@
         </is>
       </c>
       <c r="M951" s="2" t="n">
-        <v>2753.36</v>
+        <v>2712.57</v>
       </c>
     </row>
     <row r="952">
@@ -58531,7 +58531,7 @@
         </is>
       </c>
       <c r="M952" s="2" t="n">
-        <v>4966.3</v>
+        <v>4892.72</v>
       </c>
     </row>
     <row r="953">
@@ -58592,7 +58592,7 @@
         </is>
       </c>
       <c r="M953" s="2" t="n">
-        <v>4227.5</v>
+        <v>4164.87</v>
       </c>
     </row>
     <row r="954">
@@ -58653,7 +58653,7 @@
         </is>
       </c>
       <c r="M954" s="2" t="n">
-        <v>988.11</v>
+        <v>973.47</v>
       </c>
     </row>
     <row r="955">
@@ -58714,7 +58714,7 @@
         </is>
       </c>
       <c r="M955" s="2" t="n">
-        <v>32419.9</v>
+        <v>31939.57</v>
       </c>
     </row>
     <row r="956">
@@ -58775,7 +58775,7 @@
         </is>
       </c>
       <c r="M956" s="2" t="n">
-        <v>992.27</v>
+        <v>977.5700000000001</v>
       </c>
     </row>
     <row r="957">
@@ -58836,7 +58836,7 @@
         </is>
       </c>
       <c r="M957" s="2" t="n">
-        <v>1073.74</v>
+        <v>1057.83</v>
       </c>
     </row>
     <row r="958">
@@ -58897,7 +58897,7 @@
         </is>
       </c>
       <c r="M958" s="2" t="n">
-        <v>3288.17</v>
+        <v>3239.45</v>
       </c>
     </row>
     <row r="959">
@@ -58958,7 +58958,7 @@
         </is>
       </c>
       <c r="M959" s="2" t="n">
-        <v>1828.93</v>
+        <v>1801.83</v>
       </c>
     </row>
     <row r="960">
@@ -59019,7 +59019,7 @@
         </is>
       </c>
       <c r="M960" s="2" t="n">
-        <v>803.39</v>
+        <v>786.88</v>
       </c>
     </row>
     <row r="961">
@@ -59080,7 +59080,7 @@
         </is>
       </c>
       <c r="M961" s="2" t="n">
-        <v>2161.22</v>
+        <v>2116.81</v>
       </c>
     </row>
     <row r="962">
@@ -59141,7 +59141,7 @@
         </is>
       </c>
       <c r="M962" s="2" t="n">
-        <v>1908.46</v>
+        <v>1869.24</v>
       </c>
     </row>
     <row r="963">
@@ -59202,7 +59202,7 @@
         </is>
       </c>
       <c r="M963" s="2" t="n">
-        <v>2484.21</v>
+        <v>2433.16</v>
       </c>
     </row>
     <row r="964">
@@ -59263,7 +59263,7 @@
         </is>
       </c>
       <c r="M964" s="2" t="n">
-        <v>943.99</v>
+        <v>924.59</v>
       </c>
     </row>
     <row r="965">
@@ -59324,7 +59324,7 @@
         </is>
       </c>
       <c r="M965" s="2" t="n">
-        <v>7153.82</v>
+        <v>7006.8</v>
       </c>
     </row>
     <row r="966">
@@ -59385,7 +59385,7 @@
         </is>
       </c>
       <c r="M966" s="2" t="n">
-        <v>3206.13</v>
+        <v>3140.24</v>
       </c>
     </row>
     <row r="967">
@@ -59446,7 +59446,7 @@
         </is>
       </c>
       <c r="M967" s="2" t="n">
-        <v>2959.68</v>
+        <v>2898.86</v>
       </c>
     </row>
     <row r="968">
@@ -59507,7 +59507,7 @@
         </is>
       </c>
       <c r="M968" s="2" t="n">
-        <v>3219.12</v>
+        <v>3152.97</v>
       </c>
     </row>
     <row r="969">
@@ -59568,7 +59568,7 @@
         </is>
       </c>
       <c r="M969" s="2" t="n">
-        <v>6027.05</v>
+        <v>5903.18</v>
       </c>
     </row>
     <row r="970">
@@ -59629,7 +59629,7 @@
         </is>
       </c>
       <c r="M970" s="2" t="n">
-        <v>5116.24</v>
+        <v>5011.09</v>
       </c>
     </row>
     <row r="971">
@@ -59690,7 +59690,7 @@
         </is>
       </c>
       <c r="M971" s="2" t="n">
-        <v>1278.77</v>
+        <v>1252.49</v>
       </c>
     </row>
     <row r="972">
@@ -59751,7 +59751,7 @@
         </is>
       </c>
       <c r="M972" s="2" t="n">
-        <v>979.23</v>
+        <v>959.11</v>
       </c>
     </row>
     <row r="973">
@@ -59812,7 +59812,7 @@
         </is>
       </c>
       <c r="M973" s="2" t="n">
-        <v>9973.25</v>
+        <v>9768.280000000001</v>
       </c>
     </row>
     <row r="974">
@@ -59873,7 +59873,7 @@
         </is>
       </c>
       <c r="M974" s="2" t="n">
-        <v>1867.1</v>
+        <v>1828.73</v>
       </c>
     </row>
     <row r="975">
@@ -59934,7 +59934,7 @@
         </is>
       </c>
       <c r="M975" s="2" t="n">
-        <v>1151.83</v>
+        <v>1128.16</v>
       </c>
     </row>
     <row r="976">
@@ -59995,7 +59995,7 @@
         </is>
       </c>
       <c r="M976" s="2" t="n">
-        <v>4735.98</v>
+        <v>4638.64</v>
       </c>
     </row>
     <row r="977">
@@ -60056,7 +60056,7 @@
         </is>
       </c>
       <c r="M977" s="2" t="n">
-        <v>1712.36</v>
+        <v>1677.17</v>
       </c>
     </row>
     <row r="978">
@@ -60117,7 +60117,7 @@
         </is>
       </c>
       <c r="M978" s="2" t="n">
-        <v>1971.21</v>
+        <v>1930.7</v>
       </c>
     </row>
     <row r="979">
@@ -60178,7 +60178,7 @@
         </is>
       </c>
       <c r="M979" s="2" t="n">
-        <v>1308.05</v>
+        <v>1281.17</v>
       </c>
     </row>
     <row r="980">
@@ -60239,7 +60239,7 @@
         </is>
       </c>
       <c r="M980" s="2" t="n">
-        <v>2666.67</v>
+        <v>2611.87</v>
       </c>
     </row>
     <row r="981">
@@ -60300,7 +60300,7 @@
         </is>
       </c>
       <c r="M981" s="2" t="n">
-        <v>857.76</v>
+        <v>840.13</v>
       </c>
     </row>
     <row r="982">
@@ -60361,7 +60361,7 @@
         </is>
       </c>
       <c r="M982" s="2" t="n">
-        <v>1335.53</v>
+        <v>1308.08</v>
       </c>
     </row>
     <row r="983">
@@ -60422,7 +60422,7 @@
         </is>
       </c>
       <c r="M983" s="2" t="n">
-        <v>2135.68</v>
+        <v>2091.79</v>
       </c>
     </row>
     <row r="984">
@@ -60483,7 +60483,7 @@
         </is>
       </c>
       <c r="M984" s="2" t="n">
-        <v>4883.3</v>
+        <v>4782.94</v>
       </c>
     </row>
     <row r="985">
@@ -60544,7 +60544,7 @@
         </is>
       </c>
       <c r="M985" s="2" t="n">
-        <v>4484.44</v>
+        <v>4392.27</v>
       </c>
     </row>
     <row r="986">
@@ -60605,7 +60605,7 @@
         </is>
       </c>
       <c r="M986" s="2" t="n">
-        <v>4734.26</v>
+        <v>4636.97</v>
       </c>
     </row>
     <row r="987">
@@ -60666,7 +60666,7 @@
         </is>
       </c>
       <c r="M987" s="2" t="n">
-        <v>4282.74</v>
+        <v>4194.72</v>
       </c>
     </row>
     <row r="988">
@@ -60727,7 +60727,7 @@
         </is>
       </c>
       <c r="M988" s="2" t="n">
-        <v>4598.61</v>
+        <v>4504.1</v>
       </c>
     </row>
     <row r="989">
@@ -60788,7 +60788,7 @@
         </is>
       </c>
       <c r="M989" s="2" t="n">
-        <v>1716.08</v>
+        <v>1680.81</v>
       </c>
     </row>
     <row r="990">
@@ -60849,7 +60849,7 @@
         </is>
       </c>
       <c r="M990" s="2" t="n">
-        <v>3320.03</v>
+        <v>3251.8</v>
       </c>
     </row>
     <row r="991">
@@ -60910,7 +60910,7 @@
         </is>
       </c>
       <c r="M991" s="2" t="n">
-        <v>1182.77</v>
+        <v>1158.46</v>
       </c>
     </row>
     <row r="992">
@@ -60971,7 +60971,7 @@
         </is>
       </c>
       <c r="M992" s="2" t="n">
-        <v>3990.8</v>
+        <v>3908.78</v>
       </c>
     </row>
     <row r="993">
@@ -61032,7 +61032,7 @@
         </is>
       </c>
       <c r="M993" s="2" t="n">
-        <v>8750.719999999999</v>
+        <v>8570.879999999999</v>
       </c>
     </row>
     <row r="994">
@@ -61093,7 +61093,7 @@
         </is>
       </c>
       <c r="M994" s="2" t="n">
-        <v>2544.8</v>
+        <v>2492.5</v>
       </c>
     </row>
     <row r="995">
@@ -61154,7 +61154,7 @@
         </is>
       </c>
       <c r="M995" s="2" t="n">
-        <v>2529.94</v>
+        <v>2477.95</v>
       </c>
     </row>
     <row r="996">
@@ -61215,7 +61215,7 @@
         </is>
       </c>
       <c r="M996" s="2" t="n">
-        <v>2290.24</v>
+        <v>2243.17</v>
       </c>
     </row>
     <row r="997">
@@ -61276,7 +61276,7 @@
         </is>
       </c>
       <c r="M997" s="2" t="n">
-        <v>1257.71</v>
+        <v>1231.86</v>
       </c>
     </row>
     <row r="998">
@@ -61337,7 +61337,7 @@
         </is>
       </c>
       <c r="M998" s="2" t="n">
-        <v>1649.78</v>
+        <v>1615.87</v>
       </c>
     </row>
     <row r="999">
@@ -61398,7 +61398,7 @@
         </is>
       </c>
       <c r="M999" s="2" t="n">
-        <v>5457.5</v>
+        <v>5345.34</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/jun-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/jun-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jun-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jun-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6359,7 +6359,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6592,7 +6592,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9642,7 +9642,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -14217,7 +14217,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14522,7 +14522,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -14583,7 +14583,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14949,7 +14949,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -15742,7 +15742,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -16108,7 +16108,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16535,7 +16535,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -17023,7 +17023,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -17206,7 +17206,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17389,7 +17389,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -17511,7 +17511,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -17694,7 +17694,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -17755,7 +17755,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -18304,7 +18304,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -18487,7 +18487,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -18670,7 +18670,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -18731,7 +18731,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -18792,7 +18792,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -19341,7 +19341,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -20988,7 +20988,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -21171,7 +21171,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -22025,7 +22025,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -22330,7 +22330,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -22391,7 +22391,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -22940,7 +22940,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -23794,7 +23794,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -24343,7 +24343,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -24953,7 +24953,7 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
@@ -25075,7 +25075,7 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
@@ -25136,7 +25136,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -25746,7 +25746,7 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
@@ -26356,7 +26356,7 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
@@ -26600,7 +26600,7 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
@@ -27393,7 +27393,7 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -27637,7 +27637,7 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -27698,7 +27698,7 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -27942,7 +27942,7 @@
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
@@ -30504,7 +30504,7 @@
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
@@ -30687,7 +30687,7 @@
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -31602,7 +31602,7 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -31663,7 +31663,7 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
@@ -31846,7 +31846,7 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -32578,7 +32578,7 @@
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
@@ -35262,7 +35262,7 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
@@ -35384,7 +35384,7 @@
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
@@ -36055,7 +36055,7 @@
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
@@ -36543,7 +36543,7 @@
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I592" t="inlineStr">
@@ -36909,7 +36909,7 @@
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
@@ -38312,7 +38312,7 @@
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I621" t="inlineStr">
@@ -38983,7 +38983,7 @@
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I632" t="inlineStr">
@@ -39242,7 +39242,7 @@
       </c>
       <c r="K636" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L636" t="inlineStr">
@@ -39963,7 +39963,7 @@
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I648" t="inlineStr">
@@ -40756,7 +40756,7 @@
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I661" t="inlineStr">
@@ -40878,7 +40878,7 @@
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I663" t="inlineStr">
@@ -40939,7 +40939,7 @@
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I664" t="inlineStr">
@@ -41244,7 +41244,7 @@
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
@@ -41366,7 +41366,7 @@
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
@@ -42220,7 +42220,7 @@
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
@@ -42952,7 +42952,7 @@
       </c>
       <c r="H697" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I697" t="inlineStr">
@@ -43013,7 +43013,7 @@
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I698" t="inlineStr">
@@ -43196,7 +43196,7 @@
       </c>
       <c r="H701" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I701" t="inlineStr">
@@ -43318,7 +43318,7 @@
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I703" t="inlineStr">
@@ -43501,7 +43501,7 @@
       </c>
       <c r="H706" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I706" t="inlineStr">
@@ -44477,7 +44477,7 @@
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I722" t="inlineStr">
@@ -45026,7 +45026,7 @@
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I731" t="inlineStr">
@@ -45270,7 +45270,7 @@
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I735" t="inlineStr">
@@ -45331,7 +45331,7 @@
       </c>
       <c r="H736" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I736" t="inlineStr">
@@ -45392,7 +45392,7 @@
       </c>
       <c r="H737" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I737" t="inlineStr">
@@ -45453,7 +45453,7 @@
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I738" t="inlineStr">
@@ -45697,7 +45697,7 @@
       </c>
       <c r="H742" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I742" t="inlineStr">
@@ -46185,7 +46185,7 @@
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I750" t="inlineStr">
@@ -46307,7 +46307,7 @@
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I752" t="inlineStr">
@@ -46551,7 +46551,7 @@
       </c>
       <c r="H756" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I756" t="inlineStr">
@@ -47161,7 +47161,7 @@
       </c>
       <c r="H766" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I766" t="inlineStr">
@@ -47222,7 +47222,7 @@
       </c>
       <c r="H767" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I767" t="inlineStr">
@@ -47405,7 +47405,7 @@
       </c>
       <c r="H770" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I770" t="inlineStr">
@@ -47710,7 +47710,7 @@
       </c>
       <c r="H775" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I775" t="inlineStr">
@@ -47771,7 +47771,7 @@
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I776" t="inlineStr">
@@ -47832,7 +47832,7 @@
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I777" t="inlineStr">
@@ -48808,7 +48808,7 @@
       </c>
       <c r="H793" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I793" t="inlineStr">
@@ -48991,7 +48991,7 @@
       </c>
       <c r="H796" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I796" t="inlineStr">
@@ -49418,7 +49418,7 @@
       </c>
       <c r="H803" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I803" t="inlineStr">
@@ -49845,7 +49845,7 @@
       </c>
       <c r="H810" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I810" t="inlineStr">
@@ -50028,7 +50028,7 @@
       </c>
       <c r="H813" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I813" t="inlineStr">
@@ -50714,7 +50714,7 @@
       </c>
       <c r="K824" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="L824" t="inlineStr">
@@ -51069,7 +51069,7 @@
       </c>
       <c r="H830" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I830" t="inlineStr">
@@ -51923,7 +51923,7 @@
       </c>
       <c r="H844" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I844" t="inlineStr">
@@ -52594,7 +52594,7 @@
       </c>
       <c r="H855" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I855" t="inlineStr">
@@ -52838,7 +52838,7 @@
       </c>
       <c r="H859" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I859" t="inlineStr">
@@ -52899,7 +52899,7 @@
       </c>
       <c r="H860" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I860" t="inlineStr">
@@ -54241,7 +54241,7 @@
       </c>
       <c r="H882" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I882" t="inlineStr">
@@ -54302,7 +54302,7 @@
       </c>
       <c r="H883" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I883" t="inlineStr">
@@ -54485,7 +54485,7 @@
       </c>
       <c r="H886" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I886" t="inlineStr">
@@ -54607,7 +54607,7 @@
       </c>
       <c r="H888" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I888" t="inlineStr">
@@ -54668,7 +54668,7 @@
       </c>
       <c r="H889" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I889" t="inlineStr">
@@ -54790,7 +54790,7 @@
       </c>
       <c r="H891" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I891" t="inlineStr">
@@ -55034,7 +55034,7 @@
       </c>
       <c r="H895" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I895" t="inlineStr">
@@ -55156,7 +55156,7 @@
       </c>
       <c r="H897" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I897" t="inlineStr">
@@ -55278,7 +55278,7 @@
       </c>
       <c r="H899" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I899" t="inlineStr">
@@ -55644,7 +55644,7 @@
       </c>
       <c r="H905" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I905" t="inlineStr">
@@ -55705,7 +55705,7 @@
       </c>
       <c r="H906" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I906" t="inlineStr">
@@ -57779,7 +57779,7 @@
       </c>
       <c r="H940" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I940" t="inlineStr">
@@ -58450,7 +58450,7 @@
       </c>
       <c r="H951" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I951" t="inlineStr">
@@ -59304,7 +59304,7 @@
       </c>
       <c r="H965" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I965" t="inlineStr">
@@ -59426,7 +59426,7 @@
       </c>
       <c r="H967" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I967" t="inlineStr">
@@ -59487,7 +59487,7 @@
       </c>
       <c r="H968" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I968" t="inlineStr">
@@ -59731,7 +59731,7 @@
       </c>
       <c r="H972" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I972" t="inlineStr">
@@ -59853,7 +59853,7 @@
       </c>
       <c r="H974" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I974" t="inlineStr">
@@ -60951,7 +60951,7 @@
       </c>
       <c r="H992" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I992" t="inlineStr">
@@ -61012,7 +61012,7 @@
       </c>
       <c r="H993" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I993" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/jun-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/jun-2026.xlsx
@@ -562,7 +562,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +883,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +948,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1013,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1078,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1143,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1208,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1273,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1338,11 @@
           <t>78.061.716-0</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1403,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1468,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1533,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1598,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1663,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1728,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1793,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1858,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2045,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2110,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2175,11 @@
           <t>76.905.483-9</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2240,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2366,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2431,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2618,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2683,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2748,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2813,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2939,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3004,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3130,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3195,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3260,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3386,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3573,11 @@
           <t>78.199.695-5</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3638,11 @@
           <t>76.817.360-5</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3703,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3768,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3833,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3898,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4085,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4150,11 @@
           <t>77.649.678-2</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4215,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4280,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4345,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4471,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4719,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4906,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4971,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5036,11 @@
           <t>77.505.828-5</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5101,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5166,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5231,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5296,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5361,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5426,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5491,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5556,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5621,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5686,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5751,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5816,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5881,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6007,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6133,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6198,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6263,11 @@
           <t>76.539.061-3</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6328,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6454,11 @@
           <t>77.577.274-3</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6519,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6584,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6422,7 +6714,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6544,7 +6840,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6666,7 +6966,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6849,7 +7153,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6910,7 +7218,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6971,7 +7283,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7032,7 +7348,11 @@
           <t>78.203.286-0</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7093,7 +7413,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7154,7 +7478,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7215,7 +7543,11 @@
           <t>78.199.695-5</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7276,7 +7608,11 @@
           <t>78.199.695-5</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7398,7 +7734,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7459,7 +7799,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7520,7 +7864,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7703,7 +8051,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7825,7 +8177,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7886,7 +8242,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7947,7 +8307,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8008,7 +8372,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8069,7 +8437,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8130,7 +8502,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8191,7 +8567,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8374,7 +8754,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8435,7 +8819,11 @@
           <t>76.539.061-3</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8496,7 +8884,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8557,7 +8949,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8618,7 +9014,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8679,7 +9079,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8801,7 +9205,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8862,7 +9270,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8923,7 +9335,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9167,7 +9583,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9289,7 +9709,11 @@
           <t>76.817.360-5</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9350,7 +9774,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9411,7 +9839,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9472,7 +9904,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9655,7 +10091,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9716,7 +10156,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9899,7 +10343,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10021,7 +10469,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10082,7 +10534,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10204,7 +10660,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10265,7 +10725,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10326,7 +10790,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10387,7 +10855,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10448,7 +10920,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10509,7 +10985,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10570,7 +11050,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10631,7 +11115,11 @@
           <t>76.817.360-5</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10692,7 +11180,11 @@
           <t>77.577.274-3</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10753,7 +11245,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10875,7 +11371,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10936,7 +11436,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11119,7 +11623,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11180,7 +11688,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11241,7 +11753,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11607,7 +12123,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11668,7 +12188,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11790,7 +12314,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11912,7 +12440,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11973,7 +12505,11 @@
           <t>19.260.495-8</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12034,7 +12570,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12156,7 +12696,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12217,7 +12761,11 @@
           <t>77.581.865-4</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12400,7 +12948,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12583,7 +13135,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12705,7 +13261,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12766,7 +13326,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12827,7 +13391,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13010,7 +13578,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13071,7 +13643,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13193,7 +13769,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13254,7 +13834,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13315,7 +13899,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13376,7 +13964,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13437,7 +14029,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13498,7 +14094,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13620,7 +14220,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13681,7 +14285,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13803,7 +14411,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13986,7 +14598,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14108,7 +14724,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14169,7 +14789,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14230,7 +14854,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14352,7 +14980,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14535,7 +15167,11 @@
           <t>77.581.865-4</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14596,7 +15232,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14657,7 +15297,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14718,7 +15362,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14779,7 +15427,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14840,7 +15492,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14962,7 +15618,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15206,7 +15866,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15267,7 +15931,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15328,7 +15996,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15389,7 +16061,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15633,7 +16309,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15694,7 +16374,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15816,7 +16500,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15877,7 +16565,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15999,7 +16691,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16121,7 +16817,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16243,7 +16943,11 @@
           <t>78.201.425-0</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16304,7 +17008,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16365,7 +17073,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16426,7 +17138,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16548,7 +17264,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16670,7 +17390,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16792,7 +17516,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16853,7 +17581,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16914,7 +17646,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17036,7 +17772,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17097,7 +17837,11 @@
           <t>77.649.678-2</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17158,7 +17902,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17219,7 +17967,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17280,7 +18032,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17341,7 +18097,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17585,7 +18345,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17646,7 +18410,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17707,7 +18475,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17768,7 +18540,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17890,7 +18666,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17951,7 +18731,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18256,7 +19040,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18317,7 +19105,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18500,7 +19292,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18561,7 +19357,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18622,7 +19422,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18683,7 +19487,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18744,7 +19552,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18805,7 +19617,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18866,7 +19682,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18927,7 +19747,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18988,7 +19812,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19171,7 +19999,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19232,7 +20064,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19293,7 +20129,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19354,7 +20194,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19415,7 +20259,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19598,7 +20446,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19659,7 +20511,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19781,7 +20637,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19964,7 +20824,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20208,7 +21072,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20391,7 +21259,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20513,7 +21385,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20574,7 +21450,11 @@
           <t>77.743.864-6</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20635,7 +21515,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20696,7 +21580,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20757,7 +21645,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20879,7 +21771,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21001,7 +21897,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21062,7 +21962,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21306,7 +22210,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21367,7 +22275,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21428,7 +22340,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21489,7 +22405,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21550,7 +22470,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21672,7 +22596,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21733,7 +22661,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21794,7 +22726,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21977,7 +22913,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22038,7 +22978,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22099,7 +23043,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22221,7 +23169,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22404,7 +23356,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22465,7 +23421,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22648,7 +23608,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22709,7 +23673,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22770,7 +23738,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22892,7 +23864,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22953,7 +23929,11 @@
           <t>77.529.681-K</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23014,7 +23994,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23075,7 +24059,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23136,7 +24124,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23197,7 +24189,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23807,7 +24803,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23990,7 +24990,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24051,7 +25055,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24112,7 +25120,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24173,7 +25185,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24234,7 +25250,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24417,7 +25437,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24478,7 +25502,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24539,7 +25567,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24600,7 +25632,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24661,7 +25697,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24783,7 +25823,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24844,7 +25888,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24905,7 +25953,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25027,7 +26079,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25088,7 +26144,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25149,7 +26209,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25332,7 +26396,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25393,7 +26461,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25454,7 +26526,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25515,7 +26591,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25576,7 +26656,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25637,7 +26721,11 @@
           <t>78.199.695-5</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25942,7 +27030,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26003,7 +27095,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26064,7 +27160,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26125,7 +27225,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26186,7 +27290,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26247,7 +27355,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26369,7 +27481,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26430,7 +27546,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26552,7 +27672,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26613,7 +27737,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26674,7 +27802,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26735,7 +27867,11 @@
           <t>76.525.922-3</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26796,7 +27932,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26857,7 +27997,11 @@
           <t>78.076.237-3</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26979,7 +28123,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27040,7 +28188,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27101,7 +28253,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27223,7 +28379,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27284,7 +28444,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27345,7 +28509,11 @@
           <t>77.935.401-6</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27406,7 +28574,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27467,7 +28639,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27528,7 +28704,11 @@
           <t>78.199.695-5</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27589,7 +28769,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27650,7 +28834,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27711,7 +28899,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27772,7 +28964,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27833,7 +29029,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27894,7 +29094,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27955,7 +29159,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28016,7 +29224,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28077,7 +29289,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28138,7 +29354,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28199,7 +29419,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28260,7 +29484,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28382,7 +29610,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28443,7 +29675,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28565,7 +29801,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28687,7 +29927,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28809,7 +30053,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28870,7 +30118,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28931,7 +30183,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29114,7 +30370,11 @@
           <t>77.743.864-6</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29175,7 +30435,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29236,7 +30500,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29419,7 +30687,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29480,7 +30752,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29541,7 +30817,11 @@
           <t>77.037.031-0</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29602,7 +30882,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29663,7 +30947,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29724,7 +31012,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29785,7 +31077,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L481" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29907,7 +31203,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30029,7 +31329,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30090,7 +31394,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30151,7 +31459,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30212,7 +31524,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30334,7 +31650,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30395,7 +31715,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30456,7 +31780,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30517,7 +31845,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30578,7 +31910,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30639,7 +31975,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30822,7 +32162,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30944,7 +32288,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31005,7 +32353,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31127,7 +32479,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31188,7 +32544,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31310,7 +32670,11 @@
           <t>77.934.122-4</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31371,7 +32735,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31554,7 +32922,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31615,7 +32987,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31676,7 +33052,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31737,7 +33117,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31798,7 +33182,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31981,7 +33369,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32103,7 +33495,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32164,7 +33560,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32225,7 +33625,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32286,7 +33690,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32347,7 +33755,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32408,7 +33820,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L524" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32469,7 +33885,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32530,7 +33950,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32591,7 +34015,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32652,7 +34080,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32713,7 +34145,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32835,7 +34271,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33018,7 +34458,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33201,7 +34645,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33262,7 +34710,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33384,7 +34836,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L540" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33445,7 +34901,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33567,7 +35027,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33628,7 +35092,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33689,7 +35157,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33750,7 +35222,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33811,7 +35287,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L547" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33872,7 +35352,11 @@
           <t>77.935.401-6</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L548" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33994,7 +35478,11 @@
           <t>76.539.061-3</t>
         </is>
       </c>
-      <c r="K550" t="inlineStr"/>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L550" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34116,7 +35604,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34238,7 +35730,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L554" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34299,7 +35795,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34360,7 +35860,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K556" t="inlineStr"/>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L556" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34421,7 +35925,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34543,7 +36051,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34604,7 +36116,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L560" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34665,7 +36181,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34787,7 +36307,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34848,7 +36372,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34970,7 +36498,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L566" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35031,7 +36563,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L567" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35153,7 +36689,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K569" t="inlineStr"/>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L569" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35275,7 +36815,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35397,7 +36941,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr"/>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L573" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35458,7 +37006,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L574" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35519,7 +37071,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr"/>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L575" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35580,7 +37136,11 @@
           <t>76.539.061-3</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35641,7 +37201,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35824,7 +37388,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L580" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35885,7 +37453,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L581" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36007,7 +37579,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L583" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36068,7 +37644,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36129,7 +37709,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L585" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36312,7 +37896,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36373,7 +37961,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36434,7 +38026,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36617,7 +38213,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K593" t="inlineStr"/>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L593" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36678,7 +38278,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr"/>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L594" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36739,7 +38343,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr"/>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L595" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36800,7 +38408,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K596" t="inlineStr"/>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L596" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36861,7 +38473,11 @@
           <t>76.525.922-3</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36983,7 +38599,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L599" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37105,7 +38725,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L601" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37166,7 +38790,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L602" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37227,7 +38855,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37288,7 +38920,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37349,7 +38985,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr"/>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L605" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37410,7 +39050,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K606" t="inlineStr"/>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L606" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37593,7 +39237,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr"/>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L609" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37654,7 +39302,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L610" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37715,7 +39367,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K611" t="inlineStr"/>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L611" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37776,7 +39432,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K612" t="inlineStr"/>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L612" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37959,7 +39619,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K615" t="inlineStr"/>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L615" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38020,7 +39684,11 @@
           <t>77.786.423-8</t>
         </is>
       </c>
-      <c r="K616" t="inlineStr"/>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L616" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38142,7 +39810,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38386,7 +40058,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L622" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38447,7 +40123,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K623" t="inlineStr"/>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L623" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38508,7 +40188,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L624" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38569,7 +40253,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L625" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38691,7 +40379,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K627" t="inlineStr"/>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L627" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38752,7 +40444,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K628" t="inlineStr"/>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L628" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38813,7 +40509,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K629" t="inlineStr"/>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L629" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38874,7 +40574,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K630" t="inlineStr"/>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L630" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38935,7 +40639,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K631" t="inlineStr"/>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L631" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38996,7 +40704,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr"/>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L632" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39057,7 +40769,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr"/>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L633" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39179,7 +40895,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K635" t="inlineStr"/>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L635" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39427,7 +41147,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K639" t="inlineStr"/>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L639" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39549,7 +41273,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L641" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39610,7 +41338,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K642" t="inlineStr"/>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L642" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39671,7 +41403,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L643" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39732,7 +41468,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K644" t="inlineStr"/>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L644" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39915,7 +41655,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K647" t="inlineStr"/>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L647" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39976,7 +41720,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr"/>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L648" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40037,7 +41785,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K649" t="inlineStr"/>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L649" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40342,7 +42094,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K654" t="inlineStr"/>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L654" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40525,7 +42281,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K657" t="inlineStr"/>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L657" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40586,7 +42346,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K658" t="inlineStr"/>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L658" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40647,7 +42411,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K659" t="inlineStr"/>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L659" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40708,7 +42476,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K660" t="inlineStr"/>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L660" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40769,7 +42541,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K661" t="inlineStr"/>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L661" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40830,7 +42606,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K662" t="inlineStr"/>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L662" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40891,7 +42671,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K663" t="inlineStr"/>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L663" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40952,7 +42736,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr"/>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L664" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41013,7 +42801,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr"/>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L665" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41074,7 +42866,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K666" t="inlineStr"/>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L666" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41135,7 +42931,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K667" t="inlineStr"/>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L667" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41196,7 +42996,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K668" t="inlineStr"/>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L668" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41257,7 +43061,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K669" t="inlineStr"/>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L669" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41379,7 +43187,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K671" t="inlineStr"/>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L671" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41440,7 +43252,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K672" t="inlineStr"/>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L672" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41501,7 +43317,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K673" t="inlineStr"/>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L673" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41562,7 +43382,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K674" t="inlineStr"/>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L674" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41623,7 +43447,11 @@
           <t>78.199.695-5</t>
         </is>
       </c>
-      <c r="K675" t="inlineStr"/>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L675" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41745,7 +43573,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K677" t="inlineStr"/>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L677" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41989,7 +43821,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K681" t="inlineStr"/>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L681" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42172,7 +44008,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K684" t="inlineStr"/>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L684" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42233,7 +44073,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K685" t="inlineStr"/>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L685" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42294,7 +44138,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K686" t="inlineStr"/>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L686" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42355,7 +44203,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K687" t="inlineStr"/>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L687" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42416,7 +44268,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K688" t="inlineStr"/>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L688" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42477,7 +44333,11 @@
           <t>77.935.401-6</t>
         </is>
       </c>
-      <c r="K689" t="inlineStr"/>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L689" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42538,7 +44398,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K690" t="inlineStr"/>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L690" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42721,7 +44585,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K693" t="inlineStr"/>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L693" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42843,7 +44711,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K695" t="inlineStr"/>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L695" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43026,7 +44898,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K698" t="inlineStr"/>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L698" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43087,7 +44963,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K699" t="inlineStr"/>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L699" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43148,7 +45028,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K700" t="inlineStr"/>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L700" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43270,7 +45154,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K702" t="inlineStr"/>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L702" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43331,7 +45219,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K703" t="inlineStr"/>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L703" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43392,7 +45284,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K704" t="inlineStr"/>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L704" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43575,7 +45471,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K707" t="inlineStr"/>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L707" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43636,7 +45536,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K708" t="inlineStr"/>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L708" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43697,7 +45601,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K709" t="inlineStr"/>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L709" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43758,7 +45666,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K710" t="inlineStr"/>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L710" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43941,7 +45853,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K713" t="inlineStr"/>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L713" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44002,7 +45918,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K714" t="inlineStr"/>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L714" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44063,7 +45983,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K715" t="inlineStr"/>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L715" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44185,7 +46109,11 @@
           <t>77.623.039-1</t>
         </is>
       </c>
-      <c r="K717" t="inlineStr"/>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L717" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44246,7 +46174,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K718" t="inlineStr"/>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L718" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44307,7 +46239,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K719" t="inlineStr"/>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L719" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44368,7 +46304,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K720" t="inlineStr"/>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L720" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44429,7 +46369,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K721" t="inlineStr"/>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L721" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44490,7 +46434,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K722" t="inlineStr"/>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L722" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44612,7 +46560,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K724" t="inlineStr"/>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L724" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44673,7 +46625,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K725" t="inlineStr"/>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L725" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44734,7 +46690,11 @@
           <t>78.199.695-5</t>
         </is>
       </c>
-      <c r="K726" t="inlineStr"/>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L726" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44795,7 +46755,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K727" t="inlineStr"/>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L727" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44856,7 +46820,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K728" t="inlineStr"/>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L728" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44917,7 +46885,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K729" t="inlineStr"/>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L729" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44978,7 +46950,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K730" t="inlineStr"/>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L730" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45100,7 +47076,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K732" t="inlineStr"/>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L732" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45161,7 +47141,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K733" t="inlineStr"/>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L733" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45222,7 +47206,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K734" t="inlineStr"/>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L734" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45344,7 +47332,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K736" t="inlineStr"/>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L736" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45466,7 +47458,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K738" t="inlineStr"/>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L738" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45527,7 +47523,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K739" t="inlineStr"/>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L739" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45649,7 +47649,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K741" t="inlineStr"/>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L741" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45710,7 +47714,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K742" t="inlineStr"/>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L742" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45771,7 +47779,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K743" t="inlineStr"/>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L743" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45893,7 +47905,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K745" t="inlineStr"/>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L745" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45954,7 +47970,11 @@
           <t>78.076.237-3</t>
         </is>
       </c>
-      <c r="K746" t="inlineStr"/>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L746" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46015,7 +48035,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K747" t="inlineStr"/>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L747" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46076,7 +48100,11 @@
           <t>77.935.401-6</t>
         </is>
       </c>
-      <c r="K748" t="inlineStr"/>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L748" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46137,7 +48165,11 @@
           <t>77.935.401-6</t>
         </is>
       </c>
-      <c r="K749" t="inlineStr"/>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L749" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46198,7 +48230,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K750" t="inlineStr"/>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L750" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46259,7 +48295,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K751" t="inlineStr"/>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L751" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46381,7 +48421,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K753" t="inlineStr"/>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L753" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46442,7 +48486,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K754" t="inlineStr"/>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L754" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46564,7 +48612,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K756" t="inlineStr"/>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L756" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46625,7 +48677,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K757" t="inlineStr"/>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L757" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46686,7 +48742,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K758" t="inlineStr"/>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L758" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46808,7 +48868,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K760" t="inlineStr"/>
+      <c r="K760" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L760" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46991,7 +49055,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K763" t="inlineStr"/>
+      <c r="K763" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L763" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47113,7 +49181,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K765" t="inlineStr"/>
+      <c r="K765" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L765" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47174,7 +49246,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K766" t="inlineStr"/>
+      <c r="K766" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L766" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47235,7 +49311,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K767" t="inlineStr"/>
+      <c r="K767" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L767" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47296,7 +49376,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K768" t="inlineStr"/>
+      <c r="K768" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L768" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47357,7 +49441,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K769" t="inlineStr"/>
+      <c r="K769" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L769" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47418,7 +49506,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K770" t="inlineStr"/>
+      <c r="K770" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L770" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47540,7 +49632,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K772" t="inlineStr"/>
+      <c r="K772" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L772" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47601,7 +49697,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K773" t="inlineStr"/>
+      <c r="K773" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L773" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47662,7 +49762,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K774" t="inlineStr"/>
+      <c r="K774" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L774" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47906,7 +50010,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K778" t="inlineStr"/>
+      <c r="K778" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L778" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47967,7 +50075,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K779" t="inlineStr"/>
+      <c r="K779" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L779" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48211,7 +50323,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K783" t="inlineStr"/>
+      <c r="K783" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L783" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48272,7 +50388,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K784" t="inlineStr"/>
+      <c r="K784" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L784" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48333,7 +50453,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K785" t="inlineStr"/>
+      <c r="K785" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L785" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48394,7 +50518,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K786" t="inlineStr"/>
+      <c r="K786" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L786" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48516,7 +50644,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K788" t="inlineStr"/>
+      <c r="K788" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L788" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48577,7 +50709,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K789" t="inlineStr"/>
+      <c r="K789" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L789" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48699,7 +50835,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K791" t="inlineStr"/>
+      <c r="K791" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L791" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48760,7 +50900,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K792" t="inlineStr"/>
+      <c r="K792" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L792" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48882,7 +51026,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K794" t="inlineStr"/>
+      <c r="K794" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L794" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49004,7 +51152,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K796" t="inlineStr"/>
+      <c r="K796" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L796" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49187,7 +51339,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K799" t="inlineStr"/>
+      <c r="K799" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L799" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49248,7 +51404,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K800" t="inlineStr"/>
+      <c r="K800" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L800" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49309,7 +51469,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K801" t="inlineStr"/>
+      <c r="K801" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L801" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49370,7 +51534,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K802" t="inlineStr"/>
+      <c r="K802" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L802" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49431,7 +51599,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K803" t="inlineStr"/>
+      <c r="K803" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L803" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49492,7 +51664,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K804" t="inlineStr"/>
+      <c r="K804" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L804" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49553,7 +51729,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K805" t="inlineStr"/>
+      <c r="K805" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L805" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49675,7 +51855,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K807" t="inlineStr"/>
+      <c r="K807" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L807" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49736,7 +51920,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K808" t="inlineStr"/>
+      <c r="K808" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L808" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49797,7 +51985,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K809" t="inlineStr"/>
+      <c r="K809" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L809" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49858,7 +52050,11 @@
           <t>78.203.286-0</t>
         </is>
       </c>
-      <c r="K810" t="inlineStr"/>
+      <c r="K810" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L810" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49980,7 +52176,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K812" t="inlineStr"/>
+      <c r="K812" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L812" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50041,7 +52241,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K813" t="inlineStr"/>
+      <c r="K813" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L813" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50163,7 +52367,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K815" t="inlineStr"/>
+      <c r="K815" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L815" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50285,7 +52493,11 @@
           <t>77.720.988-4</t>
         </is>
       </c>
-      <c r="K817" t="inlineStr"/>
+      <c r="K817" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L817" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50346,7 +52558,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K818" t="inlineStr"/>
+      <c r="K818" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L818" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50407,7 +52623,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K819" t="inlineStr"/>
+      <c r="K819" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L819" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50468,7 +52688,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K820" t="inlineStr"/>
+      <c r="K820" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L820" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50529,7 +52753,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K821" t="inlineStr"/>
+      <c r="K821" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L821" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50651,7 +52879,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K823" t="inlineStr"/>
+      <c r="K823" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L823" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50838,7 +53070,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K826" t="inlineStr"/>
+      <c r="K826" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L826" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50899,7 +53135,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K827" t="inlineStr"/>
+      <c r="K827" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L827" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50960,7 +53200,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K828" t="inlineStr"/>
+      <c r="K828" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L828" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51021,7 +53265,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K829" t="inlineStr"/>
+      <c r="K829" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L829" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51204,7 +53452,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K832" t="inlineStr"/>
+      <c r="K832" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L832" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51265,7 +53517,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K833" t="inlineStr"/>
+      <c r="K833" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L833" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51387,7 +53643,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K835" t="inlineStr"/>
+      <c r="K835" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L835" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51448,7 +53708,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K836" t="inlineStr"/>
+      <c r="K836" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L836" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51509,7 +53773,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K837" t="inlineStr"/>
+      <c r="K837" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L837" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51631,7 +53899,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K839" t="inlineStr"/>
+      <c r="K839" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L839" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51753,7 +54025,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K841" t="inlineStr"/>
+      <c r="K841" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L841" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51814,7 +54090,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K842" t="inlineStr"/>
+      <c r="K842" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L842" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51936,7 +54216,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K844" t="inlineStr"/>
+      <c r="K844" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L844" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51997,7 +54281,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K845" t="inlineStr"/>
+      <c r="K845" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L845" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52058,7 +54346,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K846" t="inlineStr"/>
+      <c r="K846" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L846" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52241,7 +54533,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K849" t="inlineStr"/>
+      <c r="K849" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L849" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52302,7 +54598,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K850" t="inlineStr"/>
+      <c r="K850" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L850" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52363,7 +54663,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K851" t="inlineStr"/>
+      <c r="K851" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L851" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52424,7 +54728,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K852" t="inlineStr"/>
+      <c r="K852" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L852" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52485,7 +54793,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K853" t="inlineStr"/>
+      <c r="K853" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L853" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52546,7 +54858,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K854" t="inlineStr"/>
+      <c r="K854" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L854" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52607,7 +54923,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K855" t="inlineStr"/>
+      <c r="K855" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L855" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52668,7 +54988,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K856" t="inlineStr"/>
+      <c r="K856" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L856" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52729,7 +55053,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K857" t="inlineStr"/>
+      <c r="K857" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L857" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52790,7 +55118,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K858" t="inlineStr"/>
+      <c r="K858" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L858" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52851,7 +55183,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K859" t="inlineStr"/>
+      <c r="K859" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L859" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52973,7 +55309,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K861" t="inlineStr"/>
+      <c r="K861" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L861" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53034,7 +55374,11 @@
           <t>77.786.423-8</t>
         </is>
       </c>
-      <c r="K862" t="inlineStr"/>
+      <c r="K862" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L862" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53156,7 +55500,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K864" t="inlineStr"/>
+      <c r="K864" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L864" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53217,7 +55565,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K865" t="inlineStr"/>
+      <c r="K865" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L865" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53278,7 +55630,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K866" t="inlineStr"/>
+      <c r="K866" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L866" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53339,7 +55695,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K867" t="inlineStr"/>
+      <c r="K867" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L867" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53461,7 +55821,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K869" t="inlineStr"/>
+      <c r="K869" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L869" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53522,7 +55886,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K870" t="inlineStr"/>
+      <c r="K870" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L870" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53766,7 +56134,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K874" t="inlineStr"/>
+      <c r="K874" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L874" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53827,7 +56199,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K875" t="inlineStr"/>
+      <c r="K875" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L875" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53888,7 +56264,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K876" t="inlineStr"/>
+      <c r="K876" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L876" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54254,7 +56634,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K882" t="inlineStr"/>
+      <c r="K882" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L882" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54376,7 +56760,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K884" t="inlineStr"/>
+      <c r="K884" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L884" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54437,7 +56825,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K885" t="inlineStr"/>
+      <c r="K885" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L885" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54498,7 +56890,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K886" t="inlineStr"/>
+      <c r="K886" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L886" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54559,7 +56955,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K887" t="inlineStr"/>
+      <c r="K887" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L887" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54620,7 +57020,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K888" t="inlineStr"/>
+      <c r="K888" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L888" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54681,7 +57085,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K889" t="inlineStr"/>
+      <c r="K889" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L889" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54742,7 +57150,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K890" t="inlineStr"/>
+      <c r="K890" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L890" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54864,7 +57276,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K892" t="inlineStr"/>
+      <c r="K892" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L892" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54925,7 +57341,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K893" t="inlineStr"/>
+      <c r="K893" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L893" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54986,7 +57406,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K894" t="inlineStr"/>
+      <c r="K894" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L894" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55108,7 +57532,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K896" t="inlineStr"/>
+      <c r="K896" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L896" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55291,7 +57719,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K899" t="inlineStr"/>
+      <c r="K899" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L899" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55352,7 +57784,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K900" t="inlineStr"/>
+      <c r="K900" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L900" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55413,7 +57849,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K901" t="inlineStr"/>
+      <c r="K901" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L901" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55474,7 +57914,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K902" t="inlineStr"/>
+      <c r="K902" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L902" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55535,7 +57979,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K903" t="inlineStr"/>
+      <c r="K903" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L903" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55718,7 +58166,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K906" t="inlineStr"/>
+      <c r="K906" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L906" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55840,7 +58292,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K908" t="inlineStr"/>
+      <c r="K908" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L908" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55901,7 +58357,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K909" t="inlineStr"/>
+      <c r="K909" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L909" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55962,7 +58422,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K910" t="inlineStr"/>
+      <c r="K910" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L910" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56023,7 +58487,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K911" t="inlineStr"/>
+      <c r="K911" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L911" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56084,7 +58552,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K912" t="inlineStr"/>
+      <c r="K912" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L912" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56206,7 +58678,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K914" t="inlineStr"/>
+      <c r="K914" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L914" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56267,7 +58743,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K915" t="inlineStr"/>
+      <c r="K915" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L915" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56328,7 +58808,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K916" t="inlineStr"/>
+      <c r="K916" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L916" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56389,7 +58873,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K917" t="inlineStr"/>
+      <c r="K917" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L917" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56450,7 +58938,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K918" t="inlineStr"/>
+      <c r="K918" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L918" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56511,7 +59003,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K919" t="inlineStr"/>
+      <c r="K919" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L919" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56572,7 +59068,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K920" t="inlineStr"/>
+      <c r="K920" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L920" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56633,7 +59133,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K921" t="inlineStr"/>
+      <c r="K921" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L921" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56694,7 +59198,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K922" t="inlineStr"/>
+      <c r="K922" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L922" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56816,7 +59324,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K924" t="inlineStr"/>
+      <c r="K924" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L924" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56877,7 +59389,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K925" t="inlineStr"/>
+      <c r="K925" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L925" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56938,7 +59454,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K926" t="inlineStr"/>
+      <c r="K926" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L926" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56999,7 +59519,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K927" t="inlineStr"/>
+      <c r="K927" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L927" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57060,7 +59584,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K928" t="inlineStr"/>
+      <c r="K928" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L928" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57121,7 +59649,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K929" t="inlineStr"/>
+      <c r="K929" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L929" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57182,7 +59714,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K930" t="inlineStr"/>
+      <c r="K930" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L930" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57243,7 +59779,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K931" t="inlineStr"/>
+      <c r="K931" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L931" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57304,7 +59844,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K932" t="inlineStr"/>
+      <c r="K932" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L932" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57365,7 +59909,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K933" t="inlineStr"/>
+      <c r="K933" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L933" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57426,7 +59974,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K934" t="inlineStr"/>
+      <c r="K934" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L934" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57487,7 +60039,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K935" t="inlineStr"/>
+      <c r="K935" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L935" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57548,7 +60104,11 @@
           <t>78.076.237-3</t>
         </is>
       </c>
-      <c r="K936" t="inlineStr"/>
+      <c r="K936" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L936" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57609,7 +60169,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K937" t="inlineStr"/>
+      <c r="K937" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L937" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57670,7 +60234,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K938" t="inlineStr"/>
+      <c r="K938" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L938" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57731,7 +60299,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K939" t="inlineStr"/>
+      <c r="K939" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L939" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57792,7 +60364,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K940" t="inlineStr"/>
+      <c r="K940" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L940" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57914,7 +60490,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K942" t="inlineStr"/>
+      <c r="K942" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L942" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57975,7 +60555,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K943" t="inlineStr"/>
+      <c r="K943" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L943" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58036,7 +60620,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K944" t="inlineStr"/>
+      <c r="K944" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L944" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58097,7 +60685,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K945" t="inlineStr"/>
+      <c r="K945" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L945" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58158,7 +60750,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K946" t="inlineStr"/>
+      <c r="K946" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L946" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58219,7 +60815,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K947" t="inlineStr"/>
+      <c r="K947" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L947" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58280,7 +60880,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K948" t="inlineStr"/>
+      <c r="K948" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L948" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58341,7 +60945,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K949" t="inlineStr"/>
+      <c r="K949" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L949" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58463,7 +61071,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K951" t="inlineStr"/>
+      <c r="K951" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L951" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58524,7 +61136,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K952" t="inlineStr"/>
+      <c r="K952" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L952" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58585,7 +61201,11 @@
           <t>77.798.686-4</t>
         </is>
       </c>
-      <c r="K953" t="inlineStr"/>
+      <c r="K953" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L953" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58646,7 +61266,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K954" t="inlineStr"/>
+      <c r="K954" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L954" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58707,7 +61331,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K955" t="inlineStr"/>
+      <c r="K955" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L955" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58768,7 +61396,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K956" t="inlineStr"/>
+      <c r="K956" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L956" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58829,7 +61461,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K957" t="inlineStr"/>
+      <c r="K957" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L957" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58951,7 +61587,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K959" t="inlineStr"/>
+      <c r="K959" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L959" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59012,7 +61652,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K960" t="inlineStr"/>
+      <c r="K960" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L960" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59073,7 +61717,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K961" t="inlineStr"/>
+      <c r="K961" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L961" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59134,7 +61782,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K962" t="inlineStr"/>
+      <c r="K962" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L962" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59195,7 +61847,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K963" t="inlineStr"/>
+      <c r="K963" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L963" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59256,7 +61912,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K964" t="inlineStr"/>
+      <c r="K964" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L964" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59378,7 +62038,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K966" t="inlineStr"/>
+      <c r="K966" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L966" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59439,7 +62103,11 @@
           <t>78.061.716-0</t>
         </is>
       </c>
-      <c r="K967" t="inlineStr"/>
+      <c r="K967" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L967" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59500,7 +62168,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K968" t="inlineStr"/>
+      <c r="K968" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L968" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59561,7 +62233,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K969" t="inlineStr"/>
+      <c r="K969" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L969" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59622,7 +62298,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K970" t="inlineStr"/>
+      <c r="K970" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L970" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59683,7 +62363,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K971" t="inlineStr"/>
+      <c r="K971" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L971" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59866,7 +62550,11 @@
           <t>76.539.061-3</t>
         </is>
       </c>
-      <c r="K974" t="inlineStr"/>
+      <c r="K974" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L974" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59927,7 +62615,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K975" t="inlineStr"/>
+      <c r="K975" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L975" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60049,7 +62741,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K977" t="inlineStr"/>
+      <c r="K977" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L977" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60354,7 +63050,11 @@
           <t>77.983.294-5</t>
         </is>
       </c>
-      <c r="K982" t="inlineStr"/>
+      <c r="K982" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L982" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60415,7 +63115,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K983" t="inlineStr"/>
+      <c r="K983" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L983" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60476,7 +63180,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K984" t="inlineStr"/>
+      <c r="K984" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L984" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60537,7 +63245,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K985" t="inlineStr"/>
+      <c r="K985" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L985" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60598,7 +63310,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K986" t="inlineStr"/>
+      <c r="K986" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L986" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60659,7 +63375,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K987" t="inlineStr"/>
+      <c r="K987" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L987" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60781,7 +63501,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K989" t="inlineStr"/>
+      <c r="K989" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L989" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60842,7 +63566,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K990" t="inlineStr"/>
+      <c r="K990" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L990" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60964,7 +63692,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K992" t="inlineStr"/>
+      <c r="K992" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L992" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61025,7 +63757,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K993" t="inlineStr"/>
+      <c r="K993" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L993" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61086,7 +63822,11 @@
           <t>77.935.401-6</t>
         </is>
       </c>
-      <c r="K994" t="inlineStr"/>
+      <c r="K994" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L994" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61147,7 +63887,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K995" t="inlineStr"/>
+      <c r="K995" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L995" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61208,7 +63952,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K996" t="inlineStr"/>
+      <c r="K996" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L996" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61269,7 +64017,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K997" t="inlineStr"/>
+      <c r="K997" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L997" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61330,7 +64082,11 @@
           <t>77.406.941-0</t>
         </is>
       </c>
-      <c r="K998" t="inlineStr"/>
+      <c r="K998" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L998" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61391,7 +64147,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K999" t="inlineStr"/>
+      <c r="K999" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L999" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61452,7 +64212,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K1000" t="inlineStr"/>
+      <c r="K1000" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1000" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/jun-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/jun-2026.xlsx
@@ -757,7 +757,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4784,7 +4788,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5946,7 +5954,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6393,7 +6405,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6779,7 +6795,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8116,7 +8136,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8632,7 +8656,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8693,7 +8721,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9400,7 +9432,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9461,7 +9497,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9648,7 +9688,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9969,7 +10013,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10282,7 +10330,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10599,7 +10651,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11562,7 +11618,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12001,7 +12061,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12062,7 +12126,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13074,7 +13142,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13517,7 +13589,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14159,7 +14235,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14537,7 +14617,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15106,7 +15190,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15683,7 +15771,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15744,7 +15836,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15805,7 +15901,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16187,7 +16287,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16439,7 +16543,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18284,7 +18392,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18605,7 +18717,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18796,7 +18912,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19231,7 +19351,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20763,7 +20887,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20950,7 +21078,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21198,7 +21330,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21710,7 +21846,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21836,7 +21976,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22027,7 +22171,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22149,7 +22297,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22535,7 +22687,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22852,7 +23008,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24254,7 +24414,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24437,7 +24601,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24498,7 +24666,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24742,7 +24914,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25315,7 +25491,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25376,7 +25556,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25762,7 +25946,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26274,7 +26462,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26847,7 +27039,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26908,7 +27104,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26969,7 +27169,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27611,7 +27815,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29549,7 +29757,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30309,7 +30521,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31268,7 +31484,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32101,7 +32321,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32609,7 +32833,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34397,7 +34625,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34523,7 +34755,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36628,7 +36864,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36754,7 +36994,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37327,7 +37571,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K579" t="inlineStr"/>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L579" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37518,7 +37766,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K582" t="inlineStr"/>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L582" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37774,7 +38026,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L586" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38091,7 +38347,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39497,7 +39757,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K613" t="inlineStr"/>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L613" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40318,7 +40582,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K626" t="inlineStr"/>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L626" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40834,7 +41102,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr"/>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L634" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41086,7 +41358,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L638" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41212,7 +41488,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K640" t="inlineStr"/>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L640" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41911,7 +42191,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K651" t="inlineStr"/>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L651" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41972,7 +42256,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L652" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42159,7 +42447,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K655" t="inlineStr"/>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L655" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42220,7 +42512,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K656" t="inlineStr"/>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L656" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43638,7 +43934,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K678" t="inlineStr"/>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L678" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45093,7 +45393,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K701" t="inlineStr"/>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L701" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45731,7 +46035,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K711" t="inlineStr"/>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L711" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46499,7 +46807,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K723" t="inlineStr"/>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L723" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47588,7 +47900,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K740" t="inlineStr"/>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L740" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47844,7 +48160,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K744" t="inlineStr"/>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L744" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48807,7 +49127,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K759" t="inlineStr"/>
+      <c r="K759" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L759" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48933,7 +49257,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K761" t="inlineStr"/>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L761" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48994,7 +49322,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K762" t="inlineStr"/>
+      <c r="K762" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L762" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49888,7 +50220,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K776" t="inlineStr"/>
+      <c r="K776" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L776" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50140,7 +50476,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K780" t="inlineStr"/>
+      <c r="K780" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L780" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50262,7 +50602,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K782" t="inlineStr"/>
+      <c r="K782" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L782" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50774,7 +51118,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K790" t="inlineStr"/>
+      <c r="K790" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L790" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50965,7 +51313,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K793" t="inlineStr"/>
+      <c r="K793" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L793" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51278,7 +51630,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K798" t="inlineStr"/>
+      <c r="K798" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L798" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52306,7 +52662,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K814" t="inlineStr"/>
+      <c r="K814" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L814" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52818,7 +53178,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K822" t="inlineStr"/>
+      <c r="K822" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L822" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55760,7 +56124,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K868" t="inlineStr"/>
+      <c r="K868" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L868" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57597,7 +57965,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K897" t="inlineStr"/>
+      <c r="K897" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L897" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58231,7 +58603,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K907" t="inlineStr"/>
+      <c r="K907" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L907" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60429,7 +60805,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K941" t="inlineStr"/>
+      <c r="K941" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L941" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61977,7 +62357,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K965" t="inlineStr"/>
+      <c r="K965" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L965" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62489,7 +62873,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K973" t="inlineStr"/>
+      <c r="K973" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L973" t="inlineStr">
         <is>
           <t>USD</t>
